--- a/research/model/intel_valuation_model.xlsx
+++ b/research/model/intel_valuation_model.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -617,116 +617,144 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
+          <t>- China layer: the China DOMESTIC share of DCAI+CCPG revenue (China-billed share x domestic fraction) erodes at a scenario-specific annual rate</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
+          <t xml:space="preserve">  (xinchuang substitution, Hygon/Loongson/Kunpeng, retaliatory tariffs on US-fabbed chips); the loss is subtracted from revenue at full gross margin.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>- Not modeled as a line item: a Taiwan disruption. It would hit Intel too (TSMC makes Lunar/Arrow Lake tiles, part of Panther/Nova Lake).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Geopolitical second-source demand for US fabs is already inside the external-foundry drivers (Base/Bull), so it isn't added twice.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
+          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      customer, external foundry stays mostly Altera + small packaging deals; 18A cost parity slips; gross margin stays near 2026 levels.</t>
+          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
+          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
+          <t xml:space="preserve">      customer, external foundry stays mostly Altera + small packaging deals; 18A cost parity slips; gross margin stays near 2026 levels.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT CAVEATS</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
+          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
+          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANT CAVEATS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
+          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>- Not investment advice.</t>
         </is>
@@ -743,7 +771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -795,15 +823,15 @@
         </is>
       </c>
       <c r="B4" s="32">
-        <f>Inputs!$B$68</f>
+        <f>Inputs!$B$79</f>
         <v/>
       </c>
       <c r="C4" s="32">
-        <f>Inputs!$B$69</f>
+        <f>Inputs!$B$80</f>
         <v/>
       </c>
       <c r="D4" s="32">
-        <f>Inputs!$B$70</f>
+        <f>Inputs!$B$81</f>
         <v/>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -819,15 +847,15 @@
         </is>
       </c>
       <c r="B5" s="33">
-        <f>Bear!B40</f>
+        <f>Bear!B43</f>
         <v/>
       </c>
       <c r="C5" s="33">
-        <f>Base!B40</f>
+        <f>Base!B43</f>
         <v/>
       </c>
       <c r="D5" s="33">
-        <f>Bull!B40</f>
+        <f>Bull!B43</f>
         <v/>
       </c>
       <c r="E5" s="34">
@@ -847,15 +875,15 @@
         </is>
       </c>
       <c r="B6" s="32">
-        <f>Bear!B42</f>
+        <f>Bear!B45</f>
         <v/>
       </c>
       <c r="C6" s="32">
-        <f>Base!B42</f>
+        <f>Base!B45</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Bull!B42</f>
+        <f>Bull!B45</f>
         <v/>
       </c>
       <c r="E6" s="35">
@@ -863,7 +891,7 @@
         <v/>
       </c>
       <c r="F6" s="2">
-        <f>IF(ABS(Inputs!$B$71-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
+        <f>IF(ABS(Inputs!$B$82-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
         <v/>
       </c>
     </row>
@@ -874,15 +902,15 @@
         </is>
       </c>
       <c r="B7" s="36">
-        <f>Bear!B34</f>
+        <f>Bear!B37</f>
         <v/>
       </c>
       <c r="C7" s="36">
-        <f>Base!B34</f>
+        <f>Base!B37</f>
         <v/>
       </c>
       <c r="D7" s="36">
-        <f>Bull!B34</f>
+        <f>Bull!B37</f>
         <v/>
       </c>
     </row>
@@ -893,15 +921,15 @@
         </is>
       </c>
       <c r="B8" s="32">
-        <f>Bear!B43</f>
+        <f>Bear!B46</f>
         <v/>
       </c>
       <c r="C8" s="32">
-        <f>Base!B43</f>
+        <f>Base!B46</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Bull!B43</f>
+        <f>Bull!B46</f>
         <v/>
       </c>
     </row>
@@ -912,15 +940,15 @@
         </is>
       </c>
       <c r="B9" s="36">
-        <f>Bear!F11</f>
+        <f>Bear!F14</f>
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Base!F11</f>
+        <f>Base!F14</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Bull!F11</f>
+        <f>Bull!F14</f>
         <v/>
       </c>
     </row>
@@ -931,15 +959,15 @@
         </is>
       </c>
       <c r="B10" s="36">
-        <f>Bear!I11</f>
+        <f>Bear!I14</f>
         <v/>
       </c>
       <c r="C10" s="36">
-        <f>Base!I11</f>
+        <f>Base!I14</f>
         <v/>
       </c>
       <c r="D10" s="36">
-        <f>Bull!I11</f>
+        <f>Bull!I14</f>
         <v/>
       </c>
     </row>
@@ -950,15 +978,15 @@
         </is>
       </c>
       <c r="B11" s="32">
-        <f>Bear!F13</f>
+        <f>Bear!F16</f>
         <v/>
       </c>
       <c r="C11" s="32">
-        <f>Base!F13</f>
+        <f>Base!F16</f>
         <v/>
       </c>
       <c r="D11" s="32">
-        <f>Bull!F13</f>
+        <f>Bull!F16</f>
         <v/>
       </c>
     </row>
@@ -969,15 +997,15 @@
         </is>
       </c>
       <c r="B12" s="32">
-        <f>Bear!F17</f>
+        <f>Bear!F20</f>
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>Base!F17</f>
+        <f>Base!F20</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>Bull!F17</f>
+        <f>Bull!F20</f>
         <v/>
       </c>
     </row>
@@ -1003,347 +1031,366 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>2030 unlevered FCF</t>
+          <t>2033 revenue lost to China localization / trade</t>
         </is>
       </c>
       <c r="B14" s="36">
-        <f>Bear!F25</f>
+        <f>Bear!I13</f>
         <v/>
       </c>
       <c r="C14" s="36">
-        <f>Base!F25</f>
+        <f>Base!I13</f>
         <v/>
       </c>
       <c r="D14" s="36">
-        <f>Bull!F25</f>
+        <f>Bull!I13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>2030 unlevered FCF</t>
+        </is>
+      </c>
+      <c r="B15" s="36">
+        <f>Bear!F28</f>
+        <v/>
+      </c>
+      <c r="C15" s="36">
+        <f>Base!F28</f>
+        <v/>
+      </c>
+      <c r="D15" s="36">
+        <f>Bull!F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Cumulative FCF 2027-2033</t>
         </is>
       </c>
-      <c r="B15" s="36">
-        <f>SUM(Bear!C25:I25)</f>
-        <v/>
-      </c>
-      <c r="C15" s="36">
-        <f>SUM(Base!C25:I25)</f>
-        <v/>
-      </c>
-      <c r="D15" s="36">
-        <f>SUM(Bull!C25:I25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="B16" s="36">
+        <f>SUM(Bear!C28:I28)</f>
+        <v/>
+      </c>
+      <c r="C16" s="36">
+        <f>SUM(Base!C28:I28)</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>SUM(Bull!C28:I28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>MARKET SNAPSHOT</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Share price ($)</t>
-        </is>
-      </c>
-      <c r="B18" s="33">
-        <f>Inputs!$B$4</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares (bn)</t>
-        </is>
-      </c>
-      <c r="B19" s="37">
-        <f>Inputs!$B$9</f>
+          <t>Share price ($)</t>
+        </is>
+      </c>
+      <c r="B19" s="33">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Market cap</t>
-        </is>
-      </c>
-      <c r="B20" s="36">
-        <f>Inputs!$B$17</f>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B20" s="37">
+        <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value at market</t>
+          <t>Market cap</t>
         </is>
       </c>
       <c r="B21" s="36">
-        <f>Inputs!$B$18</f>
+        <f>Inputs!$B$17</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="B22" s="32">
-        <f>Inputs!$B$52</f>
+          <t>Enterprise value at market</t>
+        </is>
+      </c>
+      <c r="B22" s="36">
+        <f>Inputs!$B$18</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B23" s="32">
+        <f>Inputs!$B$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B23" s="32">
-        <f>Inputs!$B$53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="B24" s="32">
+        <f>Inputs!$B$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>REVERSE DCF: WHAT DOES TODAY'S PRICE REQUIRE? (holding Base explicit-period cash flows)</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>EV at market</t>
-        </is>
-      </c>
-      <c r="B26" s="38">
-        <f>Inputs!$B$18</f>
-        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PV of Base explicit FCF 2027-2033</t>
-        </is>
-      </c>
-      <c r="B27" s="36">
-        <f>Base!B31</f>
+          <t>EV at market</t>
+        </is>
+      </c>
+      <c r="B27" s="38">
+        <f>Inputs!$B$18</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PV of terminal value required</t>
-        </is>
-      </c>
-      <c r="B28" s="38">
-        <f>B26-B27</f>
+          <t>PV of Base explicit FCF 2027-2033</t>
+        </is>
+      </c>
+      <c r="B28" s="36">
+        <f>Base!B34</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Required normalized 2034 FCF</t>
+          <t>PV of terminal value required</t>
         </is>
       </c>
       <c r="B29" s="38">
-        <f>B28/Base!I27*(Inputs!$B$52-Inputs!$B$53)</f>
-        <v/>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>FCF in 2034 that the Base explicit years plus the market price imply</t>
-        </is>
+        <f>B27-B28</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Base-case normalized 2034 FCF</t>
-        </is>
-      </c>
-      <c r="B30" s="36">
-        <f>Base!J25</f>
-        <v/>
+          <t>Required normalized 2034 FCF</t>
+        </is>
+      </c>
+      <c r="B30" s="38">
+        <f>B29/Base!I30*(Inputs!$B$62-Inputs!$B$63)</f>
+        <v/>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>FCF in 2034 that the Base explicit years plus the market price imply</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Required / Base terminal FCF</t>
-        </is>
-      </c>
-      <c r="B31" s="11">
-        <f>IF(B30=0,0,B29/B30)</f>
+          <t>Base-case normalized 2034 FCF</t>
+        </is>
+      </c>
+      <c r="B31" s="36">
+        <f>Base!J28</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Base 2034 revenue</t>
-        </is>
-      </c>
-      <c r="B32" s="36">
-        <f>Base!J11</f>
+          <t>Required / Base terminal FCF</t>
+        </is>
+      </c>
+      <c r="B32" s="11">
+        <f>IF(B31=0,0,B30/B31)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Required 2034 FCF margin on Base revenue</t>
-        </is>
-      </c>
-      <c r="B33" s="39">
-        <f>IF(B32=0,0,B29/B32)</f>
+          <t>Base 2034 revenue</t>
+        </is>
+      </c>
+      <c r="B33" s="36">
+        <f>Base!J14</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Base 2034 FCF margin</t>
-        </is>
-      </c>
-      <c r="B34" s="32">
-        <f>Base!J26</f>
+          <t>Required 2034 FCF margin on Base revenue</t>
+        </is>
+      </c>
+      <c r="B34" s="39">
+        <f>IF(B33=0,0,B30/B33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Reference: TSMC Q2-26 operating margin (not FCF margin)</t>
-        </is>
-      </c>
-      <c r="B35" s="40" t="n">
-        <v>0.603</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Source: TSMC Q2 2026 results (60.3% op margin). Context only</t>
-        </is>
+          <t>Base 2034 FCF margin</t>
+        </is>
+      </c>
+      <c r="B35" s="32">
+        <f>Base!J29</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Market-implied perpetual FCF from today (EV x (WACC - g))</t>
-        </is>
-      </c>
-      <c r="B36" s="38">
-        <f>Inputs!$B$18*(Inputs!$B$52-Inputs!$B$53)</f>
-        <v/>
+          <t>Reference: TSMC Q2-26 operating margin (not FCF margin)</t>
+        </is>
+      </c>
+      <c r="B36" s="40" t="n">
+        <v>0.603</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Source: TSMC Q2 2026 results (60.3% op margin). Context only</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Base 2027 FCF, for comparison</t>
-        </is>
-      </c>
-      <c r="B37" s="36">
-        <f>Base!C25</f>
+          <t>Market-implied perpetual FCF from today (EV x (WACC - g))</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>Inputs!$B$18*(Inputs!$B$62-Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Required 2034 revenue if FCF margin = 20%</t>
-        </is>
-      </c>
-      <c r="B38" s="38">
-        <f>B29/0.20</f>
+          <t>Base 2027 FCF, for comparison</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>Base!C28</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Required 2034 revenue if FCF margin = 25%</t>
+          <t>Required 2034 revenue if FCF margin = 20%</t>
         </is>
       </c>
       <c r="B39" s="38">
-        <f>B29/0.25</f>
+        <f>B30/0.20</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Required 2034 revenue if FCF margin = 30%</t>
+          <t>Required 2034 revenue if FCF margin = 25%</t>
         </is>
       </c>
       <c r="B40" s="38">
-        <f>B29/0.30</f>
+        <f>B30/0.25</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Bull-case 2034 revenue, for comparison</t>
+          <t>Required 2034 revenue if FCF margin = 30%</t>
         </is>
       </c>
       <c r="B41" s="38">
-        <f>Bull!J11</f>
+        <f>B30/0.30</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>Bull-case 2034 revenue, for comparison</t>
+        </is>
+      </c>
+      <c r="B42" s="38">
+        <f>Bull!J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Bull-case 2034 FCF margin, for comparison</t>
         </is>
       </c>
-      <c r="B42" s="39">
-        <f>Bull!J26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="B43" s="39">
+        <f>Bull!J29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>HOW TO READ THIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
+          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
+          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>- Terminal value is a large share of EV in every scenario. Small changes in WACC or terminal growth move the answer a lot: see the Sensitivity sheet.</t>
         </is>
@@ -1414,23 +1461,23 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B5" s="41">
-        <f>IF($A5&lt;=B$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+B$4)+Bear!$I$22*(1+B$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*B$4)/($A5-B$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A5&lt;=B$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+B$4)+Bear!$I$25*(1+B$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*B$4)/($A5-B$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C5" s="41">
-        <f>IF($A5&lt;=C$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+C$4)+Bear!$I$22*(1+C$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*C$4)/($A5-C$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A5&lt;=C$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+C$4)+Bear!$I$25*(1+C$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*C$4)/($A5-C$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D5" s="41">
-        <f>IF($A5&lt;=D$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+D$4)+Bear!$I$22*(1+D$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*D$4)/($A5-D$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A5&lt;=D$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+D$4)+Bear!$I$25*(1+D$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*D$4)/($A5-D$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E5" s="41">
-        <f>IF($A5&lt;=E$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+E$4)+Bear!$I$22*(1+E$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*E$4)/($A5-E$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A5&lt;=E$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+E$4)+Bear!$I$25*(1+E$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*E$4)/($A5-E$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F5" s="41">
-        <f>IF($A5&lt;=F$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+F$4)+Bear!$I$22*(1+F$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*F$4)/($A5-F$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A5&lt;=F$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A5)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+F$4)+Bear!$I$25*(1+F$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*F$4)/($A5-F$4)/(1+$A5)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1439,23 +1486,23 @@
         <v>0.095</v>
       </c>
       <c r="B6" s="41">
-        <f>IF($A6&lt;=B$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+B$4)+Bear!$I$22*(1+B$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*B$4)/($A6-B$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A6&lt;=B$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+B$4)+Bear!$I$25*(1+B$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*B$4)/($A6-B$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C6" s="41">
-        <f>IF($A6&lt;=C$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+C$4)+Bear!$I$22*(1+C$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*C$4)/($A6-C$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A6&lt;=C$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+C$4)+Bear!$I$25*(1+C$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*C$4)/($A6-C$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D6" s="41">
-        <f>IF($A6&lt;=D$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+D$4)+Bear!$I$22*(1+D$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*D$4)/($A6-D$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A6&lt;=D$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+D$4)+Bear!$I$25*(1+D$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*D$4)/($A6-D$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E6" s="41">
-        <f>IF($A6&lt;=E$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+E$4)+Bear!$I$22*(1+E$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*E$4)/($A6-E$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A6&lt;=E$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+E$4)+Bear!$I$25*(1+E$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*E$4)/($A6-E$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F6" s="41">
-        <f>IF($A6&lt;=F$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+F$4)+Bear!$I$22*(1+F$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*F$4)/($A6-F$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A6&lt;=F$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A6)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+F$4)+Bear!$I$25*(1+F$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*F$4)/($A6-F$4)/(1+$A6)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1464,23 +1511,23 @@
         <v>0.105</v>
       </c>
       <c r="B7" s="41">
-        <f>IF($A7&lt;=B$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+B$4)+Bear!$I$22*(1+B$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*B$4)/($A7-B$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A7&lt;=B$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+B$4)+Bear!$I$25*(1+B$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*B$4)/($A7-B$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C7" s="41">
-        <f>IF($A7&lt;=C$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+C$4)+Bear!$I$22*(1+C$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*C$4)/($A7-C$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A7&lt;=C$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+C$4)+Bear!$I$25*(1+C$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*C$4)/($A7-C$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D7" s="41">
-        <f>IF($A7&lt;=D$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+D$4)+Bear!$I$22*(1+D$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*D$4)/($A7-D$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A7&lt;=D$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+D$4)+Bear!$I$25*(1+D$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*D$4)/($A7-D$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E7" s="41">
-        <f>IF($A7&lt;=E$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+E$4)+Bear!$I$22*(1+E$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*E$4)/($A7-E$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A7&lt;=E$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+E$4)+Bear!$I$25*(1+E$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*E$4)/($A7-E$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F7" s="41">
-        <f>IF($A7&lt;=F$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+F$4)+Bear!$I$22*(1+F$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*F$4)/($A7-F$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A7&lt;=F$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A7)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+F$4)+Bear!$I$25*(1+F$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*F$4)/($A7-F$4)/(1+$A7)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1489,23 +1536,23 @@
         <v>0.115</v>
       </c>
       <c r="B8" s="41">
-        <f>IF($A8&lt;=B$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+B$4)+Bear!$I$22*(1+B$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*B$4)/($A8-B$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A8&lt;=B$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+B$4)+Bear!$I$25*(1+B$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*B$4)/($A8-B$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C8" s="41">
-        <f>IF($A8&lt;=C$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+C$4)+Bear!$I$22*(1+C$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*C$4)/($A8-C$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A8&lt;=C$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+C$4)+Bear!$I$25*(1+C$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*C$4)/($A8-C$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D8" s="41">
-        <f>IF($A8&lt;=D$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+D$4)+Bear!$I$22*(1+D$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*D$4)/($A8-D$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A8&lt;=D$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+D$4)+Bear!$I$25*(1+D$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*D$4)/($A8-D$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E8" s="41">
-        <f>IF($A8&lt;=E$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+E$4)+Bear!$I$22*(1+E$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*E$4)/($A8-E$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A8&lt;=E$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+E$4)+Bear!$I$25*(1+E$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*E$4)/($A8-E$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F8" s="41">
-        <f>IF($A8&lt;=F$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+F$4)+Bear!$I$22*(1+F$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*F$4)/($A8-F$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A8&lt;=F$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A8)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+F$4)+Bear!$I$25*(1+F$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*F$4)/($A8-F$4)/(1+$A8)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1514,23 +1561,23 @@
         <v>0.125</v>
       </c>
       <c r="B9" s="41">
-        <f>IF($A9&lt;=B$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+B$4)+Bear!$I$22*(1+B$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*B$4)/($A9-B$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A9&lt;=B$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+B$4)+Bear!$I$25*(1+B$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*B$4)/($A9-B$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C9" s="41">
-        <f>IF($A9&lt;=C$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+C$4)+Bear!$I$22*(1+C$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*C$4)/($A9-C$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A9&lt;=C$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+C$4)+Bear!$I$25*(1+C$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*C$4)/($A9-C$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D9" s="41">
-        <f>IF($A9&lt;=D$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+D$4)+Bear!$I$22*(1+D$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*D$4)/($A9-D$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A9&lt;=D$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+D$4)+Bear!$I$25*(1+D$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*D$4)/($A9-D$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E9" s="41">
-        <f>IF($A9&lt;=E$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+E$4)+Bear!$I$22*(1+E$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*E$4)/($A9-E$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A9&lt;=E$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+E$4)+Bear!$I$25*(1+E$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*E$4)/($A9-E$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F9" s="41">
-        <f>IF($A9&lt;=F$4,0,(SUMPRODUCT(Bear!$C$25:$I$25,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$21*(1+F$4)+Bear!$I$22*(1+F$4)*(1-Inputs!$B$54)-Inputs!$B$55*Bear!$I$11*F$4)/($A9-F$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A9&lt;=F$4,0,(SUMPRODUCT(Bear!$C$28:$I$28,1/(1+$A9)^Bear!$C$4:$I$4)+(Bear!$I$24*(1+F$4)+Bear!$I$25*(1+F$4)*(1-Inputs!$B$64)-Inputs!$B$65*Bear!$I$14*F$4)/($A9-F$4)/(1+$A9)^Bear!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1568,23 +1615,23 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B13" s="41">
-        <f>IF($A13&lt;=B$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$21*(1+B$12)+Base!$I$22*(1+B$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*B$12)/($A13-B$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A13&lt;=B$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$24*(1+B$12)+Base!$I$25*(1+B$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*B$12)/($A13-B$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C13" s="41">
-        <f>IF($A13&lt;=C$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$21*(1+C$12)+Base!$I$22*(1+C$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*C$12)/($A13-C$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A13&lt;=C$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$24*(1+C$12)+Base!$I$25*(1+C$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*C$12)/($A13-C$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D13" s="41">
-        <f>IF($A13&lt;=D$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$21*(1+D$12)+Base!$I$22*(1+D$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*D$12)/($A13-D$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A13&lt;=D$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$24*(1+D$12)+Base!$I$25*(1+D$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*D$12)/($A13-D$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E13" s="41">
-        <f>IF($A13&lt;=E$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$21*(1+E$12)+Base!$I$22*(1+E$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*E$12)/($A13-E$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A13&lt;=E$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$24*(1+E$12)+Base!$I$25*(1+E$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*E$12)/($A13-E$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F13" s="41">
-        <f>IF($A13&lt;=F$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$21*(1+F$12)+Base!$I$22*(1+F$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*F$12)/($A13-F$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A13&lt;=F$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A13)^Base!$C$4:$I$4)+(Base!$I$24*(1+F$12)+Base!$I$25*(1+F$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*F$12)/($A13-F$12)/(1+$A13)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1640,23 @@
         <v>0.095</v>
       </c>
       <c r="B14" s="41">
-        <f>IF($A14&lt;=B$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$21*(1+B$12)+Base!$I$22*(1+B$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*B$12)/($A14-B$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A14&lt;=B$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$24*(1+B$12)+Base!$I$25*(1+B$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*B$12)/($A14-B$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C14" s="41">
-        <f>IF($A14&lt;=C$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$21*(1+C$12)+Base!$I$22*(1+C$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*C$12)/($A14-C$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A14&lt;=C$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$24*(1+C$12)+Base!$I$25*(1+C$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*C$12)/($A14-C$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D14" s="41">
-        <f>IF($A14&lt;=D$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$21*(1+D$12)+Base!$I$22*(1+D$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*D$12)/($A14-D$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A14&lt;=D$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$24*(1+D$12)+Base!$I$25*(1+D$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*D$12)/($A14-D$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E14" s="41">
-        <f>IF($A14&lt;=E$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$21*(1+E$12)+Base!$I$22*(1+E$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*E$12)/($A14-E$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A14&lt;=E$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$24*(1+E$12)+Base!$I$25*(1+E$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*E$12)/($A14-E$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F14" s="41">
-        <f>IF($A14&lt;=F$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$21*(1+F$12)+Base!$I$22*(1+F$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*F$12)/($A14-F$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A14&lt;=F$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A14)^Base!$C$4:$I$4)+(Base!$I$24*(1+F$12)+Base!$I$25*(1+F$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*F$12)/($A14-F$12)/(1+$A14)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1618,23 +1665,23 @@
         <v>0.105</v>
       </c>
       <c r="B15" s="41">
-        <f>IF($A15&lt;=B$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$21*(1+B$12)+Base!$I$22*(1+B$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*B$12)/($A15-B$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A15&lt;=B$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$24*(1+B$12)+Base!$I$25*(1+B$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*B$12)/($A15-B$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C15" s="41">
-        <f>IF($A15&lt;=C$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$21*(1+C$12)+Base!$I$22*(1+C$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*C$12)/($A15-C$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A15&lt;=C$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$24*(1+C$12)+Base!$I$25*(1+C$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*C$12)/($A15-C$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D15" s="41">
-        <f>IF($A15&lt;=D$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$21*(1+D$12)+Base!$I$22*(1+D$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*D$12)/($A15-D$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A15&lt;=D$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$24*(1+D$12)+Base!$I$25*(1+D$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*D$12)/($A15-D$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E15" s="41">
-        <f>IF($A15&lt;=E$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$21*(1+E$12)+Base!$I$22*(1+E$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*E$12)/($A15-E$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A15&lt;=E$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$24*(1+E$12)+Base!$I$25*(1+E$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*E$12)/($A15-E$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F15" s="41">
-        <f>IF($A15&lt;=F$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$21*(1+F$12)+Base!$I$22*(1+F$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*F$12)/($A15-F$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A15&lt;=F$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A15)^Base!$C$4:$I$4)+(Base!$I$24*(1+F$12)+Base!$I$25*(1+F$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*F$12)/($A15-F$12)/(1+$A15)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1643,23 +1690,23 @@
         <v>0.115</v>
       </c>
       <c r="B16" s="41">
-        <f>IF($A16&lt;=B$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$21*(1+B$12)+Base!$I$22*(1+B$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*B$12)/($A16-B$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A16&lt;=B$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$24*(1+B$12)+Base!$I$25*(1+B$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*B$12)/($A16-B$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C16" s="41">
-        <f>IF($A16&lt;=C$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$21*(1+C$12)+Base!$I$22*(1+C$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*C$12)/($A16-C$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A16&lt;=C$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$24*(1+C$12)+Base!$I$25*(1+C$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*C$12)/($A16-C$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D16" s="41">
-        <f>IF($A16&lt;=D$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$21*(1+D$12)+Base!$I$22*(1+D$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*D$12)/($A16-D$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A16&lt;=D$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$24*(1+D$12)+Base!$I$25*(1+D$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*D$12)/($A16-D$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E16" s="41">
-        <f>IF($A16&lt;=E$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$21*(1+E$12)+Base!$I$22*(1+E$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*E$12)/($A16-E$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A16&lt;=E$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$24*(1+E$12)+Base!$I$25*(1+E$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*E$12)/($A16-E$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F16" s="41">
-        <f>IF($A16&lt;=F$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$21*(1+F$12)+Base!$I$22*(1+F$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*F$12)/($A16-F$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A16&lt;=F$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A16)^Base!$C$4:$I$4)+(Base!$I$24*(1+F$12)+Base!$I$25*(1+F$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*F$12)/($A16-F$12)/(1+$A16)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1668,23 +1715,23 @@
         <v>0.125</v>
       </c>
       <c r="B17" s="41">
-        <f>IF($A17&lt;=B$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$21*(1+B$12)+Base!$I$22*(1+B$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*B$12)/($A17-B$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A17&lt;=B$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$24*(1+B$12)+Base!$I$25*(1+B$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*B$12)/($A17-B$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C17" s="41">
-        <f>IF($A17&lt;=C$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$21*(1+C$12)+Base!$I$22*(1+C$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*C$12)/($A17-C$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A17&lt;=C$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$24*(1+C$12)+Base!$I$25*(1+C$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*C$12)/($A17-C$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D17" s="41">
-        <f>IF($A17&lt;=D$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$21*(1+D$12)+Base!$I$22*(1+D$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*D$12)/($A17-D$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A17&lt;=D$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$24*(1+D$12)+Base!$I$25*(1+D$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*D$12)/($A17-D$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E17" s="41">
-        <f>IF($A17&lt;=E$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$21*(1+E$12)+Base!$I$22*(1+E$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*E$12)/($A17-E$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A17&lt;=E$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$24*(1+E$12)+Base!$I$25*(1+E$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*E$12)/($A17-E$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F17" s="41">
-        <f>IF($A17&lt;=F$12,0,(SUMPRODUCT(Base!$C$25:$I$25,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$21*(1+F$12)+Base!$I$22*(1+F$12)*(1-Inputs!$B$54)-Inputs!$B$55*Base!$I$11*F$12)/($A17-F$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A17&lt;=F$12,0,(SUMPRODUCT(Base!$C$28:$I$28,1/(1+$A17)^Base!$C$4:$I$4)+(Base!$I$24*(1+F$12)+Base!$I$25*(1+F$12)*(1-Inputs!$B$64)-Inputs!$B$65*Base!$I$14*F$12)/($A17-F$12)/(1+$A17)^Base!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1722,23 +1769,23 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="B21" s="41">
-        <f>IF($A21&lt;=B$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+B$20)+Bull!$I$22*(1+B$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*B$20)/($A21-B$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A21&lt;=B$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+B$20)+Bull!$I$25*(1+B$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*B$20)/($A21-B$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C21" s="41">
-        <f>IF($A21&lt;=C$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+C$20)+Bull!$I$22*(1+C$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*C$20)/($A21-C$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A21&lt;=C$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+C$20)+Bull!$I$25*(1+C$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*C$20)/($A21-C$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D21" s="41">
-        <f>IF($A21&lt;=D$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+D$20)+Bull!$I$22*(1+D$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*D$20)/($A21-D$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A21&lt;=D$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+D$20)+Bull!$I$25*(1+D$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*D$20)/($A21-D$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E21" s="41">
-        <f>IF($A21&lt;=E$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+E$20)+Bull!$I$22*(1+E$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*E$20)/($A21-E$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A21&lt;=E$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+E$20)+Bull!$I$25*(1+E$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*E$20)/($A21-E$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F21" s="41">
-        <f>IF($A21&lt;=F$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+F$20)+Bull!$I$22*(1+F$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*F$20)/($A21-F$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A21&lt;=F$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A21)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+F$20)+Bull!$I$25*(1+F$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*F$20)/($A21-F$20)/(1+$A21)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1747,23 +1794,23 @@
         <v>0.095</v>
       </c>
       <c r="B22" s="41">
-        <f>IF($A22&lt;=B$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+B$20)+Bull!$I$22*(1+B$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*B$20)/($A22-B$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A22&lt;=B$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+B$20)+Bull!$I$25*(1+B$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*B$20)/($A22-B$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C22" s="41">
-        <f>IF($A22&lt;=C$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+C$20)+Bull!$I$22*(1+C$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*C$20)/($A22-C$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A22&lt;=C$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+C$20)+Bull!$I$25*(1+C$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*C$20)/($A22-C$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>IF($A22&lt;=D$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+D$20)+Bull!$I$22*(1+D$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*D$20)/($A22-D$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A22&lt;=D$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+D$20)+Bull!$I$25*(1+D$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*D$20)/($A22-D$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>IF($A22&lt;=E$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+E$20)+Bull!$I$22*(1+E$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*E$20)/($A22-E$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A22&lt;=E$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+E$20)+Bull!$I$25*(1+E$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*E$20)/($A22-E$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>IF($A22&lt;=F$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+F$20)+Bull!$I$22*(1+F$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*F$20)/($A22-F$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A22&lt;=F$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A22)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+F$20)+Bull!$I$25*(1+F$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*F$20)/($A22-F$20)/(1+$A22)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1772,23 +1819,23 @@
         <v>0.105</v>
       </c>
       <c r="B23" s="41">
-        <f>IF($A23&lt;=B$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+B$20)+Bull!$I$22*(1+B$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*B$20)/($A23-B$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A23&lt;=B$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+B$20)+Bull!$I$25*(1+B$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*B$20)/($A23-B$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C23" s="41">
-        <f>IF($A23&lt;=C$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+C$20)+Bull!$I$22*(1+C$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*C$20)/($A23-C$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A23&lt;=C$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+C$20)+Bull!$I$25*(1+C$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*C$20)/($A23-C$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D23" s="41">
-        <f>IF($A23&lt;=D$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+D$20)+Bull!$I$22*(1+D$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*D$20)/($A23-D$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A23&lt;=D$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+D$20)+Bull!$I$25*(1+D$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*D$20)/($A23-D$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E23" s="41">
-        <f>IF($A23&lt;=E$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+E$20)+Bull!$I$22*(1+E$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*E$20)/($A23-E$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A23&lt;=E$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+E$20)+Bull!$I$25*(1+E$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*E$20)/($A23-E$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F23" s="41">
-        <f>IF($A23&lt;=F$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+F$20)+Bull!$I$22*(1+F$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*F$20)/($A23-F$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A23&lt;=F$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A23)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+F$20)+Bull!$I$25*(1+F$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*F$20)/($A23-F$20)/(1+$A23)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1797,23 +1844,23 @@
         <v>0.115</v>
       </c>
       <c r="B24" s="41">
-        <f>IF($A24&lt;=B$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+B$20)+Bull!$I$22*(1+B$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*B$20)/($A24-B$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A24&lt;=B$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+B$20)+Bull!$I$25*(1+B$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*B$20)/($A24-B$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C24" s="41">
-        <f>IF($A24&lt;=C$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+C$20)+Bull!$I$22*(1+C$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*C$20)/($A24-C$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A24&lt;=C$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+C$20)+Bull!$I$25*(1+C$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*C$20)/($A24-C$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D24" s="41">
-        <f>IF($A24&lt;=D$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+D$20)+Bull!$I$22*(1+D$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*D$20)/($A24-D$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A24&lt;=D$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+D$20)+Bull!$I$25*(1+D$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*D$20)/($A24-D$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E24" s="41">
-        <f>IF($A24&lt;=E$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+E$20)+Bull!$I$22*(1+E$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*E$20)/($A24-E$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A24&lt;=E$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+E$20)+Bull!$I$25*(1+E$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*E$20)/($A24-E$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F24" s="41">
-        <f>IF($A24&lt;=F$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+F$20)+Bull!$I$22*(1+F$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*F$20)/($A24-F$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A24&lt;=F$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A24)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+F$20)+Bull!$I$25*(1+F$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*F$20)/($A24-F$20)/(1+$A24)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1822,23 +1869,23 @@
         <v>0.125</v>
       </c>
       <c r="B25" s="41">
-        <f>IF($A25&lt;=B$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+B$20)+Bull!$I$22*(1+B$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*B$20)/($A25-B$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A25&lt;=B$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+B$20)+Bull!$I$25*(1+B$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*B$20)/($A25-B$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="C25" s="41">
-        <f>IF($A25&lt;=C$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+C$20)+Bull!$I$22*(1+C$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*C$20)/($A25-C$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A25&lt;=C$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+C$20)+Bull!$I$25*(1+C$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*C$20)/($A25-C$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="D25" s="41">
-        <f>IF($A25&lt;=D$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+D$20)+Bull!$I$22*(1+D$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*D$20)/($A25-D$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A25&lt;=D$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+D$20)+Bull!$I$25*(1+D$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*D$20)/($A25-D$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="E25" s="41">
-        <f>IF($A25&lt;=E$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+E$20)+Bull!$I$22*(1+E$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*E$20)/($A25-E$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A25&lt;=E$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+E$20)+Bull!$I$25*(1+E$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*E$20)/($A25-E$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
       <c r="F25" s="41">
-        <f>IF($A25&lt;=F$20,0,(SUMPRODUCT(Bull!$C$25:$I$25,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$21*(1+F$20)+Bull!$I$22*(1+F$20)*(1-Inputs!$B$54)-Inputs!$B$55*Bull!$I$11*F$20)/($A25-F$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9)</f>
+        <f>MAX(0,IF($A25&lt;=F$20,0,(SUMPRODUCT(Bull!$C$28:$I$28,1/(1+$A25)^Bull!$C$4:$I$4)+(Bull!$I$24*(1+F$20)+Bull!$I$25*(1+F$20)*(1-Inputs!$B$64)-Inputs!$B$65*Bull!$I$14*F$20)/($A25-F$20)/(1+$A25)^Bull!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
@@ -1894,13 +1941,13 @@
         </is>
       </c>
       <c r="B31" s="42" t="n">
-        <v>19.13</v>
+        <v>16.94</v>
       </c>
       <c r="C31" s="42" t="n">
-        <v>36.77</v>
+        <v>32.43</v>
       </c>
       <c r="D31" s="43">
-        <f>Base!B40</f>
+        <f>Base!B43</f>
         <v/>
       </c>
       <c r="E31" s="44">
@@ -1911,17 +1958,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>DCAI growth -3 / +3 pts per yr</t>
+          <t>China erosion 10 pts/yr faster / 5 pts/yr slower</t>
         </is>
       </c>
       <c r="B32" s="42" t="n">
-        <v>20.23</v>
+        <v>19.98</v>
       </c>
       <c r="C32" s="42" t="n">
-        <v>29.39</v>
+        <v>23.72</v>
       </c>
       <c r="D32" s="43">
-        <f>Base!B40</f>
+        <f>Base!B43</f>
         <v/>
       </c>
       <c r="E32" s="44">
@@ -1932,17 +1979,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Gross margin -3 / +3 pts, all years</t>
+          <t>DCAI growth -3 / +3 pts per yr</t>
         </is>
       </c>
       <c r="B33" s="42" t="n">
-        <v>19.97</v>
+        <v>18.07</v>
       </c>
       <c r="C33" s="42" t="n">
-        <v>28.92</v>
+        <v>26.82</v>
       </c>
       <c r="D33" s="43">
-        <f>Base!B40</f>
+        <f>Base!B43</f>
         <v/>
       </c>
       <c r="E33" s="44">
@@ -1953,21 +2000,42 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Capex x1.15 / x0.85 (2027+)</t>
+          <t>Gross margin -3 / +3 pts, all years</t>
         </is>
       </c>
       <c r="B34" s="42" t="n">
-        <v>22.07</v>
+        <v>17.77</v>
       </c>
       <c r="C34" s="42" t="n">
-        <v>26.83</v>
+        <v>26.43</v>
       </c>
       <c r="D34" s="43">
-        <f>Base!B40</f>
+        <f>Base!B43</f>
         <v/>
       </c>
       <c r="E34" s="44">
         <f>C34-B34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Capex x1.15 / x0.85 (2027+)</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="C35" s="42" t="n">
+        <v>24.48</v>
+      </c>
+      <c r="D35" s="43">
+        <f>Base!B43</f>
+        <v/>
+      </c>
+      <c r="E35" s="44">
+        <f>C35-B35</f>
         <v/>
       </c>
     </row>
@@ -1989,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J108"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2587,7 +2655,7 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>VALUATION PARAMETERS</t>
+          <t>CHINA EXPOSURE</t>
         </is>
       </c>
     </row>
@@ -2606,1283 +2674,1570 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B45" s="53" t="n">
-        <v>0.043</v>
+          <t>FY2024 China (incl. HK) billed revenue</t>
+        </is>
+      </c>
+      <c r="B45" s="47" t="n">
+        <v>15.53</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION: ~10y UST; update</t>
+          <t>Intel FY2024 10-K geographic note (billing location); 29% of revenue</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B46" s="53" t="n">
-        <v>0.05</v>
+          <t>FY2025 total revenue</t>
+        </is>
+      </c>
+      <c r="B46" s="47" t="n">
+        <v>52.9</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>Intel Q4/FY2025 results (22 Jan 2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Equity beta</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="n">
-        <v>1.3</v>
+          <t>FY2025 US + Taiwan + Singapore + Other billed revenue</t>
+        </is>
+      </c>
+      <c r="B47" s="51">
+        <f>15.76+7.67+9.54+7.20</f>
+        <v/>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION: semis/turnaround risk</t>
+          <t>FY2025 10-K geographic note via search extract (US 15.76, Taiwan 7.67, Singapore 9.54, Other 7.20); VERIFY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-      <c r="B48" s="39">
-        <f>$B$45+$B$47*$B$46</f>
+          <t>FY2025 China billed revenue (derived residual)</t>
+        </is>
+      </c>
+      <c r="B48" s="51">
+        <f>$B$46-$B$47</f>
         <v/>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>CAPM</t>
+          <t>Derived = total - other regions. Not read directly from the 10-K; VERIFY</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Pre-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="B49" s="40" t="n">
-        <v>0.055</v>
+          <t>China billed share of revenue (FY2025)</t>
+        </is>
+      </c>
+      <c r="B49" s="39">
+        <f>IF($B$46=0,0,$B$48/$B$46)</f>
+        <v/>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Tax rate</t>
+          <t>Share of China-billed revenue that is China DOMESTIC end-demand</t>
         </is>
       </c>
       <c r="B50" s="53" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION: normalized cash tax; Intel has large NOLs near term</t>
+          <t>JUDGMENT. Billing location includes PCs/servers assembled in China for export (Lenovo, ODMs), which domestic substitution does not hit. No source splits this; test 0.35-0.70</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Debt weight</t>
-        </is>
-      </c>
-      <c r="B51" s="39">
-        <f>$B$13/($B$13+$B$17)</f>
-        <v/>
-      </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Market-value weights</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="B52" s="39">
-        <f>(1-$B$51)*$B$48+$B$51*$B$49*(1-$B$50)</f>
-        <v/>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Formula</t>
+          <t>China levers: xinchuang bans Intel/AMD in government PCs &amp; servers (Mar 2024); Hygon+Zhaoxin ~15-20% of China server CPUs, Kunpeng 8-12% (2026 est.); Loongson 1M desktop CPUs; China customs treats WAFER-FAB location as origin -&gt; US-fabbed chips (Intel) face retaliatory tariffs, TSMC-made rivals don't; US-China truce expires 10 Nov 2026.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Terminal FCF growth</t>
-        </is>
-      </c>
-      <c r="B53" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION PARAMETERS</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Terminal capex / D&amp;A ratio</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>ASSUMPTION: maintenance + modest growth capex in steady state</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Net working capital, % of revenue change</t>
-        </is>
-      </c>
-      <c r="B55" s="40" t="n">
-        <v>0.1</v>
+          <t>Risk-free rate</t>
+        </is>
+      </c>
+      <c r="B55" s="53" t="n">
+        <v>0.043</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION</t>
+          <t>ASSUMPTION: ~10y UST; update</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A catch-up toward prior-year capex (per year)</t>
-        </is>
-      </c>
-      <c r="B56" s="40" t="n">
-        <v>0.15</v>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
+      <c r="B56" s="53" t="n">
+        <v>0.05</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A(t) = D&amp;A(t-1) + x * (capex(t-1) - D&amp;A(t-1))</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Discount period offset (valuation date 30 Sep 2026)</t>
-        </is>
-      </c>
-      <c r="B57" s="26" t="n">
-        <v>0.25</v>
+          <t>Equity beta</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="n">
+        <v>1.3</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>End-2027 cash flow is 1.25 years out</t>
+          <t>ASSUMPTION: semis/turnaround risk</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Other revenue growth (all scenarios)</t>
-        </is>
-      </c>
-      <c r="B58" s="40" t="n">
-        <v>0.05</v>
+          <t>Cost of equity</t>
+        </is>
+      </c>
+      <c r="B58" s="39">
+        <f>$B$55+$B$57*$B$56</f>
+        <v/>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
+          <t>CAPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B59" s="40" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>ASSUMPTION</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>FLEX LEVERS (for sensitivity; leave at defaults 0 / 0 / 1 / 1)</t>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="B60" s="53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMPTION: normalized cash tax; Intel has large NOLs near term</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Gross margin shift, all years, all scenarios (pts)</t>
-        </is>
-      </c>
-      <c r="B61" s="40" t="n">
-        <v>0</v>
+          <t>Debt weight</t>
+        </is>
+      </c>
+      <c r="B61" s="39">
+        <f>$B$13/($B$13+$B$17)</f>
+        <v/>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>e.g. -0.03 = 3 pts lower</t>
+          <t>Market-value weights</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DCAI growth shift per year (pts)</t>
-        </is>
-      </c>
-      <c r="B62" s="40" t="n">
-        <v>0</v>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B62" s="39">
+        <f>(1-$B$61)*$B$58+$B$61*$B$59*(1-$B$60)</f>
+        <v/>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>e.g. 0.03 = +3 pts/yr</t>
+          <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>External foundry revenue multiplier</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="n">
-        <v>1</v>
+          <t>Terminal FCF growth</t>
+        </is>
+      </c>
+      <c r="B63" s="53" t="n">
+        <v>0.03</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>e.g. 0.5 = half</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Capex multiplier (2027+)</t>
+          <t>Terminal capex / D&amp;A ratio</t>
         </is>
       </c>
       <c r="B64" s="25" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>e.g. 1.15 = 15% more</t>
+          <t>ASSUMPTION: maintenance + modest growth capex in steady state</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Net working capital, % of revenue change</t>
+        </is>
+      </c>
+      <c r="B65" s="40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>SCENARIO WEIGHTS (judgment; must sum to 100%)</t>
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A catch-up toward prior-year capex (per year)</t>
+        </is>
+      </c>
+      <c r="B66" s="40" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A(t) = D&amp;A(t-1) + x * (capex(t-1) - D&amp;A(t-1))</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Weight</t>
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Discount period offset (valuation date 30 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>End-2027 cash flow is 1.25 years out</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B68" s="53" t="n">
-        <v>0.3</v>
+          <t>Other revenue growth (all scenarios)</t>
+        </is>
+      </c>
+      <c r="B68" s="40" t="n">
+        <v>0.05</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>My judgment; edit</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="B69" s="53" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>My judgment; edit</t>
+          <t>ASSUMPTION</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="B70" s="53" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>My judgment; edit</t>
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>FLEX LEVERS (for sensitivity; leave at defaults 0 / 0 / 1 / 1)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Check: sum of weights</t>
-        </is>
-      </c>
-      <c r="B71" s="39">
-        <f>$B$68+$B$69+$B$70</f>
-        <v/>
+          <t>Gross margin shift, all years, all scenarios (pts)</t>
+        </is>
+      </c>
+      <c r="B71" s="40" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Must equal 100%</t>
+          <t>e.g. -0.03 = 3 pts lower</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>DCAI growth shift per year (pts)</t>
+        </is>
+      </c>
+      <c r="B72" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>e.g. 0.03 = +3 pts/yr</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>SCENARIO DRIVERS (2027-2033). Hypothetical paths tied to product evidence; NOT forecasts I endorse</t>
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>External foundry revenue multiplier</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>e.g. 0.5 = half</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="inlineStr">
-        <is>
-          <t>DCAI revenue growth</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Capex multiplier (2027+)</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>e.g. 1.15 = 15% more</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
+          <t>China domestic revenue change shift per year (pts)</t>
+        </is>
+      </c>
+      <c r="B75" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>e.g. -0.10 = 10 pts faster erosion every year</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>SCENARIO WEIGHTS (judgment; must sum to 100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="C75" s="53" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="D75" s="53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E75" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G75" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H75" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I75" s="53" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DCAI revenue growth - Base</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B79" s="53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C76" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D76" s="53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E76" s="53" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F76" s="53" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G76" s="53" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H76" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I76" s="53" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C77" s="53" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D77" s="53" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E77" s="53" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F77" s="53" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G77" s="53" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H77" s="53" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I77" s="53" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Bear: shortage ASP spike (+48% YoY in Q2-26) reverses as Venice ships Q4-26 and Diamond Rapids slips; Bull: DMR competitive + agentic CPU demand persists</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>CCPG (client) revenue growth</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
+      <c r="B80" s="53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C81" s="53" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="D81" s="53" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="E81" s="53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F81" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G81" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H81" s="53" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I81" s="53" t="n">
-        <v>-0.01</v>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="B81" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C82" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D82" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E82" s="53" t="n">
+          <t>Check: sum of weights</t>
+        </is>
+      </c>
+      <c r="B82" s="39">
+        <f>$B$79+$B$80+$B$81</f>
+        <v/>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>Must equal 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>SCENARIO DRIVERS (2027-2033). Hypothetical paths tied to product evidence; NOT forecasts I endorse</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>DCAI revenue growth</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C86" s="53" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D86" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E86" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="53" t="n">
         <v>0.02</v>
       </c>
-      <c r="F82" s="53" t="n">
+      <c r="G86" s="53" t="n">
         <v>0.02</v>
       </c>
-      <c r="G82" s="53" t="n">
+      <c r="H86" s="53" t="n">
         <v>0.02</v>
       </c>
-      <c r="H82" s="53" t="n">
+      <c r="I86" s="53" t="n">
         <v>0.02</v>
-      </c>
-      <c r="I82" s="53" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C83" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D83" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E83" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F83" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G83" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H83" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I83" s="53" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>External foundry + packaging revenue ($bn)</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
+          <t xml:space="preserve">  DCAI revenue growth - Base</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C87" s="52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D87" s="52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E87" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F87" s="52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G87" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="H87" s="52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I87" s="52" t="n">
-        <v>4</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C87" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D87" s="53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E87" s="53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F87" s="53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G87" s="53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H87" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I87" s="53" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
+          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C88" s="52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D88" s="52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E88" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="F88" s="52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G88" s="52" t="n">
-        <v>11</v>
-      </c>
-      <c r="H88" s="52" t="n">
-        <v>13</v>
-      </c>
-      <c r="I88" s="52" t="n">
-        <v>15</v>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C88" s="53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D88" s="53" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E88" s="53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F88" s="53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G88" s="53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H88" s="53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I88" s="53" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C89" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" s="52" t="n">
-        <v>7</v>
-      </c>
-      <c r="E89" s="52" t="n">
-        <v>12</v>
-      </c>
-      <c r="F89" s="52" t="n">
-        <v>18</v>
-      </c>
-      <c r="G89" s="52" t="n">
-        <v>24</v>
-      </c>
-      <c r="H89" s="52" t="n">
-        <v>29</v>
-      </c>
-      <c r="I89" s="52" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
+          <t xml:space="preserve">  Rationale: Bear: shortage ASP spike (+48% YoY in Q2-26) reverses as Venice ships Q4-26 and Diamond Rapids slips; Bull: DMR competitive + agentic CPU demand persists</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>CCPG (client) revenue growth</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C92" s="53" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D92" s="53" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E92" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F92" s="53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="G92" s="53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="H92" s="53" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I92" s="53" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C93" s="53" t="n">
-        <v>0.39</v>
+        <v>-0.02</v>
       </c>
       <c r="D93" s="53" t="n">
-        <v>0.39</v>
+        <v>0.01</v>
       </c>
       <c r="E93" s="53" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="F93" s="53" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="G93" s="53" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="H93" s="53" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="I93" s="53" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Base</t>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="C94" s="53" t="n">
-        <v>0.43</v>
+        <v>0.04</v>
       </c>
       <c r="D94" s="53" t="n">
-        <v>0.45</v>
+        <v>0.04</v>
       </c>
       <c r="E94" s="53" t="n">
-        <v>0.47</v>
+        <v>0.03</v>
       </c>
       <c r="F94" s="53" t="n">
-        <v>0.48</v>
+        <v>0.03</v>
       </c>
       <c r="G94" s="53" t="n">
-        <v>0.49</v>
+        <v>0.03</v>
       </c>
       <c r="H94" s="53" t="n">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="I94" s="53" t="n">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C95" s="53" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="D95" s="53" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E95" s="53" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F95" s="53" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G95" s="53" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H95" s="53" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I95" s="53" t="n">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
+          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>External foundry + packaging revenue ($bn)</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP opex growth</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C98" s="52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D98" s="52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E98" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G98" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H98" s="52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I98" s="52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="D99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H99" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I99" s="53" t="n">
-        <v>0.01</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C99" s="52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D99" s="52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E99" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F99" s="52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G99" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="H99" s="52" t="n">
+        <v>13</v>
+      </c>
+      <c r="I99" s="52" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="D100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H100" s="53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I100" s="53" t="n">
-        <v>0.03</v>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C100" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="F100" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="G100" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="H100" s="52" t="n">
+        <v>29</v>
+      </c>
+      <c r="I100" s="52" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I101" s="53" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
+          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="inlineStr">
-        <is>
-          <t>Gross capex ($bn)</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G104" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C104" s="53" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D104" s="53" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E104" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F104" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G104" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H104" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I104" s="53" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Base</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C105" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="D105" s="52" t="n">
-        <v>18</v>
-      </c>
-      <c r="E105" s="52" t="n">
-        <v>16</v>
-      </c>
-      <c r="F105" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="G105" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="H105" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="I105" s="52" t="n">
-        <v>15</v>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C105" s="53" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D105" s="53" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E105" s="53" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F105" s="53" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G105" s="53" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H105" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I105" s="53" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C106" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="D106" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="E106" s="52" t="n">
-        <v>24</v>
-      </c>
-      <c r="F106" s="52" t="n">
-        <v>22</v>
-      </c>
-      <c r="G106" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="H106" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="I106" s="52" t="n">
-        <v>20</v>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C106" s="53" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D106" s="53" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E106" s="53" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="F106" s="53" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G106" s="53" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H106" s="53" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I106" s="53" t="n">
+        <v>0.57</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP opex growth</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I110" s="53" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I111" s="53" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I112" s="53" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>China domestic end-demand revenue change per year</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bear</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C116" s="53" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D116" s="53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E116" s="53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F116" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G116" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H116" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I116" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Base</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C117" s="53" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D117" s="53" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E117" s="53" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F117" s="53" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G117" s="53" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H117" s="53" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I117" s="53" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bull</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I118" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: Bear: truce lapses Nov-26, xinchuang spreads from government to SOEs/finance/telecom, and origin rule hits 18A (US-fabbed) parts. Base: steady localization. Bull: truce holds, erosion slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>Gross capex ($bn)</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C122" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="D122" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E122" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="F122" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="G122" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="H122" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="I122" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C123" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="D123" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="E123" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F123" s="52" t="n">
+        <v>22</v>
+      </c>
+      <c r="G123" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H123" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="I123" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Gross capex ($bn) - Bull</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
-      <c r="C107" s="52" t="n">
+      <c r="C124" s="52" t="n">
         <v>30</v>
       </c>
-      <c r="D107" s="52" t="n">
+      <c r="D124" s="52" t="n">
         <v>32</v>
       </c>
-      <c r="E107" s="52" t="n">
+      <c r="E124" s="52" t="n">
         <v>30</v>
       </c>
-      <c r="F107" s="52" t="n">
+      <c r="F124" s="52" t="n">
         <v>28</v>
       </c>
-      <c r="G107" s="52" t="n">
+      <c r="G124" s="52" t="n">
         <v>26</v>
       </c>
-      <c r="H107" s="52" t="n">
+      <c r="H124" s="52" t="n">
         <v>26</v>
       </c>
-      <c r="I107" s="52" t="n">
+      <c r="I124" s="52" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rationale: 2027 guided 'significantly above' 2026 (&gt;$20bn). Gross; excludes SCIP partner/government offsets (conservative)</t>
         </is>
@@ -3899,7 +4254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3980,31 +4335,31 @@
         </is>
       </c>
       <c r="C4" s="27">
-        <f>Inputs!$B$57+1</f>
+        <f>Inputs!$B$67+1</f>
         <v/>
       </c>
       <c r="D4" s="27">
-        <f>Inputs!$B$57+2</f>
+        <f>Inputs!$B$67+2</f>
         <v/>
       </c>
       <c r="E4" s="27">
-        <f>Inputs!$B$57+3</f>
+        <f>Inputs!$B$67+3</f>
         <v/>
       </c>
       <c r="F4" s="27">
-        <f>Inputs!$B$57+4</f>
+        <f>Inputs!$B$67+4</f>
         <v/>
       </c>
       <c r="G4" s="27">
-        <f>Inputs!$B$57+5</f>
+        <f>Inputs!$B$67+5</f>
         <v/>
       </c>
       <c r="H4" s="27">
-        <f>Inputs!$B$57+6</f>
+        <f>Inputs!$B$67+6</f>
         <v/>
       </c>
       <c r="I4" s="27">
-        <f>Inputs!$B$57+7</f>
+        <f>Inputs!$B$67+7</f>
         <v/>
       </c>
     </row>
@@ -4054,31 +4409,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C75+Inputs!$B$62</f>
+        <f>Inputs!C86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D75+Inputs!$B$62</f>
+        <f>Inputs!D86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E75+Inputs!$B$62</f>
+        <f>Inputs!E86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F75+Inputs!$B$62</f>
+        <f>Inputs!F86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G75+Inputs!$B$62</f>
+        <f>Inputs!G86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H75+Inputs!$B$62</f>
+        <f>Inputs!H86+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I75+Inputs!$B$62</f>
+        <f>Inputs!I86+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -4128,31 +4483,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C81</f>
+        <f>Inputs!C92</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D81</f>
+        <f>Inputs!D92</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E81</f>
+        <f>Inputs!E92</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F81</f>
+        <f>Inputs!F92</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G81</f>
+        <f>Inputs!G92</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H81</f>
+        <f>Inputs!H92</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I81</f>
+        <f>Inputs!I92</f>
         <v/>
       </c>
     </row>
@@ -4167,31 +4522,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C87*Inputs!$B$63</f>
+        <f>Inputs!C98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D87*Inputs!$B$63</f>
+        <f>Inputs!D98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E87*Inputs!$B$63</f>
+        <f>Inputs!E98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F87*Inputs!$B$63</f>
+        <f>Inputs!F98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G87*Inputs!$B$63</f>
+        <f>Inputs!G98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H87*Inputs!$B$63</f>
+        <f>Inputs!H98*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I87*Inputs!$B$63</f>
+        <f>Inputs!I98*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -4206,899 +4561,1015 @@
         <v/>
       </c>
       <c r="C10" s="38">
-        <f>B10*(1+Inputs!$B$58)</f>
+        <f>B10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="D10" s="38">
-        <f>C10*(1+Inputs!$B$58)</f>
+        <f>C10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="E10" s="38">
-        <f>D10*(1+Inputs!$B$58)</f>
+        <f>D10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="F10" s="38">
-        <f>E10*(1+Inputs!$B$58)</f>
+        <f>E10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="G10" s="38">
-        <f>F10*(1+Inputs!$B$58)</f>
+        <f>F10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="H10" s="38">
-        <f>G10*(1+Inputs!$B$58)</f>
+        <f>G10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="I10" s="38">
-        <f>H10*(1+Inputs!$B$58)</f>
+        <f>H10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="54">
-        <f>SUM(B5,B7,B9,B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="54">
-        <f>SUM(C5,C7,C9,C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="54">
-        <f>SUM(D5,D7,D9,D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="54">
-        <f>SUM(E5,E7,E9,E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="54">
-        <f>SUM(F5,F7,F9,F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="54">
-        <f>SUM(G5,G7,G9,G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="54">
-        <f>SUM(H5,H7,H9,H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="54">
-        <f>SUM(I5,I7,I9,I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="54">
-        <f>I11*(1+Inputs!$B$53)</f>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>China domestic-demand revenue exposed (pre-erosion)</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>(B5+B7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="C11" s="38">
+        <f>(C5+C7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>(D5+D7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>(E5+E7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="F11" s="38">
+        <f>(F5+F7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G11" s="38">
+        <f>(G5+G7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="H11" s="38">
+        <f>(H5+H7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="I11" s="38">
+        <f>(I5+I7)*Inputs!$B$49*Inputs!$B$50</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  growth</t>
-        </is>
-      </c>
-      <c r="C12" s="39">
-        <f>IF(B11=0,0,C11/B11-1)</f>
-        <v/>
-      </c>
-      <c r="D12" s="39">
-        <f>IF(C11=0,0,D11/C11-1)</f>
-        <v/>
-      </c>
-      <c r="E12" s="39">
-        <f>IF(D11=0,0,E11/D11-1)</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
-        <f>IF(E11=0,0,F11/E11-1)</f>
-        <v/>
-      </c>
-      <c r="G12" s="39">
-        <f>IF(F11=0,0,G11/F11-1)</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>IF(G11=0,0,H11/G11-1)</f>
-        <v/>
-      </c>
-      <c r="I12" s="39">
-        <f>IF(H11=0,0,I11/H11-1)</f>
+          <t xml:space="preserve">  China erosion index (2026 = 1.00)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="27">
+        <f>MAX(0,B12*(1+Inputs!C116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>MAX(0,C12*(1+Inputs!D116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>MAX(0,D12*(1+Inputs!E116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>MAX(0,E12*(1+Inputs!F116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>MAX(0,F12*(1+Inputs!G116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>MAX(0,G12*(1+Inputs!H116+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>MAX(0,H12*(1+Inputs!I116+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B13" s="32">
-        <f>Inputs!$B$32+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>Inputs!C93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="D13" s="32">
-        <f>Inputs!D93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="E13" s="32">
-        <f>Inputs!E93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="F13" s="32">
-        <f>Inputs!F93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="G13" s="32">
-        <f>Inputs!G93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="H13" s="32">
-        <f>Inputs!H93+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="I13" s="32">
-        <f>Inputs!I93+Inputs!$B$61</f>
+          <t>Less: China localization / trade revenue loss</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>-B11*(1-B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>-C11*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>-D11*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>-E11*(1-E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>-F11*(1-F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>-G11*(1-G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>-H11*(1-H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38">
+        <f>-I11*(1-I12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B14" s="38">
-        <f>B11*B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="38">
-        <f>C11*C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="38">
-        <f>D11*D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="38">
-        <f>E11*E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="38">
-        <f>F11*F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="38">
-        <f>G11*G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="38">
-        <f>H11*H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="38">
-        <f>I11*I13</f>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="54">
+        <f>SUM(B5,B7,B9,B10,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="54">
+        <f>SUM(C5,C7,C9,C10,C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="54">
+        <f>SUM(D5,D7,D9,D10,D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>SUM(E5,E7,E9,E10,E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="54">
+        <f>SUM(F5,F7,F9,F10,F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="54">
+        <f>SUM(G5,G7,G9,G10,G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="54">
+        <f>SUM(H5,H7,H9,H10,H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="54">
+        <f>SUM(I5,I7,I9,I10,I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="54">
+        <f>I14*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP opex</t>
-        </is>
-      </c>
-      <c r="B15" s="36">
-        <f>Inputs!$B$33</f>
-        <v/>
-      </c>
-      <c r="C15" s="38">
-        <f>B15*(1+Inputs!C99)</f>
-        <v/>
-      </c>
-      <c r="D15" s="38">
-        <f>C15*(1+Inputs!D99)</f>
-        <v/>
-      </c>
-      <c r="E15" s="38">
-        <f>D15*(1+Inputs!E99)</f>
-        <v/>
-      </c>
-      <c r="F15" s="38">
-        <f>E15*(1+Inputs!F99)</f>
-        <v/>
-      </c>
-      <c r="G15" s="38">
-        <f>F15*(1+Inputs!G99)</f>
-        <v/>
-      </c>
-      <c r="H15" s="38">
-        <f>G15*(1+Inputs!H99)</f>
-        <v/>
-      </c>
-      <c r="I15" s="38">
-        <f>H15*(1+Inputs!I99)</f>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>IF(B14=0,0,C14/B14-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="39">
+        <f>IF(C14=0,0,D14/C14-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
+        <f>IF(D14=0,0,E14/D14-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="39">
+        <f>IF(E14=0,0,F14/E14-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>IF(F14=0,0,G14/F14-1)</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>IF(G14=0,0,H14/G14-1)</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>IF(H14=0,0,I14/H14-1)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Non-GAAP operating income</t>
-        </is>
-      </c>
-      <c r="B16" s="54">
-        <f>B14-B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="54">
-        <f>C14-C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="54">
-        <f>D14-D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="54">
-        <f>E14-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="54">
-        <f>F14-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="54">
-        <f>G14-G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="54">
-        <f>H14-H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="54">
-        <f>I14-I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="30" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>Inputs!$B$32+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>Inputs!C104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>Inputs!D104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>Inputs!E104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>Inputs!F104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>Inputs!G104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>Inputs!H104+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>Inputs!I104+Inputs!$B$71</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  operating margin</t>
-        </is>
-      </c>
-      <c r="B17" s="39">
-        <f>IF(B11=0,0,B16/B11)</f>
-        <v/>
-      </c>
-      <c r="C17" s="39">
-        <f>IF(C11=0,0,C16/C11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>IF(D11=0,0,D16/D11)</f>
-        <v/>
-      </c>
-      <c r="E17" s="39">
-        <f>IF(E11=0,0,E16/E11)</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
-        <f>IF(F11=0,0,F16/F11)</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>IF(G11=0,0,G16/G11)</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>IF(H11=0,0,H16/H11)</f>
-        <v/>
-      </c>
-      <c r="I17" s="39">
-        <f>IF(I11=0,0,I16/I11)</f>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="38">
+        <f>C14*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>D14*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E14*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="38">
+        <f>F14*F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="38">
+        <f>G14*G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>H14*H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>I14*I16</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Non-GAAP opex</t>
         </is>
       </c>
       <c r="B18" s="36">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$33</f>
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C99)</f>
+        <f>B18*(1+Inputs!C110)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D99)</f>
+        <f>C18*(1+Inputs!D110)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E99)</f>
+        <f>D18*(1+Inputs!E110)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F99)</f>
+        <f>E18*(1+Inputs!F110)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G99)</f>
+        <f>F18*(1+Inputs!G110)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H99)</f>
+        <f>G18*(1+Inputs!H110)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I99)</f>
+        <f>H18*(1+Inputs!I110)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>EBIT after SBC</t>
-        </is>
-      </c>
-      <c r="C19" s="38">
-        <f>C16-C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="38">
-        <f>D16-D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="38">
-        <f>E16-E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="38">
-        <f>F16-F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="38">
-        <f>G16-G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="38">
-        <f>H16-H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="38">
-        <f>I16-I18</f>
-        <v/>
-      </c>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B19" s="54">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="54">
+        <f>C17-C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="54">
+        <f>D17-D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>E17-E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="54">
+        <f>F17-F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="54">
+        <f>G17-G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="54">
+        <f>H17-H18</f>
+        <v/>
+      </c>
+      <c r="I19" s="54">
+        <f>I17-I18</f>
+        <v/>
+      </c>
+      <c r="J19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Taxes on EBIT</t>
-        </is>
-      </c>
-      <c r="C20" s="38">
-        <f>MAX(0,C19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="D20" s="38">
-        <f>MAX(0,D19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="E20" s="38">
-        <f>MAX(0,E19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="F20" s="38">
-        <f>MAX(0,F19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="G20" s="38">
-        <f>MAX(0,G19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="H20" s="38">
-        <f>MAX(0,H19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="I20" s="38">
-        <f>MAX(0,I19)*Inputs!$B$50</f>
+          <t xml:space="preserve">  operating margin</t>
+        </is>
+      </c>
+      <c r="B20" s="39">
+        <f>IF(B14=0,0,B19/B14)</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>IF(C14=0,0,C19/C14)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>IF(D14=0,0,D19/D14)</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
+        <f>IF(E14=0,0,E19/E14)</f>
+        <v/>
+      </c>
+      <c r="F20" s="39">
+        <f>IF(F14=0,0,F19/F14)</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>IF(G14=0,0,G19/G14)</f>
+        <v/>
+      </c>
+      <c r="H20" s="39">
+        <f>IF(H14=0,0,H19/H14)</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>IF(I14=0,0,I19/I14)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NOPAT</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
+        <f>Inputs!$B$34</f>
+        <v/>
       </c>
       <c r="C21" s="38">
-        <f>C19-C20</f>
+        <f>B21*(1+Inputs!C110)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>D19-D20</f>
+        <f>C21*(1+Inputs!D110)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>E19-E20</f>
+        <f>D21*(1+Inputs!E110)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>F19-F20</f>
+        <f>E21*(1+Inputs!F110)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>G19-G20</f>
+        <f>F21*(1+Inputs!G110)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>H19-H20</f>
+        <f>G21*(1+Inputs!H110)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>I19-I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="38">
-        <f>I21*(1+Inputs!$B$53)</f>
+        <f>H21*(1+Inputs!I110)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B22" s="36">
-        <f>Inputs!$B$35</f>
-        <v/>
+          <t>EBIT after SBC</t>
+        </is>
       </c>
       <c r="C22" s="38">
-        <f>B22+Inputs!$B$56*(B23-B22)</f>
+        <f>C19-C21</f>
         <v/>
       </c>
       <c r="D22" s="38">
-        <f>C22+Inputs!$B$56*(C23-C22)</f>
+        <f>D19-D21</f>
         <v/>
       </c>
       <c r="E22" s="38">
-        <f>D22+Inputs!$B$56*(D23-D22)</f>
+        <f>E19-E21</f>
         <v/>
       </c>
       <c r="F22" s="38">
-        <f>E22+Inputs!$B$56*(E23-E22)</f>
+        <f>F19-F21</f>
         <v/>
       </c>
       <c r="G22" s="38">
-        <f>F22+Inputs!$B$56*(F23-F22)</f>
+        <f>G19-G21</f>
         <v/>
       </c>
       <c r="H22" s="38">
-        <f>G22+Inputs!$B$56*(G23-G22)</f>
+        <f>H19-H21</f>
         <v/>
       </c>
       <c r="I22" s="38">
-        <f>H22+Inputs!$B$56*(H23-H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="38">
-        <f>I22*(1+Inputs!$B$53)</f>
+        <f>I19-I21</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="B23" s="36">
-        <f>Inputs!$B$36</f>
-        <v/>
-      </c>
-      <c r="C23" s="36">
-        <f>Inputs!C105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
-        <f>Inputs!D105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="E23" s="36">
-        <f>Inputs!E105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="F23" s="36">
-        <f>Inputs!F105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="G23" s="36">
-        <f>Inputs!G105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="H23" s="36">
-        <f>Inputs!H105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="I23" s="36">
-        <f>Inputs!I105*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="J23" s="38">
-        <f>J22*Inputs!$B$54</f>
+          <t>Taxes on EBIT</t>
+        </is>
+      </c>
+      <c r="C23" s="38">
+        <f>MAX(0,C22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
+        <f>MAX(0,D22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>MAX(0,E22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="F23" s="38">
+        <f>MAX(0,F22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G23" s="38">
+        <f>MAX(0,G22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="H23" s="38">
+        <f>MAX(0,H22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="I23" s="38">
+        <f>MAX(0,I22)*Inputs!$B$60</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Change in net working capital</t>
+          <t>NOPAT</t>
         </is>
       </c>
       <c r="C24" s="38">
-        <f>Inputs!$B$55*(C11-B11)</f>
+        <f>C22-C23</f>
         <v/>
       </c>
       <c r="D24" s="38">
-        <f>Inputs!$B$55*(D11-C11)</f>
+        <f>D22-D23</f>
         <v/>
       </c>
       <c r="E24" s="38">
-        <f>Inputs!$B$55*(E11-D11)</f>
+        <f>E22-E23</f>
         <v/>
       </c>
       <c r="F24" s="38">
-        <f>Inputs!$B$55*(F11-E11)</f>
+        <f>F22-F23</f>
         <v/>
       </c>
       <c r="G24" s="38">
-        <f>Inputs!$B$55*(G11-F11)</f>
+        <f>G22-G23</f>
         <v/>
       </c>
       <c r="H24" s="38">
-        <f>Inputs!$B$55*(H11-G11)</f>
+        <f>H22-H23</f>
         <v/>
       </c>
       <c r="I24" s="38">
-        <f>Inputs!$B$55*(I11-H11)</f>
+        <f>I22-I23</f>
         <v/>
       </c>
       <c r="J24" s="38">
-        <f>Inputs!$B$55*(J11-I11)</f>
+        <f>I24*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="54">
-        <f>C21+C22-C23-C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="54">
-        <f>D21+D22-D23-D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="54">
-        <f>E21+E22-E23-E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="54">
-        <f>F21+F22-F23-F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="54">
-        <f>G21+G22-G23-G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="54">
-        <f>H21+H22-H23-H24</f>
-        <v/>
-      </c>
-      <c r="I25" s="54">
-        <f>I21+I22-I23-I24</f>
-        <v/>
-      </c>
-      <c r="J25" s="54">
-        <f>J21+J22-J23-J24</f>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B25" s="36">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="C25" s="38">
+        <f>B25+Inputs!$B$66*(B26-B25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="38">
+        <f>C25+Inputs!$B$66*(C26-C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>D25+Inputs!$B$66*(D26-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="38">
+        <f>E25+Inputs!$B$66*(E26-E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="38">
+        <f>F25+Inputs!$B$66*(F26-F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="38">
+        <f>G25+Inputs!$B$66*(G26-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>H25+Inputs!$B$66*(H26-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="38">
+        <f>I25*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FCF margin</t>
-        </is>
-      </c>
-      <c r="C26" s="39">
-        <f>IF(C11=0,0,C25/C11)</f>
-        <v/>
-      </c>
-      <c r="D26" s="39">
-        <f>IF(D11=0,0,D25/D11)</f>
-        <v/>
-      </c>
-      <c r="E26" s="39">
-        <f>IF(E11=0,0,E25/E11)</f>
-        <v/>
-      </c>
-      <c r="F26" s="39">
-        <f>IF(F11=0,0,F25/F11)</f>
-        <v/>
-      </c>
-      <c r="G26" s="39">
-        <f>IF(G11=0,0,G25/G11)</f>
-        <v/>
-      </c>
-      <c r="H26" s="39">
-        <f>IF(H11=0,0,H25/H11)</f>
-        <v/>
-      </c>
-      <c r="I26" s="39">
-        <f>IF(I11=0,0,I25/I11)</f>
-        <v/>
-      </c>
-      <c r="J26" s="39">
-        <f>IF(J11=0,0,J25/J11)</f>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Inputs!C122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Inputs!D122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>Inputs!E122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>Inputs!F122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>Inputs!G122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="H26" s="36">
+        <f>Inputs!H122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="I26" s="36">
+        <f>Inputs!I122*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="J26" s="38">
+        <f>J25*Inputs!$B$64</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Change in net working capital</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>Inputs!$B$65*(C14-B14)</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>Inputs!$B$65*(D14-C14)</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>Inputs!$B$65*(E14-D14)</f>
+        <v/>
+      </c>
+      <c r="F27" s="38">
+        <f>Inputs!$B$65*(F14-E14)</f>
+        <v/>
+      </c>
+      <c r="G27" s="38">
+        <f>Inputs!$B$65*(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="H27" s="38">
+        <f>Inputs!$B$65*(H14-G14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="38">
+        <f>Inputs!$B$65*(I14-H14)</f>
+        <v/>
+      </c>
+      <c r="J27" s="38">
+        <f>Inputs!$B$65*(J14-I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="54">
+        <f>C24+C25-C26-C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="54">
+        <f>D24+D25-D26-D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="54">
+        <f>E24+E25-E26-E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="54">
+        <f>F24+F25-F26-F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="54">
+        <f>G24+G25-G26-G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="54">
+        <f>H24+H25-H26-H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="54">
+        <f>I24+I25-I26-I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="54">
+        <f>J24+J25-J26-J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF margin</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>IF(C14=0,0,C28/C14)</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>IF(D14=0,0,D28/D14)</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>IF(E14=0,0,E28/E14)</f>
+        <v/>
+      </c>
+      <c r="F29" s="39">
+        <f>IF(F14=0,0,F28/F14)</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>IF(G14=0,0,G28/G14)</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>IF(H14=0,0,H28/H14)</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>IF(I14=0,0,I28/I14)</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>IF(J14=0,0,J28/J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C27" s="31">
-        <f>1/(1+Inputs!$B$52)^C4</f>
-        <v/>
-      </c>
-      <c r="D27" s="31">
-        <f>1/(1+Inputs!$B$52)^D4</f>
-        <v/>
-      </c>
-      <c r="E27" s="31">
-        <f>1/(1+Inputs!$B$52)^E4</f>
-        <v/>
-      </c>
-      <c r="F27" s="31">
-        <f>1/(1+Inputs!$B$52)^F4</f>
-        <v/>
-      </c>
-      <c r="G27" s="31">
-        <f>1/(1+Inputs!$B$52)^G4</f>
-        <v/>
-      </c>
-      <c r="H27" s="31">
-        <f>1/(1+Inputs!$B$52)^H4</f>
-        <v/>
-      </c>
-      <c r="I27" s="31">
-        <f>1/(1+Inputs!$B$52)^I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>PV of FCF</t>
-        </is>
-      </c>
-      <c r="C28" s="38">
-        <f>C25*C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="38">
-        <f>D25*D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="38">
-        <f>E25*E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="38">
-        <f>F25*F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="38">
-        <f>G25*G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="38">
-        <f>H25*H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="38">
-        <f>I25*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>VALUATION</t>
-        </is>
+      <c r="C30" s="31">
+        <f>1/(1+Inputs!$B$62)^C4</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>1/(1+Inputs!$B$62)^D4</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>1/(1+Inputs!$B$62)^E4</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>1/(1+Inputs!$B$62)^F4</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>1/(1+Inputs!$B$62)^G4</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>1/(1+Inputs!$B$62)^H4</f>
+        <v/>
+      </c>
+      <c r="I30" s="31">
+        <f>1/(1+Inputs!$B$62)^I4</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C31" s="38">
+        <f>C28*C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="38">
+        <f>D28*D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E28*E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="38">
+        <f>F28*F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="38">
+        <f>G28*G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="38">
+        <f>H28*H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="38">
+        <f>I28*I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION (value per share floored at $0: equity has limited liability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>Sum of PV of explicit FCF (2027-2033)</t>
         </is>
       </c>
-      <c r="B31" s="38">
-        <f>SUM(C28:I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value at end-2033</t>
-        </is>
-      </c>
-      <c r="B32" s="38">
-        <f>IF(Inputs!$B$52&lt;=Inputs!$B$53,0,J25/(Inputs!$B$52-Inputs!$B$53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B33" s="38">
-        <f>B32*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
       <c r="B34" s="38">
-        <f>B31+B33</f>
+        <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>+ Net cash (incl. Aug-26 raise)</t>
-        </is>
-      </c>
-      <c r="B35" s="36">
-        <f>Inputs!$B$16</f>
+          <t>Terminal value at end-2033</t>
+        </is>
+      </c>
+      <c r="B35" s="38">
+        <f>IF(Inputs!$B$62&lt;=Inputs!$B$63,0,J28/(Inputs!$B$62-Inputs!$B$63))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>+ Altera stake</t>
-        </is>
-      </c>
-      <c r="B36" s="36">
-        <f>Inputs!$B$14</f>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B36" s="38">
+        <f>B35*I30</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>- Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="B37" s="36">
-        <f>-Inputs!$B$15</f>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>B34+B36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="B38" s="38">
-        <f>B34+B35+B36+B37</f>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>+ Net cash (incl. Aug-26 raise)</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>Inputs!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares (bn)</t>
-        </is>
-      </c>
-      <c r="B39" s="37">
-        <f>Inputs!$B$9</f>
+          <t>+ Altera stake</t>
+        </is>
+      </c>
+      <c r="B39" s="36">
+        <f>Inputs!$B$14</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Value per share ($)</t>
-        </is>
-      </c>
-      <c r="B40" s="34">
-        <f>IF(B39=0,0,B38/B39)</f>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>- Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>-Inputs!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B41" s="33">
-        <f>Inputs!$B$4</f>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B41" s="38">
+        <f>B37+B38+B39+B40</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B42" s="39">
-        <f>IF(B41=0,0,B40/B41-1)</f>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value as % of EV</t>
-        </is>
-      </c>
-      <c r="B43" s="39">
-        <f>IF(B34=0,0,B33/B34)</f>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Value per share ($)</t>
+        </is>
+      </c>
+      <c r="B43" s="34">
+        <f>IF(B42=0,0,MAX(0,B41/B42))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B44" s="11">
-        <f>IF(C21&lt;=0,0,B40/(C21/B39))</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>Upside / (downside) vs price</t>
+        </is>
+      </c>
+      <c r="B45" s="39">
+        <f>IF(B44=0,0,B43/B44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>IF(B37=0,0,B36/B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>IF(C24&lt;=0,0,B43/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B45" s="11">
-        <f>IF(C21&lt;=0,0,B41/(C21/B39))</f>
+      <c r="B48" s="11">
+        <f>IF(C24&lt;=0,0,B44/(C24/B42))</f>
         <v/>
       </c>
     </row>
@@ -5113,7 +5584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5135,6 +5606,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5194,31 +5666,31 @@
         </is>
       </c>
       <c r="C4" s="27">
-        <f>Inputs!$B$57+1</f>
+        <f>Inputs!$B$67+1</f>
         <v/>
       </c>
       <c r="D4" s="27">
-        <f>Inputs!$B$57+2</f>
+        <f>Inputs!$B$67+2</f>
         <v/>
       </c>
       <c r="E4" s="27">
-        <f>Inputs!$B$57+3</f>
+        <f>Inputs!$B$67+3</f>
         <v/>
       </c>
       <c r="F4" s="27">
-        <f>Inputs!$B$57+4</f>
+        <f>Inputs!$B$67+4</f>
         <v/>
       </c>
       <c r="G4" s="27">
-        <f>Inputs!$B$57+5</f>
+        <f>Inputs!$B$67+5</f>
         <v/>
       </c>
       <c r="H4" s="27">
-        <f>Inputs!$B$57+6</f>
+        <f>Inputs!$B$67+6</f>
         <v/>
       </c>
       <c r="I4" s="27">
-        <f>Inputs!$B$57+7</f>
+        <f>Inputs!$B$67+7</f>
         <v/>
       </c>
     </row>
@@ -5268,31 +5740,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C76+Inputs!$B$62</f>
+        <f>Inputs!C87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D76+Inputs!$B$62</f>
+        <f>Inputs!D87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E76+Inputs!$B$62</f>
+        <f>Inputs!E87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F76+Inputs!$B$62</f>
+        <f>Inputs!F87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G76+Inputs!$B$62</f>
+        <f>Inputs!G87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H76+Inputs!$B$62</f>
+        <f>Inputs!H87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I76+Inputs!$B$62</f>
+        <f>Inputs!I87+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -5342,31 +5814,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C82</f>
+        <f>Inputs!C93</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D82</f>
+        <f>Inputs!D93</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E82</f>
+        <f>Inputs!E93</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F82</f>
+        <f>Inputs!F93</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G82</f>
+        <f>Inputs!G93</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H82</f>
+        <f>Inputs!H93</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I82</f>
+        <f>Inputs!I93</f>
         <v/>
       </c>
     </row>
@@ -5381,31 +5853,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C88*Inputs!$B$63</f>
+        <f>Inputs!C99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D88*Inputs!$B$63</f>
+        <f>Inputs!D99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E88*Inputs!$B$63</f>
+        <f>Inputs!E99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F88*Inputs!$B$63</f>
+        <f>Inputs!F99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G88*Inputs!$B$63</f>
+        <f>Inputs!G99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H88*Inputs!$B$63</f>
+        <f>Inputs!H99*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I88*Inputs!$B$63</f>
+        <f>Inputs!I99*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -5420,902 +5892,1050 @@
         <v/>
       </c>
       <c r="C10" s="38">
-        <f>B10*(1+Inputs!$B$58)</f>
+        <f>B10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="D10" s="38">
-        <f>C10*(1+Inputs!$B$58)</f>
+        <f>C10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="E10" s="38">
-        <f>D10*(1+Inputs!$B$58)</f>
+        <f>D10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="F10" s="38">
-        <f>E10*(1+Inputs!$B$58)</f>
+        <f>E10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="G10" s="38">
-        <f>F10*(1+Inputs!$B$58)</f>
+        <f>F10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="H10" s="38">
-        <f>G10*(1+Inputs!$B$58)</f>
+        <f>G10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="I10" s="38">
-        <f>H10*(1+Inputs!$B$58)</f>
+        <f>H10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="54">
-        <f>SUM(B5,B7,B9,B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="54">
-        <f>SUM(C5,C7,C9,C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="54">
-        <f>SUM(D5,D7,D9,D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="54">
-        <f>SUM(E5,E7,E9,E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="54">
-        <f>SUM(F5,F7,F9,F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="54">
-        <f>SUM(G5,G7,G9,G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="54">
-        <f>SUM(H5,H7,H9,H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="54">
-        <f>SUM(I5,I7,I9,I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="54">
-        <f>I11*(1+Inputs!$B$53)</f>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>China domestic-demand revenue exposed (pre-erosion)</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>(B5+B7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="C11" s="38">
+        <f>(C5+C7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>(D5+D7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>(E5+E7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="F11" s="38">
+        <f>(F5+F7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G11" s="38">
+        <f>(G5+G7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="H11" s="38">
+        <f>(H5+H7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="I11" s="38">
+        <f>(I5+I7)*Inputs!$B$49*Inputs!$B$50</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  growth</t>
-        </is>
-      </c>
-      <c r="C12" s="39">
-        <f>IF(B11=0,0,C11/B11-1)</f>
-        <v/>
-      </c>
-      <c r="D12" s="39">
-        <f>IF(C11=0,0,D11/C11-1)</f>
-        <v/>
-      </c>
-      <c r="E12" s="39">
-        <f>IF(D11=0,0,E11/D11-1)</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
-        <f>IF(E11=0,0,F11/E11-1)</f>
-        <v/>
-      </c>
-      <c r="G12" s="39">
-        <f>IF(F11=0,0,G11/F11-1)</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>IF(G11=0,0,H11/G11-1)</f>
-        <v/>
-      </c>
-      <c r="I12" s="39">
-        <f>IF(H11=0,0,I11/H11-1)</f>
+          <t xml:space="preserve">  China erosion index (2026 = 1.00)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="27">
+        <f>MAX(0,B12*(1+Inputs!C117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>MAX(0,C12*(1+Inputs!D117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>MAX(0,D12*(1+Inputs!E117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>MAX(0,E12*(1+Inputs!F117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>MAX(0,F12*(1+Inputs!G117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>MAX(0,G12*(1+Inputs!H117+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>MAX(0,H12*(1+Inputs!I117+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B13" s="32">
-        <f>Inputs!$B$32+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>Inputs!C94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="D13" s="32">
-        <f>Inputs!D94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="E13" s="32">
-        <f>Inputs!E94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="F13" s="32">
-        <f>Inputs!F94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="G13" s="32">
-        <f>Inputs!G94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="H13" s="32">
-        <f>Inputs!H94+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="I13" s="32">
-        <f>Inputs!I94+Inputs!$B$61</f>
+          <t>Less: China localization / trade revenue loss</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>-B11*(1-B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>-C11*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>-D11*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>-E11*(1-E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>-F11*(1-F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>-G11*(1-G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>-H11*(1-H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38">
+        <f>-I11*(1-I12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B14" s="38">
-        <f>B11*B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="38">
-        <f>C11*C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="38">
-        <f>D11*D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="38">
-        <f>E11*E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="38">
-        <f>F11*F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="38">
-        <f>G11*G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="38">
-        <f>H11*H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="38">
-        <f>I11*I13</f>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="54">
+        <f>SUM(B5,B7,B9,B10,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="54">
+        <f>SUM(C5,C7,C9,C10,C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="54">
+        <f>SUM(D5,D7,D9,D10,D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>SUM(E5,E7,E9,E10,E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="54">
+        <f>SUM(F5,F7,F9,F10,F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="54">
+        <f>SUM(G5,G7,G9,G10,G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="54">
+        <f>SUM(H5,H7,H9,H10,H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="54">
+        <f>SUM(I5,I7,I9,I10,I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="54">
+        <f>I14*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP opex</t>
-        </is>
-      </c>
-      <c r="B15" s="36">
-        <f>Inputs!$B$33</f>
-        <v/>
-      </c>
-      <c r="C15" s="38">
-        <f>B15*(1+Inputs!C100)</f>
-        <v/>
-      </c>
-      <c r="D15" s="38">
-        <f>C15*(1+Inputs!D100)</f>
-        <v/>
-      </c>
-      <c r="E15" s="38">
-        <f>D15*(1+Inputs!E100)</f>
-        <v/>
-      </c>
-      <c r="F15" s="38">
-        <f>E15*(1+Inputs!F100)</f>
-        <v/>
-      </c>
-      <c r="G15" s="38">
-        <f>F15*(1+Inputs!G100)</f>
-        <v/>
-      </c>
-      <c r="H15" s="38">
-        <f>G15*(1+Inputs!H100)</f>
-        <v/>
-      </c>
-      <c r="I15" s="38">
-        <f>H15*(1+Inputs!I100)</f>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>IF(B14=0,0,C14/B14-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="39">
+        <f>IF(C14=0,0,D14/C14-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
+        <f>IF(D14=0,0,E14/D14-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="39">
+        <f>IF(E14=0,0,F14/E14-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>IF(F14=0,0,G14/F14-1)</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>IF(G14=0,0,H14/G14-1)</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>IF(H14=0,0,I14/H14-1)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Non-GAAP operating income</t>
-        </is>
-      </c>
-      <c r="B16" s="54">
-        <f>B14-B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="54">
-        <f>C14-C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="54">
-        <f>D14-D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="54">
-        <f>E14-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="54">
-        <f>F14-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="54">
-        <f>G14-G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="54">
-        <f>H14-H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="54">
-        <f>I14-I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="30" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>Inputs!$B$32+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>Inputs!C105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>Inputs!D105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>Inputs!E105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>Inputs!F105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>Inputs!G105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>Inputs!H105+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>Inputs!I105+Inputs!$B$71</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  operating margin</t>
-        </is>
-      </c>
-      <c r="B17" s="39">
-        <f>IF(B11=0,0,B16/B11)</f>
-        <v/>
-      </c>
-      <c r="C17" s="39">
-        <f>IF(C11=0,0,C16/C11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>IF(D11=0,0,D16/D11)</f>
-        <v/>
-      </c>
-      <c r="E17" s="39">
-        <f>IF(E11=0,0,E16/E11)</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
-        <f>IF(F11=0,0,F16/F11)</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>IF(G11=0,0,G16/G11)</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>IF(H11=0,0,H16/H11)</f>
-        <v/>
-      </c>
-      <c r="I17" s="39">
-        <f>IF(I11=0,0,I16/I11)</f>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="38">
+        <f>C14*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>D14*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E14*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="38">
+        <f>F14*F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="38">
+        <f>G14*G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>H14*H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>I14*I16</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Non-GAAP opex</t>
         </is>
       </c>
       <c r="B18" s="36">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$33</f>
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C100)</f>
+        <f>B18*(1+Inputs!C111)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D100)</f>
+        <f>C18*(1+Inputs!D111)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E100)</f>
+        <f>D18*(1+Inputs!E111)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F100)</f>
+        <f>E18*(1+Inputs!F111)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G100)</f>
+        <f>F18*(1+Inputs!G111)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H100)</f>
+        <f>G18*(1+Inputs!H111)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I100)</f>
+        <f>H18*(1+Inputs!I111)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>EBIT after SBC</t>
-        </is>
-      </c>
-      <c r="C19" s="38">
-        <f>C16-C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="38">
-        <f>D16-D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="38">
-        <f>E16-E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="38">
-        <f>F16-F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="38">
-        <f>G16-G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="38">
-        <f>H16-H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="38">
-        <f>I16-I18</f>
-        <v/>
-      </c>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B19" s="54">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="54">
+        <f>C17-C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="54">
+        <f>D17-D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>E17-E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="54">
+        <f>F17-F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="54">
+        <f>G17-G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="54">
+        <f>H17-H18</f>
+        <v/>
+      </c>
+      <c r="I19" s="54">
+        <f>I17-I18</f>
+        <v/>
+      </c>
+      <c r="J19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Taxes on EBIT</t>
-        </is>
-      </c>
-      <c r="C20" s="38">
-        <f>MAX(0,C19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="D20" s="38">
-        <f>MAX(0,D19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="E20" s="38">
-        <f>MAX(0,E19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="F20" s="38">
-        <f>MAX(0,F19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="G20" s="38">
-        <f>MAX(0,G19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="H20" s="38">
-        <f>MAX(0,H19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="I20" s="38">
-        <f>MAX(0,I19)*Inputs!$B$50</f>
+          <t xml:space="preserve">  operating margin</t>
+        </is>
+      </c>
+      <c r="B20" s="39">
+        <f>IF(B14=0,0,B19/B14)</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>IF(C14=0,0,C19/C14)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>IF(D14=0,0,D19/D14)</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
+        <f>IF(E14=0,0,E19/E14)</f>
+        <v/>
+      </c>
+      <c r="F20" s="39">
+        <f>IF(F14=0,0,F19/F14)</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>IF(G14=0,0,G19/G14)</f>
+        <v/>
+      </c>
+      <c r="H20" s="39">
+        <f>IF(H14=0,0,H19/H14)</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>IF(I14=0,0,I19/I14)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NOPAT</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
+        <f>Inputs!$B$34</f>
+        <v/>
       </c>
       <c r="C21" s="38">
-        <f>C19-C20</f>
+        <f>B21*(1+Inputs!C111)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>D19-D20</f>
+        <f>C21*(1+Inputs!D111)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>E19-E20</f>
+        <f>D21*(1+Inputs!E111)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>F19-F20</f>
+        <f>E21*(1+Inputs!F111)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>G19-G20</f>
+        <f>F21*(1+Inputs!G111)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>H19-H20</f>
+        <f>G21*(1+Inputs!H111)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>I19-I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="38">
-        <f>I21*(1+Inputs!$B$53)</f>
+        <f>H21*(1+Inputs!I111)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B22" s="36">
-        <f>Inputs!$B$35</f>
-        <v/>
+          <t>EBIT after SBC</t>
+        </is>
       </c>
       <c r="C22" s="38">
-        <f>B22+Inputs!$B$56*(B23-B22)</f>
+        <f>C19-C21</f>
         <v/>
       </c>
       <c r="D22" s="38">
-        <f>C22+Inputs!$B$56*(C23-C22)</f>
+        <f>D19-D21</f>
         <v/>
       </c>
       <c r="E22" s="38">
-        <f>D22+Inputs!$B$56*(D23-D22)</f>
+        <f>E19-E21</f>
         <v/>
       </c>
       <c r="F22" s="38">
-        <f>E22+Inputs!$B$56*(E23-E22)</f>
+        <f>F19-F21</f>
         <v/>
       </c>
       <c r="G22" s="38">
-        <f>F22+Inputs!$B$56*(F23-F22)</f>
+        <f>G19-G21</f>
         <v/>
       </c>
       <c r="H22" s="38">
-        <f>G22+Inputs!$B$56*(G23-G22)</f>
+        <f>H19-H21</f>
         <v/>
       </c>
       <c r="I22" s="38">
-        <f>H22+Inputs!$B$56*(H23-H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="38">
-        <f>I22*(1+Inputs!$B$53)</f>
+        <f>I19-I21</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="B23" s="36">
-        <f>Inputs!$B$36</f>
-        <v/>
-      </c>
-      <c r="C23" s="36">
-        <f>Inputs!C106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
-        <f>Inputs!D106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="E23" s="36">
-        <f>Inputs!E106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="F23" s="36">
-        <f>Inputs!F106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="G23" s="36">
-        <f>Inputs!G106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="H23" s="36">
-        <f>Inputs!H106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="I23" s="36">
-        <f>Inputs!I106*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="J23" s="38">
-        <f>J22*Inputs!$B$54</f>
+          <t>Taxes on EBIT</t>
+        </is>
+      </c>
+      <c r="C23" s="38">
+        <f>MAX(0,C22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
+        <f>MAX(0,D22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>MAX(0,E22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="F23" s="38">
+        <f>MAX(0,F22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G23" s="38">
+        <f>MAX(0,G22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="H23" s="38">
+        <f>MAX(0,H22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="I23" s="38">
+        <f>MAX(0,I22)*Inputs!$B$60</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Change in net working capital</t>
+          <t>NOPAT</t>
         </is>
       </c>
       <c r="C24" s="38">
-        <f>Inputs!$B$55*(C11-B11)</f>
+        <f>C22-C23</f>
         <v/>
       </c>
       <c r="D24" s="38">
-        <f>Inputs!$B$55*(D11-C11)</f>
+        <f>D22-D23</f>
         <v/>
       </c>
       <c r="E24" s="38">
-        <f>Inputs!$B$55*(E11-D11)</f>
+        <f>E22-E23</f>
         <v/>
       </c>
       <c r="F24" s="38">
-        <f>Inputs!$B$55*(F11-E11)</f>
+        <f>F22-F23</f>
         <v/>
       </c>
       <c r="G24" s="38">
-        <f>Inputs!$B$55*(G11-F11)</f>
+        <f>G22-G23</f>
         <v/>
       </c>
       <c r="H24" s="38">
-        <f>Inputs!$B$55*(H11-G11)</f>
+        <f>H22-H23</f>
         <v/>
       </c>
       <c r="I24" s="38">
-        <f>Inputs!$B$55*(I11-H11)</f>
+        <f>I22-I23</f>
         <v/>
       </c>
       <c r="J24" s="38">
-        <f>Inputs!$B$55*(J11-I11)</f>
+        <f>I24*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="54">
-        <f>C21+C22-C23-C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="54">
-        <f>D21+D22-D23-D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="54">
-        <f>E21+E22-E23-E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="54">
-        <f>F21+F22-F23-F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="54">
-        <f>G21+G22-G23-G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="54">
-        <f>H21+H22-H23-H24</f>
-        <v/>
-      </c>
-      <c r="I25" s="54">
-        <f>I21+I22-I23-I24</f>
-        <v/>
-      </c>
-      <c r="J25" s="54">
-        <f>J21+J22-J23-J24</f>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B25" s="36">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="C25" s="38">
+        <f>B25+Inputs!$B$66*(B26-B25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="38">
+        <f>C25+Inputs!$B$66*(C26-C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>D25+Inputs!$B$66*(D26-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="38">
+        <f>E25+Inputs!$B$66*(E26-E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="38">
+        <f>F25+Inputs!$B$66*(F26-F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="38">
+        <f>G25+Inputs!$B$66*(G26-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>H25+Inputs!$B$66*(H26-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="38">
+        <f>I25*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FCF margin</t>
-        </is>
-      </c>
-      <c r="C26" s="39">
-        <f>IF(C11=0,0,C25/C11)</f>
-        <v/>
-      </c>
-      <c r="D26" s="39">
-        <f>IF(D11=0,0,D25/D11)</f>
-        <v/>
-      </c>
-      <c r="E26" s="39">
-        <f>IF(E11=0,0,E25/E11)</f>
-        <v/>
-      </c>
-      <c r="F26" s="39">
-        <f>IF(F11=0,0,F25/F11)</f>
-        <v/>
-      </c>
-      <c r="G26" s="39">
-        <f>IF(G11=0,0,G25/G11)</f>
-        <v/>
-      </c>
-      <c r="H26" s="39">
-        <f>IF(H11=0,0,H25/H11)</f>
-        <v/>
-      </c>
-      <c r="I26" s="39">
-        <f>IF(I11=0,0,I25/I11)</f>
-        <v/>
-      </c>
-      <c r="J26" s="39">
-        <f>IF(J11=0,0,J25/J11)</f>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Inputs!C123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Inputs!D123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>Inputs!E123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>Inputs!F123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>Inputs!G123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="H26" s="36">
+        <f>Inputs!H123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="I26" s="36">
+        <f>Inputs!I123*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="J26" s="38">
+        <f>J25*Inputs!$B$64</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Change in net working capital</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>Inputs!$B$65*(C14-B14)</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>Inputs!$B$65*(D14-C14)</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>Inputs!$B$65*(E14-D14)</f>
+        <v/>
+      </c>
+      <c r="F27" s="38">
+        <f>Inputs!$B$65*(F14-E14)</f>
+        <v/>
+      </c>
+      <c r="G27" s="38">
+        <f>Inputs!$B$65*(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="H27" s="38">
+        <f>Inputs!$B$65*(H14-G14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="38">
+        <f>Inputs!$B$65*(I14-H14)</f>
+        <v/>
+      </c>
+      <c r="J27" s="38">
+        <f>Inputs!$B$65*(J14-I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="54">
+        <f>C24+C25-C26-C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="54">
+        <f>D24+D25-D26-D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="54">
+        <f>E24+E25-E26-E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="54">
+        <f>F24+F25-F26-F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="54">
+        <f>G24+G25-G26-G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="54">
+        <f>H24+H25-H26-H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="54">
+        <f>I24+I25-I26-I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="54">
+        <f>J24+J25-J26-J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF margin</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>IF(C14=0,0,C28/C14)</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>IF(D14=0,0,D28/D14)</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>IF(E14=0,0,E28/E14)</f>
+        <v/>
+      </c>
+      <c r="F29" s="39">
+        <f>IF(F14=0,0,F28/F14)</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>IF(G14=0,0,G28/G14)</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>IF(H14=0,0,H28/H14)</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>IF(I14=0,0,I28/I14)</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>IF(J14=0,0,J28/J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C27" s="31">
-        <f>1/(1+Inputs!$B$52)^C4</f>
-        <v/>
-      </c>
-      <c r="D27" s="31">
-        <f>1/(1+Inputs!$B$52)^D4</f>
-        <v/>
-      </c>
-      <c r="E27" s="31">
-        <f>1/(1+Inputs!$B$52)^E4</f>
-        <v/>
-      </c>
-      <c r="F27" s="31">
-        <f>1/(1+Inputs!$B$52)^F4</f>
-        <v/>
-      </c>
-      <c r="G27" s="31">
-        <f>1/(1+Inputs!$B$52)^G4</f>
-        <v/>
-      </c>
-      <c r="H27" s="31">
-        <f>1/(1+Inputs!$B$52)^H4</f>
-        <v/>
-      </c>
-      <c r="I27" s="31">
-        <f>1/(1+Inputs!$B$52)^I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>PV of FCF</t>
-        </is>
-      </c>
-      <c r="C28" s="38">
-        <f>C25*C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="38">
-        <f>D25*D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="38">
-        <f>E25*E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="38">
-        <f>F25*F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="38">
-        <f>G25*G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="38">
-        <f>H25*H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="38">
-        <f>I25*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>VALUATION</t>
-        </is>
+      <c r="C30" s="31">
+        <f>1/(1+Inputs!$B$62)^C4</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>1/(1+Inputs!$B$62)^D4</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>1/(1+Inputs!$B$62)^E4</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>1/(1+Inputs!$B$62)^F4</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>1/(1+Inputs!$B$62)^G4</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>1/(1+Inputs!$B$62)^H4</f>
+        <v/>
+      </c>
+      <c r="I30" s="31">
+        <f>1/(1+Inputs!$B$62)^I4</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C31" s="38">
+        <f>C28*C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="38">
+        <f>D28*D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E28*E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="38">
+        <f>F28*F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="38">
+        <f>G28*G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="38">
+        <f>H28*H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="38">
+        <f>I28*I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION (value per share floored at $0: equity has limited liability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>Sum of PV of explicit FCF (2027-2033)</t>
         </is>
       </c>
-      <c r="B31" s="38">
-        <f>SUM(C28:I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value at end-2033</t>
-        </is>
-      </c>
-      <c r="B32" s="38">
-        <f>IF(Inputs!$B$52&lt;=Inputs!$B$53,0,J25/(Inputs!$B$52-Inputs!$B$53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B33" s="38">
-        <f>B32*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
       <c r="B34" s="38">
-        <f>B31+B33</f>
+        <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>+ Net cash (incl. Aug-26 raise)</t>
-        </is>
-      </c>
-      <c r="B35" s="36">
-        <f>Inputs!$B$16</f>
+          <t>Terminal value at end-2033</t>
+        </is>
+      </c>
+      <c r="B35" s="38">
+        <f>IF(Inputs!$B$62&lt;=Inputs!$B$63,0,J28/(Inputs!$B$62-Inputs!$B$63))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>+ Altera stake</t>
-        </is>
-      </c>
-      <c r="B36" s="36">
-        <f>Inputs!$B$14</f>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B36" s="38">
+        <f>B35*I30</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>- Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="B37" s="36">
-        <f>-Inputs!$B$15</f>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>B34+B36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="B38" s="38">
-        <f>B34+B35+B36+B37</f>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>+ Net cash (incl. Aug-26 raise)</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>Inputs!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares (bn)</t>
-        </is>
-      </c>
-      <c r="B39" s="37">
-        <f>Inputs!$B$9</f>
+          <t>+ Altera stake</t>
+        </is>
+      </c>
+      <c r="B39" s="36">
+        <f>Inputs!$B$14</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Value per share ($)</t>
-        </is>
-      </c>
-      <c r="B40" s="34">
-        <f>IF(B39=0,0,B38/B39)</f>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>- Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>-Inputs!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B41" s="33">
-        <f>Inputs!$B$4</f>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B41" s="38">
+        <f>B37+B38+B39+B40</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B42" s="39">
-        <f>IF(B41=0,0,B40/B41-1)</f>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value as % of EV</t>
-        </is>
-      </c>
-      <c r="B43" s="39">
-        <f>IF(B34=0,0,B33/B34)</f>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Value per share ($)</t>
+        </is>
+      </c>
+      <c r="B43" s="34">
+        <f>IF(B42=0,0,MAX(0,B41/B42))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B44" s="11">
-        <f>IF(C21&lt;=0,0,B40/(C21/B39))</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>Upside / (downside) vs price</t>
+        </is>
+      </c>
+      <c r="B45" s="39">
+        <f>IF(B44=0,0,B43/B44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>IF(B37=0,0,B36/B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>IF(C24&lt;=0,0,B43/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B45" s="11">
-        <f>IF(C21&lt;=0,0,B41/(C21/B39))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B48" s="11">
+        <f>IF(C24&lt;=0,0,B44/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6327,7 +6947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6408,31 +7028,31 @@
         </is>
       </c>
       <c r="C4" s="27">
-        <f>Inputs!$B$57+1</f>
+        <f>Inputs!$B$67+1</f>
         <v/>
       </c>
       <c r="D4" s="27">
-        <f>Inputs!$B$57+2</f>
+        <f>Inputs!$B$67+2</f>
         <v/>
       </c>
       <c r="E4" s="27">
-        <f>Inputs!$B$57+3</f>
+        <f>Inputs!$B$67+3</f>
         <v/>
       </c>
       <c r="F4" s="27">
-        <f>Inputs!$B$57+4</f>
+        <f>Inputs!$B$67+4</f>
         <v/>
       </c>
       <c r="G4" s="27">
-        <f>Inputs!$B$57+5</f>
+        <f>Inputs!$B$67+5</f>
         <v/>
       </c>
       <c r="H4" s="27">
-        <f>Inputs!$B$57+6</f>
+        <f>Inputs!$B$67+6</f>
         <v/>
       </c>
       <c r="I4" s="27">
-        <f>Inputs!$B$57+7</f>
+        <f>Inputs!$B$67+7</f>
         <v/>
       </c>
     </row>
@@ -6482,31 +7102,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C77+Inputs!$B$62</f>
+        <f>Inputs!C88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D77+Inputs!$B$62</f>
+        <f>Inputs!D88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E77+Inputs!$B$62</f>
+        <f>Inputs!E88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F77+Inputs!$B$62</f>
+        <f>Inputs!F88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G77+Inputs!$B$62</f>
+        <f>Inputs!G88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H77+Inputs!$B$62</f>
+        <f>Inputs!H88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I77+Inputs!$B$62</f>
+        <f>Inputs!I88+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -6556,31 +7176,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C83</f>
+        <f>Inputs!C94</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D83</f>
+        <f>Inputs!D94</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E83</f>
+        <f>Inputs!E94</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F83</f>
+        <f>Inputs!F94</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G83</f>
+        <f>Inputs!G94</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H83</f>
+        <f>Inputs!H94</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I83</f>
+        <f>Inputs!I94</f>
         <v/>
       </c>
     </row>
@@ -6595,31 +7215,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C89*Inputs!$B$63</f>
+        <f>Inputs!C100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D89*Inputs!$B$63</f>
+        <f>Inputs!D100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E89*Inputs!$B$63</f>
+        <f>Inputs!E100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F89*Inputs!$B$63</f>
+        <f>Inputs!F100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G89*Inputs!$B$63</f>
+        <f>Inputs!G100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H89*Inputs!$B$63</f>
+        <f>Inputs!H100*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I89*Inputs!$B$63</f>
+        <f>Inputs!I100*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -6634,899 +7254,1015 @@
         <v/>
       </c>
       <c r="C10" s="38">
-        <f>B10*(1+Inputs!$B$58)</f>
+        <f>B10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="D10" s="38">
-        <f>C10*(1+Inputs!$B$58)</f>
+        <f>C10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="E10" s="38">
-        <f>D10*(1+Inputs!$B$58)</f>
+        <f>D10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="F10" s="38">
-        <f>E10*(1+Inputs!$B$58)</f>
+        <f>E10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="G10" s="38">
-        <f>F10*(1+Inputs!$B$58)</f>
+        <f>F10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="H10" s="38">
-        <f>G10*(1+Inputs!$B$58)</f>
+        <f>G10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="I10" s="38">
-        <f>H10*(1+Inputs!$B$58)</f>
+        <f>H10*(1+Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Total revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="54">
-        <f>SUM(B5,B7,B9,B10)</f>
-        <v/>
-      </c>
-      <c r="C11" s="54">
-        <f>SUM(C5,C7,C9,C10)</f>
-        <v/>
-      </c>
-      <c r="D11" s="54">
-        <f>SUM(D5,D7,D9,D10)</f>
-        <v/>
-      </c>
-      <c r="E11" s="54">
-        <f>SUM(E5,E7,E9,E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="54">
-        <f>SUM(F5,F7,F9,F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="54">
-        <f>SUM(G5,G7,G9,G10)</f>
-        <v/>
-      </c>
-      <c r="H11" s="54">
-        <f>SUM(H5,H7,H9,H10)</f>
-        <v/>
-      </c>
-      <c r="I11" s="54">
-        <f>SUM(I5,I7,I9,I10)</f>
-        <v/>
-      </c>
-      <c r="J11" s="54">
-        <f>I11*(1+Inputs!$B$53)</f>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>China domestic-demand revenue exposed (pre-erosion)</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>(B5+B7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="C11" s="38">
+        <f>(C5+C7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>(D5+D7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>(E5+E7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="F11" s="38">
+        <f>(F5+F7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G11" s="38">
+        <f>(G5+G7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="H11" s="38">
+        <f>(H5+H7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="I11" s="38">
+        <f>(I5+I7)*Inputs!$B$49*Inputs!$B$50</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  growth</t>
-        </is>
-      </c>
-      <c r="C12" s="39">
-        <f>IF(B11=0,0,C11/B11-1)</f>
-        <v/>
-      </c>
-      <c r="D12" s="39">
-        <f>IF(C11=0,0,D11/C11-1)</f>
-        <v/>
-      </c>
-      <c r="E12" s="39">
-        <f>IF(D11=0,0,E11/D11-1)</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
-        <f>IF(E11=0,0,F11/E11-1)</f>
-        <v/>
-      </c>
-      <c r="G12" s="39">
-        <f>IF(F11=0,0,G11/F11-1)</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>IF(G11=0,0,H11/G11-1)</f>
-        <v/>
-      </c>
-      <c r="I12" s="39">
-        <f>IF(H11=0,0,I11/H11-1)</f>
+          <t xml:space="preserve">  China erosion index (2026 = 1.00)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="27">
+        <f>MAX(0,B12*(1+Inputs!C118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>MAX(0,C12*(1+Inputs!D118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>MAX(0,D12*(1+Inputs!E118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>MAX(0,E12*(1+Inputs!F118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>MAX(0,F12*(1+Inputs!G118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>MAX(0,G12*(1+Inputs!H118+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>MAX(0,H12*(1+Inputs!I118+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B13" s="32">
-        <f>Inputs!$B$32+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="C13" s="32">
-        <f>Inputs!C95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="D13" s="32">
-        <f>Inputs!D95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="E13" s="32">
-        <f>Inputs!E95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="F13" s="32">
-        <f>Inputs!F95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="G13" s="32">
-        <f>Inputs!G95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="H13" s="32">
-        <f>Inputs!H95+Inputs!$B$61</f>
-        <v/>
-      </c>
-      <c r="I13" s="32">
-        <f>Inputs!I95+Inputs!$B$61</f>
+          <t>Less: China localization / trade revenue loss</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>-B11*(1-B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>-C11*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>-D11*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>-E11*(1-E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>-F11*(1-F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>-G11*(1-G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>-H11*(1-H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38">
+        <f>-I11*(1-I12)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="B14" s="38">
-        <f>B11*B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="38">
-        <f>C11*C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="38">
-        <f>D11*D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="38">
-        <f>E11*E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="38">
-        <f>F11*F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="38">
-        <f>G11*G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="38">
-        <f>H11*H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="38">
-        <f>I11*I13</f>
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="54">
+        <f>SUM(B5,B7,B9,B10,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="54">
+        <f>SUM(C5,C7,C9,C10,C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="54">
+        <f>SUM(D5,D7,D9,D10,D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>SUM(E5,E7,E9,E10,E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="54">
+        <f>SUM(F5,F7,F9,F10,F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="54">
+        <f>SUM(G5,G7,G9,G10,G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="54">
+        <f>SUM(H5,H7,H9,H10,H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="54">
+        <f>SUM(I5,I7,I9,I10,I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="54">
+        <f>I14*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Non-GAAP opex</t>
-        </is>
-      </c>
-      <c r="B15" s="36">
-        <f>Inputs!$B$33</f>
-        <v/>
-      </c>
-      <c r="C15" s="38">
-        <f>B15*(1+Inputs!C101)</f>
-        <v/>
-      </c>
-      <c r="D15" s="38">
-        <f>C15*(1+Inputs!D101)</f>
-        <v/>
-      </c>
-      <c r="E15" s="38">
-        <f>D15*(1+Inputs!E101)</f>
-        <v/>
-      </c>
-      <c r="F15" s="38">
-        <f>E15*(1+Inputs!F101)</f>
-        <v/>
-      </c>
-      <c r="G15" s="38">
-        <f>F15*(1+Inputs!G101)</f>
-        <v/>
-      </c>
-      <c r="H15" s="38">
-        <f>G15*(1+Inputs!H101)</f>
-        <v/>
-      </c>
-      <c r="I15" s="38">
-        <f>H15*(1+Inputs!I101)</f>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>IF(B14=0,0,C14/B14-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="39">
+        <f>IF(C14=0,0,D14/C14-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
+        <f>IF(D14=0,0,E14/D14-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="39">
+        <f>IF(E14=0,0,F14/E14-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>IF(F14=0,0,G14/F14-1)</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>IF(G14=0,0,H14/G14-1)</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>IF(H14=0,0,I14/H14-1)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>Non-GAAP operating income</t>
-        </is>
-      </c>
-      <c r="B16" s="54">
-        <f>B14-B15</f>
-        <v/>
-      </c>
-      <c r="C16" s="54">
-        <f>C14-C15</f>
-        <v/>
-      </c>
-      <c r="D16" s="54">
-        <f>D14-D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="54">
-        <f>E14-E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="54">
-        <f>F14-F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="54">
-        <f>G14-G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="54">
-        <f>H14-H15</f>
-        <v/>
-      </c>
-      <c r="I16" s="54">
-        <f>I14-I15</f>
-        <v/>
-      </c>
-      <c r="J16" s="30" t="n"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>Inputs!$B$32+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>Inputs!C106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>Inputs!D106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>Inputs!E106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>Inputs!F106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>Inputs!G106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>Inputs!H106+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>Inputs!I106+Inputs!$B$71</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  operating margin</t>
-        </is>
-      </c>
-      <c r="B17" s="39">
-        <f>IF(B11=0,0,B16/B11)</f>
-        <v/>
-      </c>
-      <c r="C17" s="39">
-        <f>IF(C11=0,0,C16/C11)</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
-        <f>IF(D11=0,0,D16/D11)</f>
-        <v/>
-      </c>
-      <c r="E17" s="39">
-        <f>IF(E11=0,0,E16/E11)</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
-        <f>IF(F11=0,0,F16/F11)</f>
-        <v/>
-      </c>
-      <c r="G17" s="39">
-        <f>IF(G11=0,0,G16/G11)</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>IF(H11=0,0,H16/H11)</f>
-        <v/>
-      </c>
-      <c r="I17" s="39">
-        <f>IF(I11=0,0,I16/I11)</f>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="38">
+        <f>C14*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>D14*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E14*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="38">
+        <f>F14*F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="38">
+        <f>G14*G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>H14*H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>I14*I16</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
+          <t>Non-GAAP opex</t>
         </is>
       </c>
       <c r="B18" s="36">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$33</f>
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C101)</f>
+        <f>B18*(1+Inputs!C112)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D101)</f>
+        <f>C18*(1+Inputs!D112)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E101)</f>
+        <f>D18*(1+Inputs!E112)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F101)</f>
+        <f>E18*(1+Inputs!F112)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G101)</f>
+        <f>F18*(1+Inputs!G112)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H101)</f>
+        <f>G18*(1+Inputs!H112)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I101)</f>
+        <f>H18*(1+Inputs!I112)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>EBIT after SBC</t>
-        </is>
-      </c>
-      <c r="C19" s="38">
-        <f>C16-C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="38">
-        <f>D16-D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="38">
-        <f>E16-E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="38">
-        <f>F16-F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="38">
-        <f>G16-G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="38">
-        <f>H16-H18</f>
-        <v/>
-      </c>
-      <c r="I19" s="38">
-        <f>I16-I18</f>
-        <v/>
-      </c>
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B19" s="54">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="54">
+        <f>C17-C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="54">
+        <f>D17-D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>E17-E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="54">
+        <f>F17-F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="54">
+        <f>G17-G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="54">
+        <f>H17-H18</f>
+        <v/>
+      </c>
+      <c r="I19" s="54">
+        <f>I17-I18</f>
+        <v/>
+      </c>
+      <c r="J19" s="30" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Taxes on EBIT</t>
-        </is>
-      </c>
-      <c r="C20" s="38">
-        <f>MAX(0,C19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="D20" s="38">
-        <f>MAX(0,D19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="E20" s="38">
-        <f>MAX(0,E19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="F20" s="38">
-        <f>MAX(0,F19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="G20" s="38">
-        <f>MAX(0,G19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="H20" s="38">
-        <f>MAX(0,H19)*Inputs!$B$50</f>
-        <v/>
-      </c>
-      <c r="I20" s="38">
-        <f>MAX(0,I19)*Inputs!$B$50</f>
+          <t xml:space="preserve">  operating margin</t>
+        </is>
+      </c>
+      <c r="B20" s="39">
+        <f>IF(B14=0,0,B19/B14)</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>IF(C14=0,0,C19/C14)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>IF(D14=0,0,D19/D14)</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
+        <f>IF(E14=0,0,E19/E14)</f>
+        <v/>
+      </c>
+      <c r="F20" s="39">
+        <f>IF(F14=0,0,F19/F14)</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>IF(G14=0,0,G19/G14)</f>
+        <v/>
+      </c>
+      <c r="H20" s="39">
+        <f>IF(H14=0,0,H19/H14)</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>IF(I14=0,0,I19/I14)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>NOPAT</t>
-        </is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
+        <f>Inputs!$B$34</f>
+        <v/>
       </c>
       <c r="C21" s="38">
-        <f>C19-C20</f>
+        <f>B21*(1+Inputs!C112)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>D19-D20</f>
+        <f>C21*(1+Inputs!D112)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>E19-E20</f>
+        <f>D21*(1+Inputs!E112)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>F19-F20</f>
+        <f>E21*(1+Inputs!F112)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>G19-G20</f>
+        <f>F21*(1+Inputs!G112)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>H19-H20</f>
+        <f>G21*(1+Inputs!H112)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>I19-I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="38">
-        <f>I21*(1+Inputs!$B$53)</f>
+        <f>H21*(1+Inputs!I112)</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>D&amp;A</t>
-        </is>
-      </c>
-      <c r="B22" s="36">
-        <f>Inputs!$B$35</f>
-        <v/>
+          <t>EBIT after SBC</t>
+        </is>
       </c>
       <c r="C22" s="38">
-        <f>B22+Inputs!$B$56*(B23-B22)</f>
+        <f>C19-C21</f>
         <v/>
       </c>
       <c r="D22" s="38">
-        <f>C22+Inputs!$B$56*(C23-C22)</f>
+        <f>D19-D21</f>
         <v/>
       </c>
       <c r="E22" s="38">
-        <f>D22+Inputs!$B$56*(D23-D22)</f>
+        <f>E19-E21</f>
         <v/>
       </c>
       <c r="F22" s="38">
-        <f>E22+Inputs!$B$56*(E23-E22)</f>
+        <f>F19-F21</f>
         <v/>
       </c>
       <c r="G22" s="38">
-        <f>F22+Inputs!$B$56*(F23-F22)</f>
+        <f>G19-G21</f>
         <v/>
       </c>
       <c r="H22" s="38">
-        <f>G22+Inputs!$B$56*(G23-G22)</f>
+        <f>H19-H21</f>
         <v/>
       </c>
       <c r="I22" s="38">
-        <f>H22+Inputs!$B$56*(H23-H22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="38">
-        <f>I22*(1+Inputs!$B$53)</f>
+        <f>I19-I21</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Capex</t>
-        </is>
-      </c>
-      <c r="B23" s="36">
-        <f>Inputs!$B$36</f>
-        <v/>
-      </c>
-      <c r="C23" s="36">
-        <f>Inputs!C107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
-        <f>Inputs!D107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="E23" s="36">
-        <f>Inputs!E107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="F23" s="36">
-        <f>Inputs!F107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="G23" s="36">
-        <f>Inputs!G107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="H23" s="36">
-        <f>Inputs!H107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="I23" s="36">
-        <f>Inputs!I107*Inputs!$B$64</f>
-        <v/>
-      </c>
-      <c r="J23" s="38">
-        <f>J22*Inputs!$B$54</f>
+          <t>Taxes on EBIT</t>
+        </is>
+      </c>
+      <c r="C23" s="38">
+        <f>MAX(0,C22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
+        <f>MAX(0,D22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>MAX(0,E22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="F23" s="38">
+        <f>MAX(0,F22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G23" s="38">
+        <f>MAX(0,G22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="H23" s="38">
+        <f>MAX(0,H22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="I23" s="38">
+        <f>MAX(0,I22)*Inputs!$B$60</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Change in net working capital</t>
+          <t>NOPAT</t>
         </is>
       </c>
       <c r="C24" s="38">
-        <f>Inputs!$B$55*(C11-B11)</f>
+        <f>C22-C23</f>
         <v/>
       </c>
       <c r="D24" s="38">
-        <f>Inputs!$B$55*(D11-C11)</f>
+        <f>D22-D23</f>
         <v/>
       </c>
       <c r="E24" s="38">
-        <f>Inputs!$B$55*(E11-D11)</f>
+        <f>E22-E23</f>
         <v/>
       </c>
       <c r="F24" s="38">
-        <f>Inputs!$B$55*(F11-E11)</f>
+        <f>F22-F23</f>
         <v/>
       </c>
       <c r="G24" s="38">
-        <f>Inputs!$B$55*(G11-F11)</f>
+        <f>G22-G23</f>
         <v/>
       </c>
       <c r="H24" s="38">
-        <f>Inputs!$B$55*(H11-G11)</f>
+        <f>H22-H23</f>
         <v/>
       </c>
       <c r="I24" s="38">
-        <f>Inputs!$B$55*(I11-H11)</f>
+        <f>I22-I23</f>
         <v/>
       </c>
       <c r="J24" s="38">
-        <f>Inputs!$B$55*(J11-I11)</f>
+        <f>I24*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow</t>
-        </is>
-      </c>
-      <c r="B25" s="30" t="n"/>
-      <c r="C25" s="54">
-        <f>C21+C22-C23-C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="54">
-        <f>D21+D22-D23-D24</f>
-        <v/>
-      </c>
-      <c r="E25" s="54">
-        <f>E21+E22-E23-E24</f>
-        <v/>
-      </c>
-      <c r="F25" s="54">
-        <f>F21+F22-F23-F24</f>
-        <v/>
-      </c>
-      <c r="G25" s="54">
-        <f>G21+G22-G23-G24</f>
-        <v/>
-      </c>
-      <c r="H25" s="54">
-        <f>H21+H22-H23-H24</f>
-        <v/>
-      </c>
-      <c r="I25" s="54">
-        <f>I21+I22-I23-I24</f>
-        <v/>
-      </c>
-      <c r="J25" s="54">
-        <f>J21+J22-J23-J24</f>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B25" s="36">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="C25" s="38">
+        <f>B25+Inputs!$B$66*(B26-B25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="38">
+        <f>C25+Inputs!$B$66*(C26-C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>D25+Inputs!$B$66*(D26-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="38">
+        <f>E25+Inputs!$B$66*(E26-E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="38">
+        <f>F25+Inputs!$B$66*(F26-F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="38">
+        <f>G25+Inputs!$B$66*(G26-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>H25+Inputs!$B$66*(H26-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="38">
+        <f>I25*(1+Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FCF margin</t>
-        </is>
-      </c>
-      <c r="C26" s="39">
-        <f>IF(C11=0,0,C25/C11)</f>
-        <v/>
-      </c>
-      <c r="D26" s="39">
-        <f>IF(D11=0,0,D25/D11)</f>
-        <v/>
-      </c>
-      <c r="E26" s="39">
-        <f>IF(E11=0,0,E25/E11)</f>
-        <v/>
-      </c>
-      <c r="F26" s="39">
-        <f>IF(F11=0,0,F25/F11)</f>
-        <v/>
-      </c>
-      <c r="G26" s="39">
-        <f>IF(G11=0,0,G25/G11)</f>
-        <v/>
-      </c>
-      <c r="H26" s="39">
-        <f>IF(H11=0,0,H25/H11)</f>
-        <v/>
-      </c>
-      <c r="I26" s="39">
-        <f>IF(I11=0,0,I25/I11)</f>
-        <v/>
-      </c>
-      <c r="J26" s="39">
-        <f>IF(J11=0,0,J25/J11)</f>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Inputs!C124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Inputs!D124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>Inputs!E124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>Inputs!F124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>Inputs!G124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="H26" s="36">
+        <f>Inputs!H124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="I26" s="36">
+        <f>Inputs!I124*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="J26" s="38">
+        <f>J25*Inputs!$B$64</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Change in net working capital</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>Inputs!$B$65*(C14-B14)</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>Inputs!$B$65*(D14-C14)</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>Inputs!$B$65*(E14-D14)</f>
+        <v/>
+      </c>
+      <c r="F27" s="38">
+        <f>Inputs!$B$65*(F14-E14)</f>
+        <v/>
+      </c>
+      <c r="G27" s="38">
+        <f>Inputs!$B$65*(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="H27" s="38">
+        <f>Inputs!$B$65*(H14-G14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="38">
+        <f>Inputs!$B$65*(I14-H14)</f>
+        <v/>
+      </c>
+      <c r="J27" s="38">
+        <f>Inputs!$B$65*(J14-I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="54">
+        <f>C24+C25-C26-C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="54">
+        <f>D24+D25-D26-D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="54">
+        <f>E24+E25-E26-E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="54">
+        <f>F24+F25-F26-F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="54">
+        <f>G24+G25-G26-G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="54">
+        <f>H24+H25-H26-H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="54">
+        <f>I24+I25-I26-I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="54">
+        <f>J24+J25-J26-J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF margin</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>IF(C14=0,0,C28/C14)</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>IF(D14=0,0,D28/D14)</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>IF(E14=0,0,E28/E14)</f>
+        <v/>
+      </c>
+      <c r="F29" s="39">
+        <f>IF(F14=0,0,F28/F14)</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>IF(G14=0,0,G28/G14)</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>IF(H14=0,0,H28/H14)</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>IF(I14=0,0,I28/I14)</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>IF(J14=0,0,J28/J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C27" s="31">
-        <f>1/(1+Inputs!$B$52)^C4</f>
-        <v/>
-      </c>
-      <c r="D27" s="31">
-        <f>1/(1+Inputs!$B$52)^D4</f>
-        <v/>
-      </c>
-      <c r="E27" s="31">
-        <f>1/(1+Inputs!$B$52)^E4</f>
-        <v/>
-      </c>
-      <c r="F27" s="31">
-        <f>1/(1+Inputs!$B$52)^F4</f>
-        <v/>
-      </c>
-      <c r="G27" s="31">
-        <f>1/(1+Inputs!$B$52)^G4</f>
-        <v/>
-      </c>
-      <c r="H27" s="31">
-        <f>1/(1+Inputs!$B$52)^H4</f>
-        <v/>
-      </c>
-      <c r="I27" s="31">
-        <f>1/(1+Inputs!$B$52)^I4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>PV of FCF</t>
-        </is>
-      </c>
-      <c r="C28" s="38">
-        <f>C25*C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="38">
-        <f>D25*D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="38">
-        <f>E25*E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="38">
-        <f>F25*F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="38">
-        <f>G25*G27</f>
-        <v/>
-      </c>
-      <c r="H28" s="38">
-        <f>H25*H27</f>
-        <v/>
-      </c>
-      <c r="I28" s="38">
-        <f>I25*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>VALUATION</t>
-        </is>
+      <c r="C30" s="31">
+        <f>1/(1+Inputs!$B$62)^C4</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>1/(1+Inputs!$B$62)^D4</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>1/(1+Inputs!$B$62)^E4</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>1/(1+Inputs!$B$62)^F4</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>1/(1+Inputs!$B$62)^G4</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>1/(1+Inputs!$B$62)^H4</f>
+        <v/>
+      </c>
+      <c r="I30" s="31">
+        <f>1/(1+Inputs!$B$62)^I4</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C31" s="38">
+        <f>C28*C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="38">
+        <f>D28*D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E28*E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="38">
+        <f>F28*F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="38">
+        <f>G28*G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="38">
+        <f>H28*H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="38">
+        <f>I28*I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION (value per share floored at $0: equity has limited liability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>Sum of PV of explicit FCF (2027-2033)</t>
         </is>
       </c>
-      <c r="B31" s="38">
-        <f>SUM(C28:I28)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value at end-2033</t>
-        </is>
-      </c>
-      <c r="B32" s="38">
-        <f>IF(Inputs!$B$52&lt;=Inputs!$B$53,0,J25/(Inputs!$B$52-Inputs!$B$53))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B33" s="38">
-        <f>B32*I27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
       <c r="B34" s="38">
-        <f>B31+B33</f>
+        <f>SUM(C31:I31)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>+ Net cash (incl. Aug-26 raise)</t>
-        </is>
-      </c>
-      <c r="B35" s="36">
-        <f>Inputs!$B$16</f>
+          <t>Terminal value at end-2033</t>
+        </is>
+      </c>
+      <c r="B35" s="38">
+        <f>IF(Inputs!$B$62&lt;=Inputs!$B$63,0,J28/(Inputs!$B$62-Inputs!$B$63))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>+ Altera stake</t>
-        </is>
-      </c>
-      <c r="B36" s="36">
-        <f>Inputs!$B$14</f>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B36" s="38">
+        <f>B35*I30</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>- Non-controlling interests</t>
-        </is>
-      </c>
-      <c r="B37" s="36">
-        <f>-Inputs!$B$15</f>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>B34+B36</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="B38" s="38">
-        <f>B34+B35+B36+B37</f>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>+ Net cash (incl. Aug-26 raise)</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>Inputs!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Diluted shares (bn)</t>
-        </is>
-      </c>
-      <c r="B39" s="37">
-        <f>Inputs!$B$9</f>
+          <t>+ Altera stake</t>
+        </is>
+      </c>
+      <c r="B39" s="36">
+        <f>Inputs!$B$14</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Value per share ($)</t>
-        </is>
-      </c>
-      <c r="B40" s="34">
-        <f>IF(B39=0,0,B38/B39)</f>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>- Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>-Inputs!$B$15</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B41" s="33">
-        <f>Inputs!$B$4</f>
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B41" s="38">
+        <f>B37+B38+B39+B40</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B42" s="39">
-        <f>IF(B41=0,0,B40/B41-1)</f>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Terminal value as % of EV</t>
-        </is>
-      </c>
-      <c r="B43" s="39">
-        <f>IF(B34=0,0,B33/B34)</f>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Value per share ($)</t>
+        </is>
+      </c>
+      <c r="B43" s="34">
+        <f>IF(B42=0,0,MAX(0,B41/B42))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B44" s="11">
-        <f>IF(C21&lt;=0,0,B40/(C21/B39))</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>Upside / (downside) vs price</t>
+        </is>
+      </c>
+      <c r="B45" s="39">
+        <f>IF(B44=0,0,B43/B44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>IF(B37=0,0,B36/B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>IF(C24&lt;=0,0,B43/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B45" s="11">
-        <f>IF(C21&lt;=0,0,B41/(C21/B39))</f>
+      <c r="B48" s="11">
+        <f>IF(C24&lt;=0,0,B44/(C24/B42))</f>
         <v/>
       </c>
     </row>

--- a/research/model/intel_valuation_model.xlsx
+++ b/research/model/intel_valuation_model.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Bear" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Base" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Bull" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Taiwan" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -525,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A35"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -645,116 +646,151 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
+          <t>- TAIWAN scenario (4th): Taiwan fabs cut off from Western customers from 2027 (invasion, blockade, or reunification followed by US export controls</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
+          <t xml:space="preserve">  treating Taiwan as China). Intel becomes the main non-Asian leading-edge source; AMD/Qualcomm/Apple/NVIDIA lose TSMC supply. Modeled: server/client</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  share capture after a 2027 disruption year, external foundry revenue up to $70bn (capacity-limited), GM to 62%, China revenue to zero, capex ~$40-50bn.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Not modeled: global recession depth, US price controls/Defense Production Act allocation, higher cost of capital, loss of Intel's own TSMC-made tiles</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
+          <t xml:space="preserve">  beyond 2027, damage to Asian packaging/test sites (Malaysia) and suppliers. The Summary sheet solves for the probability that justifies the price.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      customer, external foundry stays mostly Altera + small packaging deals; 18A cost parity slips; gross margin stays near 2026 levels.</t>
+          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
+          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
+          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      customer, external foundry stays mostly Altera + small packaging deals; 18A cost parity slips; gross margin stays near 2026 levels.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT CAVEATS</t>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
+          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
+          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
+          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANT CAVEATS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>- Not investment advice.</t>
         </is>
@@ -771,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -779,7 +815,8 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -812,6 +849,11 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>Prob-weighted</t>
         </is>
       </c>
@@ -834,7 +876,11 @@
         <f>Inputs!$B$81</f>
         <v/>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="32">
+        <f>Inputs!$B$82</f>
+        <v/>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Weights are my judgment (Inputs sheet); they must sum to 100%</t>
         </is>
@@ -858,11 +904,15 @@
         <f>Bull!B43</f>
         <v/>
       </c>
-      <c r="E5" s="34">
-        <f>SUMPRODUCT(B4:D4,B5:D5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="33">
+        <f>Taiwan!B43</f>
+        <v/>
+      </c>
+      <c r="F5" s="34">
+        <f>SUMPRODUCT(B4:E4,B5:E5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Check weights sum:</t>
         </is>
@@ -886,12 +936,16 @@
         <f>Bull!B45</f>
         <v/>
       </c>
-      <c r="E6" s="35">
-        <f>IF(Inputs!$B$4=0,0,E5/Inputs!$B$4-1)</f>
-        <v/>
-      </c>
-      <c r="F6" s="2">
-        <f>IF(ABS(Inputs!$B$82-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
+      <c r="E6" s="32">
+        <f>Taiwan!B45</f>
+        <v/>
+      </c>
+      <c r="F6" s="35">
+        <f>IF(Inputs!$B$4=0,0,F5/Inputs!$B$4-1)</f>
+        <v/>
+      </c>
+      <c r="G6" s="2">
+        <f>IF(ABS(Inputs!$B$83-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
         <v/>
       </c>
     </row>
@@ -913,6 +967,10 @@
         <f>Bull!B37</f>
         <v/>
       </c>
+      <c r="E7" s="36">
+        <f>Taiwan!B37</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -932,6 +990,10 @@
         <f>Bull!B46</f>
         <v/>
       </c>
+      <c r="E8" s="32">
+        <f>Taiwan!B46</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -951,6 +1013,10 @@
         <f>Bull!F14</f>
         <v/>
       </c>
+      <c r="E9" s="36">
+        <f>Taiwan!F14</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -970,6 +1036,10 @@
         <f>Bull!I14</f>
         <v/>
       </c>
+      <c r="E10" s="36">
+        <f>Taiwan!I14</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -989,6 +1059,10 @@
         <f>Bull!F16</f>
         <v/>
       </c>
+      <c r="E11" s="32">
+        <f>Taiwan!F16</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1008,6 +1082,10 @@
         <f>Bull!F20</f>
         <v/>
       </c>
+      <c r="E12" s="32">
+        <f>Taiwan!F20</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1027,6 +1105,10 @@
         <f>Bull!I9</f>
         <v/>
       </c>
+      <c r="E13" s="36">
+        <f>Taiwan!I9</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1046,6 +1128,10 @@
         <f>Bull!I13</f>
         <v/>
       </c>
+      <c r="E14" s="36">
+        <f>Taiwan!I13</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1065,6 +1151,10 @@
         <f>Bull!F28</f>
         <v/>
       </c>
+      <c r="E15" s="36">
+        <f>Taiwan!F28</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1084,6 +1174,10 @@
         <f>SUM(Bull!C28:I28)</f>
         <v/>
       </c>
+      <c r="E16" s="36">
+        <f>SUM(Taiwan!C28:I28)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1208,7 +1302,7 @@
         <f>B29/Base!I30*(Inputs!$B$62-Inputs!$B$63)</f>
         <v/>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>FCF in 2034 that the Base explicit years plus the market price imply</t>
         </is>
@@ -1278,7 +1372,7 @@
       <c r="B36" s="40" t="n">
         <v>0.603</v>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Source: TSMC Q2 2026 results (60.3% op margin). Context only</t>
         </is>
@@ -1364,33 +1458,89 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>HOW TO READ THIS</t>
+          <t>TAIWAN TEST: WHAT PROBABILITY OF THE TAIWAN SCENARIO WOULD JUSTIFY TODAY'S PRICE?</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
-        </is>
+          <t>Taiwan-scenario value per share ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="41">
+        <f>E5</f>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
-        </is>
+          <t>Non-Taiwan value per share, re-weighted (Bear/Base/Bull weights normalized)</t>
+        </is>
+      </c>
+      <c r="B47" s="41">
+        <f>IF((Inputs!$B$79+Inputs!$B$80+Inputs!$B$81)=0,0,(B5*Inputs!$B$79+C5*Inputs!$B$80+D5*Inputs!$B$81)/(Inputs!$B$79+Inputs!$B$80+Inputs!$B$81))</f>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
-        </is>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B48" s="41">
+        <f>Inputs!$B$4</f>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Break-even probability of Taiwan scenario to justify price</t>
+        </is>
+      </c>
+      <c r="B49" s="39">
+        <f>IF(B46&lt;=B48,"Not reachable: Taiwan value &lt; price",(B48-B47)/(B46-B47))</f>
+        <v/>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Read as: 'the market price is fair IF you believe this is the probability of a Taiwan cut-off (with Taiwan-scenario payoffs as modeled)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>- Terminal value is a large share of EV in every scenario. Small changes in WACC or terminal growth move the answer a lot: see the Sensitivity sheet.</t>
         </is>
@@ -1407,7 +1557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1890,157 +2040,311 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Current price ($)</t>
-        </is>
-      </c>
-      <c r="B27" s="33">
-        <f>Inputs!$B$4</f>
-        <v/>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Taiwan scenario: value/share vs WACC and terminal growth (live formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>WACC (down) / terminal g (across)</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C28" s="40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D28" s="40" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E28" s="40" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F28" s="40" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>TORNADO (Base scenario): one input flexed at a time</t>
-        </is>
+      <c r="A29" s="40" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="B29" s="41">
+        <f>MAX(0,IF($A29&lt;=B$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A29)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+B$28)+Taiwan!$I$25*(1+B$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*B$28)/($A29-B$28)/(1+$A29)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C29" s="41">
+        <f>MAX(0,IF($A29&lt;=C$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A29)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+C$28)+Taiwan!$I$25*(1+C$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*C$28)/($A29-C$28)/(1+$A29)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D29" s="41">
+        <f>MAX(0,IF($A29&lt;=D$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A29)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+D$28)+Taiwan!$I$25*(1+D$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*D$28)/($A29-D$28)/(1+$A29)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E29" s="41">
+        <f>MAX(0,IF($A29&lt;=E$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A29)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+E$28)+Taiwan!$I$25*(1+E$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*E$28)/($A29-E$28)/(1+$A29)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F29" s="41">
+        <f>MAX(0,IF($A29&lt;=F$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A29)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+F$28)+Taiwan!$I$25*(1+F$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*F$28)/($A29-F$28)/(1+$A29)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Input flexed (Base scenario, others held)</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>Low case $/sh</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>High case $/sh</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>Base $/sh</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>Swing $/sh</t>
-        </is>
+      <c r="A30" s="40" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="B30" s="41">
+        <f>MAX(0,IF($A30&lt;=B$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A30)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+B$28)+Taiwan!$I$25*(1+B$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*B$28)/($A30-B$28)/(1+$A30)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C30" s="41">
+        <f>MAX(0,IF($A30&lt;=C$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A30)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+C$28)+Taiwan!$I$25*(1+C$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*C$28)/($A30-C$28)/(1+$A30)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D30" s="41">
+        <f>MAX(0,IF($A30&lt;=D$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A30)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+D$28)+Taiwan!$I$25*(1+D$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*D$28)/($A30-D$28)/(1+$A30)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E30" s="41">
+        <f>MAX(0,IF($A30&lt;=E$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A30)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+E$28)+Taiwan!$I$25*(1+E$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*E$28)/($A30-E$28)/(1+$A30)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F30" s="41">
+        <f>MAX(0,IF($A30&lt;=F$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A30)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+F$28)+Taiwan!$I$25*(1+F$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*F$28)/($A30-F$28)/(1+$A30)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Ext. foundry revenue x0.5 / x2.0</t>
-        </is>
-      </c>
-      <c r="B31" s="42" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="C31" s="42" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="D31" s="43">
-        <f>Base!B43</f>
-        <v/>
-      </c>
-      <c r="E31" s="44">
-        <f>C31-B31</f>
+      <c r="A31" s="40" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="B31" s="41">
+        <f>MAX(0,IF($A31&lt;=B$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A31)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+B$28)+Taiwan!$I$25*(1+B$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*B$28)/($A31-B$28)/(1+$A31)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C31" s="41">
+        <f>MAX(0,IF($A31&lt;=C$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A31)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+C$28)+Taiwan!$I$25*(1+C$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*C$28)/($A31-C$28)/(1+$A31)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D31" s="41">
+        <f>MAX(0,IF($A31&lt;=D$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A31)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+D$28)+Taiwan!$I$25*(1+D$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*D$28)/($A31-D$28)/(1+$A31)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E31" s="41">
+        <f>MAX(0,IF($A31&lt;=E$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A31)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+E$28)+Taiwan!$I$25*(1+E$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*E$28)/($A31-E$28)/(1+$A31)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F31" s="41">
+        <f>MAX(0,IF($A31&lt;=F$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A31)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+F$28)+Taiwan!$I$25*(1+F$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*F$28)/($A31-F$28)/(1+$A31)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>China erosion 10 pts/yr faster / 5 pts/yr slower</t>
-        </is>
-      </c>
-      <c r="B32" s="42" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="C32" s="42" t="n">
-        <v>23.72</v>
-      </c>
-      <c r="D32" s="43">
-        <f>Base!B43</f>
-        <v/>
-      </c>
-      <c r="E32" s="44">
-        <f>C32-B32</f>
+      <c r="A32" s="40" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="B32" s="41">
+        <f>MAX(0,IF($A32&lt;=B$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A32)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+B$28)+Taiwan!$I$25*(1+B$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*B$28)/($A32-B$28)/(1+$A32)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C32" s="41">
+        <f>MAX(0,IF($A32&lt;=C$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A32)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+C$28)+Taiwan!$I$25*(1+C$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*C$28)/($A32-C$28)/(1+$A32)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D32" s="41">
+        <f>MAX(0,IF($A32&lt;=D$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A32)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+D$28)+Taiwan!$I$25*(1+D$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*D$28)/($A32-D$28)/(1+$A32)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E32" s="41">
+        <f>MAX(0,IF($A32&lt;=E$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A32)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+E$28)+Taiwan!$I$25*(1+E$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*E$28)/($A32-E$28)/(1+$A32)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F32" s="41">
+        <f>MAX(0,IF($A32&lt;=F$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A32)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+F$28)+Taiwan!$I$25*(1+F$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*F$28)/($A32-F$28)/(1+$A32)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>DCAI growth -3 / +3 pts per yr</t>
-        </is>
-      </c>
-      <c r="B33" s="42" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="C33" s="42" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="D33" s="43">
-        <f>Base!B43</f>
-        <v/>
-      </c>
-      <c r="E33" s="44">
-        <f>C33-B33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Gross margin -3 / +3 pts, all years</t>
-        </is>
-      </c>
-      <c r="B34" s="42" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="C34" s="42" t="n">
-        <v>26.43</v>
-      </c>
-      <c r="D34" s="43">
-        <f>Base!B43</f>
-        <v/>
-      </c>
-      <c r="E34" s="44">
-        <f>C34-B34</f>
+      <c r="A33" s="40" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="B33" s="41">
+        <f>MAX(0,IF($A33&lt;=B$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A33)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+B$28)+Taiwan!$I$25*(1+B$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*B$28)/($A33-B$28)/(1+$A33)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C33" s="41">
+        <f>MAX(0,IF($A33&lt;=C$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A33)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+C$28)+Taiwan!$I$25*(1+C$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*C$28)/($A33-C$28)/(1+$A33)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D33" s="41">
+        <f>MAX(0,IF($A33&lt;=D$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A33)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+D$28)+Taiwan!$I$25*(1+D$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*D$28)/($A33-D$28)/(1+$A33)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E33" s="41">
+        <f>MAX(0,IF($A33&lt;=E$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A33)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+E$28)+Taiwan!$I$25*(1+E$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*E$28)/($A33-E$28)/(1+$A33)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F33" s="41">
+        <f>MAX(0,IF($A33&lt;=F$28,0,(SUMPRODUCT(Taiwan!$C$28:$I$28,1/(1+$A33)^Taiwan!$C$4:$I$4)+(Taiwan!$I$24*(1+F$28)+Taiwan!$I$25*(1+F$28)*(1-Inputs!$B$64)-Inputs!$B$65*Taiwan!$I$14*F$28)/($A33-F$28)/(1+$A33)^Taiwan!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>Current price ($)</t>
+        </is>
+      </c>
+      <c r="B35" s="33">
+        <f>Inputs!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>TORNADO (Base scenario): one input flexed at a time</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Input flexed (Base scenario, others held)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>Low case $/sh</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>High case $/sh</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Base $/sh</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Swing $/sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Ext. foundry revenue x0.5 / x2.0</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="C39" s="42" t="n">
+        <v>32.43</v>
+      </c>
+      <c r="D39" s="43">
+        <f>Base!B43</f>
+        <v/>
+      </c>
+      <c r="E39" s="44">
+        <f>C39-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>China erosion 10 pts/yr faster / 5 pts/yr slower</t>
+        </is>
+      </c>
+      <c r="B40" s="42" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="C40" s="42" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="D40" s="43">
+        <f>Base!B43</f>
+        <v/>
+      </c>
+      <c r="E40" s="44">
+        <f>C40-B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>DCAI growth -3 / +3 pts per yr</t>
+        </is>
+      </c>
+      <c r="B41" s="42" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="C41" s="42" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="D41" s="43">
+        <f>Base!B43</f>
+        <v/>
+      </c>
+      <c r="E41" s="44">
+        <f>C41-B41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Gross margin -3 / +3 pts, all years</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="n">
+        <v>17.77</v>
+      </c>
+      <c r="C42" s="42" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="D42" s="43">
+        <f>Base!B43</f>
+        <v/>
+      </c>
+      <c r="E42" s="44">
+        <f>C42-B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
           <t>Capex x1.15 / x0.85 (2027+)</t>
         </is>
       </c>
-      <c r="B35" s="42" t="n">
+      <c r="B43" s="42" t="n">
         <v>19.72</v>
       </c>
-      <c r="C35" s="42" t="n">
+      <c r="C43" s="42" t="n">
         <v>24.48</v>
       </c>
-      <c r="D35" s="43">
+      <c r="D43" s="43">
         <f>Base!B43</f>
         <v/>
       </c>
-      <c r="E35" s="44">
-        <f>C35-B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="45" t="inlineStr">
+      <c r="E43" s="44">
+        <f>C43-B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>Tornado values are static: computed by setting each Inputs 'FLEX LEVER' and recalculating at the default inputs. Re-run them via the flex levers if you change base inputs. WACC and terminal-growth sensitivity: live grids above.</t>
         </is>
@@ -2057,7 +2361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3111,7 +3415,7 @@
         </is>
       </c>
       <c r="B79" s="53" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -3126,7 +3430,7 @@
         </is>
       </c>
       <c r="B80" s="53" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -3141,7 +3445,7 @@
         </is>
       </c>
       <c r="B81" s="53" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -3152,948 +3456,975 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>Taiwan (disruption / cut-off of Taiwan fabs from Western customers, from 2027)</t>
+        </is>
+      </c>
+      <c r="B82" s="53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit. The Summary sheet solves for the probability that would justify the current price</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>Check: sum of weights</t>
         </is>
       </c>
-      <c r="B82" s="39">
-        <f>$B$79+$B$80+$B$81</f>
-        <v/>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
+      <c r="B83" s="39">
+        <f>$B$79+$B$80+$B$81+$B$82</f>
+        <v/>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Must equal 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>SCENARIO DRIVERS (2027-2033). Hypothetical paths tied to product evidence; NOT forecasts I endorse</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
+          <t>SCENARIO DRIVERS (2027-2033). Hypothetical paths tied to product evidence; NOT forecasts I endorse</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
           <t>DCAI revenue growth</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
+      <c r="I86" s="3" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C86" s="53" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="D86" s="53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E86" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G86" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H86" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I86" s="53" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCAI revenue growth - Base</t>
+          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C87" s="53" t="n">
-        <v>0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="D87" s="53" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="E87" s="53" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F87" s="53" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="G87" s="53" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H87" s="53" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I87" s="53" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
+          <t xml:space="preserve">  DCAI revenue growth - Base</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C88" s="53" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="D88" s="53" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="E88" s="53" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="F88" s="53" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G88" s="53" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="H88" s="53" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I88" s="53" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C89" s="53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D89" s="53" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E89" s="53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F89" s="53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G89" s="53" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H89" s="53" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I89" s="53" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DCAI revenue growth - Taiwan</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C90" s="53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D90" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E90" s="53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F90" s="53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G90" s="53" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H90" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I90" s="53" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Rationale: Bear: shortage ASP spike (+48% YoY in Q2-26) reverses as Venice ships Q4-26 and Diamond Rapids slips; Bull: DMR competitive + agentic CPU demand persists</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
         <is>
           <t>CCPG (client) revenue growth</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="F91" s="3" t="inlineStr">
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="G91" s="3" t="inlineStr">
+      <c r="G93" s="3" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="H91" s="3" t="inlineStr">
+      <c r="H93" s="3" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C92" s="53" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="D92" s="53" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="E92" s="53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F92" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G92" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H92" s="53" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I92" s="53" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C93" s="53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D93" s="53" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E93" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F93" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G93" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H93" s="53" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I93" s="53" t="n">
-        <v>0.02</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C94" s="53" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="D94" s="53" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="E94" s="53" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="F94" s="53" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G94" s="53" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H94" s="53" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I94" s="53" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
-        </is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C95" s="53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D95" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E95" s="53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F95" s="53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G95" s="53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H95" s="53" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I95" s="53" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C96" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D96" s="53" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E96" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F96" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G96" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H96" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I96" s="53" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="inlineStr">
-        <is>
-          <t>External foundry + packaging revenue ($bn)</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Taiwan</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C97" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D97" s="53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E97" s="53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F97" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G97" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H97" s="53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I97" s="53" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C98" s="52" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D98" s="52" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E98" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="F98" s="52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G98" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="H98" s="52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I98" s="52" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C99" s="52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D99" s="52" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E99" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="F99" s="52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G99" s="52" t="n">
-        <v>11</v>
-      </c>
-      <c r="H99" s="52" t="n">
-        <v>13</v>
-      </c>
-      <c r="I99" s="52" t="n">
-        <v>15</v>
+          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
+        </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C100" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D100" s="52" t="n">
-        <v>7</v>
-      </c>
-      <c r="E100" s="52" t="n">
-        <v>12</v>
-      </c>
-      <c r="F100" s="52" t="n">
-        <v>18</v>
-      </c>
-      <c r="G100" s="52" t="n">
-        <v>24</v>
-      </c>
-      <c r="H100" s="52" t="n">
-        <v>29</v>
-      </c>
-      <c r="I100" s="52" t="n">
-        <v>33</v>
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>External foundry + packaging revenue ($bn)</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
-        </is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C101" s="52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D101" s="52" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E101" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G101" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H101" s="52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I101" s="52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C102" s="52" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D102" s="52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E102" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F102" s="52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G102" s="52" t="n">
+        <v>11</v>
+      </c>
+      <c r="H102" s="52" t="n">
+        <v>13</v>
+      </c>
+      <c r="I102" s="52" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G103" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C103" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="F103" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="G103" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="H103" s="52" t="n">
+        <v>29</v>
+      </c>
+      <c r="I103" s="52" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Taiwan</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C104" s="53" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D104" s="53" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E104" s="53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F104" s="53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G104" s="53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H104" s="53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I104" s="53" t="n">
-        <v>0.4</v>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C104" s="52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D104" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="E104" s="52" t="n">
+        <v>45</v>
+      </c>
+      <c r="F104" s="52" t="n">
+        <v>55</v>
+      </c>
+      <c r="G104" s="52" t="n">
+        <v>60</v>
+      </c>
+      <c r="H104" s="52" t="n">
+        <v>65</v>
+      </c>
+      <c r="I104" s="52" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C108" s="53" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D108" s="53" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E108" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F108" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G108" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H108" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I108" s="53" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Non-GAAP gross margin - Base</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="C105" s="53" t="n">
+      <c r="C109" s="53" t="n">
         <v>0.43</v>
       </c>
-      <c r="D105" s="53" t="n">
+      <c r="D109" s="53" t="n">
         <v>0.45</v>
       </c>
-      <c r="E105" s="53" t="n">
+      <c r="E109" s="53" t="n">
         <v>0.47</v>
       </c>
-      <c r="F105" s="53" t="n">
+      <c r="F109" s="53" t="n">
         <v>0.48</v>
       </c>
-      <c r="G105" s="53" t="n">
+      <c r="G109" s="53" t="n">
         <v>0.49</v>
       </c>
-      <c r="H105" s="53" t="n">
+      <c r="H109" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="I105" s="53" t="n">
+      <c r="I109" s="53" t="n">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C106" s="53" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="D106" s="53" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E106" s="53" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F106" s="53" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G106" s="53" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H106" s="53" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I106" s="53" t="n">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP opex growth</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="C110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.46</v>
       </c>
       <c r="D110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.49</v>
       </c>
       <c r="E110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="F110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.54</v>
       </c>
       <c r="G110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.55</v>
       </c>
       <c r="H110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I110" s="53" t="n">
-        <v>0.01</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Taiwan</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.45</v>
       </c>
       <c r="D111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="E111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="F111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="G111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="H111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="I111" s="53" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="G112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="H112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I112" s="53" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
+          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP opex growth</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>China domestic end-demand revenue change per year</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G115" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H115" s="53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I115" s="53" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bear</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C116" s="53" t="n">
-        <v>-0.2</v>
+        <v>0.03</v>
       </c>
       <c r="D116" s="53" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="E116" s="53" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="F116" s="53" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G116" s="53" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H116" s="53" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I116" s="53" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Base</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="C117" s="53" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D117" s="53" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E117" s="53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F117" s="53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G117" s="53" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H117" s="53" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I117" s="53" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bull</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Taiwan</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="D118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I118" s="53" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Bear: truce lapses Nov-26, xinchuang spreads from government to SOEs/finance/telecom, and origin rule hits 18A (US-fabbed) parts. Base: steady localization. Bull: truce holds, erosion slow</t>
+          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>Gross capex ($bn)</t>
+          <t>China domestic end-demand revenue change per year</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4140,7 +4471,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bear</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -4148,32 +4479,32 @@
           <t>Bear</t>
         </is>
       </c>
-      <c r="C122" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="D122" s="52" t="n">
-        <v>18</v>
-      </c>
-      <c r="E122" s="52" t="n">
-        <v>16</v>
-      </c>
-      <c r="F122" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="G122" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="H122" s="52" t="n">
-        <v>15</v>
-      </c>
-      <c r="I122" s="52" t="n">
-        <v>15</v>
+      <c r="C122" s="53" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="D122" s="53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E122" s="53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F122" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G122" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H122" s="53" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I122" s="53" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Base</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -4181,32 +4512,32 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="C123" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="D123" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="E123" s="52" t="n">
-        <v>24</v>
-      </c>
-      <c r="F123" s="52" t="n">
-        <v>22</v>
-      </c>
-      <c r="G123" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="H123" s="52" t="n">
-        <v>20</v>
-      </c>
-      <c r="I123" s="52" t="n">
-        <v>20</v>
+      <c r="C123" s="53" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D123" s="53" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E123" s="53" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F123" s="53" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G123" s="53" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H123" s="53" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I123" s="53" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Bull</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bull</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -4214,30 +4545,249 @@
           <t>Bull</t>
         </is>
       </c>
-      <c r="C124" s="52" t="n">
-        <v>30</v>
-      </c>
-      <c r="D124" s="52" t="n">
-        <v>32</v>
-      </c>
-      <c r="E124" s="52" t="n">
-        <v>30</v>
-      </c>
-      <c r="F124" s="52" t="n">
-        <v>28</v>
-      </c>
-      <c r="G124" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="H124" s="52" t="n">
-        <v>26</v>
-      </c>
-      <c r="I124" s="52" t="n">
-        <v>26</v>
+      <c r="C124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H124" s="53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I124" s="53" t="n">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Taiwan</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C125" s="53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: Bear: truce lapses Nov-26, xinchuang spreads from government to SOEs/finance/telecom, and origin rule hits 18A (US-fabbed) parts. Base: steady localization. Bull: truce holds, erosion slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>Gross capex ($bn)</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C129" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="D129" s="52" t="n">
+        <v>18</v>
+      </c>
+      <c r="E129" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="F129" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="G129" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="H129" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="I129" s="52" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C130" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="D130" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="E130" s="52" t="n">
+        <v>24</v>
+      </c>
+      <c r="F130" s="52" t="n">
+        <v>22</v>
+      </c>
+      <c r="G130" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H130" s="52" t="n">
+        <v>20</v>
+      </c>
+      <c r="I130" s="52" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Bull</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C131" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="D131" s="52" t="n">
+        <v>32</v>
+      </c>
+      <c r="E131" s="52" t="n">
+        <v>30</v>
+      </c>
+      <c r="F131" s="52" t="n">
+        <v>28</v>
+      </c>
+      <c r="G131" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="H131" s="52" t="n">
+        <v>26</v>
+      </c>
+      <c r="I131" s="52" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Taiwan</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C132" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="D132" s="52" t="n">
+        <v>50</v>
+      </c>
+      <c r="E132" s="52" t="n">
+        <v>50</v>
+      </c>
+      <c r="F132" s="52" t="n">
+        <v>45</v>
+      </c>
+      <c r="G132" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="H132" s="52" t="n">
+        <v>35</v>
+      </c>
+      <c r="I132" s="52" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rationale: 2027 guided 'significantly above' 2026 (&gt;$20bn). Gross; excludes SCIP partner/government offsets (conservative)</t>
         </is>
@@ -4409,31 +4959,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C86+Inputs!$B$72</f>
+        <f>Inputs!C87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D86+Inputs!$B$72</f>
+        <f>Inputs!D87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E86+Inputs!$B$72</f>
+        <f>Inputs!E87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F86+Inputs!$B$72</f>
+        <f>Inputs!F87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G86+Inputs!$B$72</f>
+        <f>Inputs!G87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H86+Inputs!$B$72</f>
+        <f>Inputs!H87+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I86+Inputs!$B$72</f>
+        <f>Inputs!I87+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -4483,31 +5033,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C92</f>
+        <f>Inputs!C94</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D92</f>
+        <f>Inputs!D94</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E92</f>
+        <f>Inputs!E94</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F92</f>
+        <f>Inputs!F94</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G92</f>
+        <f>Inputs!G94</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H92</f>
+        <f>Inputs!H94</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I92</f>
+        <f>Inputs!I94</f>
         <v/>
       </c>
     </row>
@@ -4522,31 +5072,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C98*Inputs!$B$73</f>
+        <f>Inputs!C101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D98*Inputs!$B$73</f>
+        <f>Inputs!D101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E98*Inputs!$B$73</f>
+        <f>Inputs!E101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F98*Inputs!$B$73</f>
+        <f>Inputs!F101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G98*Inputs!$B$73</f>
+        <f>Inputs!G101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H98*Inputs!$B$73</f>
+        <f>Inputs!H101*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I98*Inputs!$B$73</f>
+        <f>Inputs!I101*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -4638,31 +5188,31 @@
         <v>1</v>
       </c>
       <c r="C12" s="27">
-        <f>MAX(0,B12*(1+Inputs!C116+Inputs!$B$75))</f>
+        <f>MAX(0,B12*(1+Inputs!C122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D12" s="27">
-        <f>MAX(0,C12*(1+Inputs!D116+Inputs!$B$75))</f>
+        <f>MAX(0,C12*(1+Inputs!D122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>MAX(0,D12*(1+Inputs!E116+Inputs!$B$75))</f>
+        <f>MAX(0,D12*(1+Inputs!E122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>MAX(0,E12*(1+Inputs!F116+Inputs!$B$75))</f>
+        <f>MAX(0,E12*(1+Inputs!F122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G12" s="27">
-        <f>MAX(0,F12*(1+Inputs!G116+Inputs!$B$75))</f>
+        <f>MAX(0,F12*(1+Inputs!G122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H12" s="27">
-        <f>MAX(0,G12*(1+Inputs!H116+Inputs!$B$75))</f>
+        <f>MAX(0,G12*(1+Inputs!H122+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I12" s="27">
-        <f>MAX(0,H12*(1+Inputs!I116+Inputs!$B$75))</f>
+        <f>MAX(0,H12*(1+Inputs!I122+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -4794,31 +5344,31 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>Inputs!C104+Inputs!$B$71</f>
+        <f>Inputs!C108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D16" s="32">
-        <f>Inputs!D104+Inputs!$B$71</f>
+        <f>Inputs!D108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>Inputs!E104+Inputs!$B$71</f>
+        <f>Inputs!E108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F16" s="32">
-        <f>Inputs!F104+Inputs!$B$71</f>
+        <f>Inputs!F108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>Inputs!G104+Inputs!$B$71</f>
+        <f>Inputs!G108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>Inputs!H104+Inputs!$B$71</f>
+        <f>Inputs!H108+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>Inputs!I104+Inputs!$B$71</f>
+        <f>Inputs!I108+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -4872,31 +5422,31 @@
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C110)</f>
+        <f>B18*(1+Inputs!C115)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D110)</f>
+        <f>C18*(1+Inputs!D115)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E110)</f>
+        <f>D18*(1+Inputs!E115)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F110)</f>
+        <f>E18*(1+Inputs!F115)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G110)</f>
+        <f>F18*(1+Inputs!G115)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H110)</f>
+        <f>G18*(1+Inputs!H115)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I110)</f>
+        <f>H18*(1+Inputs!I115)</f>
         <v/>
       </c>
     </row>
@@ -4990,31 +5540,31 @@
         <v/>
       </c>
       <c r="C21" s="38">
-        <f>B21*(1+Inputs!C110)</f>
+        <f>B21*(1+Inputs!C115)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>C21*(1+Inputs!D110)</f>
+        <f>C21*(1+Inputs!D115)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>D21*(1+Inputs!E110)</f>
+        <f>D21*(1+Inputs!E115)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>E21*(1+Inputs!F110)</f>
+        <f>E21*(1+Inputs!F115)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>F21*(1+Inputs!G110)</f>
+        <f>F21*(1+Inputs!G115)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>G21*(1+Inputs!H110)</f>
+        <f>G21*(1+Inputs!H115)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>H21*(1+Inputs!I110)</f>
+        <f>H21*(1+Inputs!I115)</f>
         <v/>
       </c>
     </row>
@@ -5181,31 +5731,31 @@
         <v/>
       </c>
       <c r="C26" s="36">
-        <f>Inputs!C122*Inputs!$B$74</f>
+        <f>Inputs!C129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="D26" s="36">
-        <f>Inputs!D122*Inputs!$B$74</f>
+        <f>Inputs!D129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="E26" s="36">
-        <f>Inputs!E122*Inputs!$B$74</f>
+        <f>Inputs!E129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="F26" s="36">
-        <f>Inputs!F122*Inputs!$B$74</f>
+        <f>Inputs!F129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="G26" s="36">
-        <f>Inputs!G122*Inputs!$B$74</f>
+        <f>Inputs!G129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="H26" s="36">
-        <f>Inputs!H122*Inputs!$B$74</f>
+        <f>Inputs!H129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="I26" s="36">
-        <f>Inputs!I122*Inputs!$B$74</f>
+        <f>Inputs!I129*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="J26" s="38">
@@ -5740,31 +6290,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C87+Inputs!$B$72</f>
+        <f>Inputs!C88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D87+Inputs!$B$72</f>
+        <f>Inputs!D88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E87+Inputs!$B$72</f>
+        <f>Inputs!E88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F87+Inputs!$B$72</f>
+        <f>Inputs!F88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G87+Inputs!$B$72</f>
+        <f>Inputs!G88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H87+Inputs!$B$72</f>
+        <f>Inputs!H88+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I87+Inputs!$B$72</f>
+        <f>Inputs!I88+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -5814,31 +6364,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C93</f>
+        <f>Inputs!C95</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D93</f>
+        <f>Inputs!D95</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E93</f>
+        <f>Inputs!E95</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F93</f>
+        <f>Inputs!F95</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G93</f>
+        <f>Inputs!G95</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H93</f>
+        <f>Inputs!H95</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I93</f>
+        <f>Inputs!I95</f>
         <v/>
       </c>
     </row>
@@ -5853,31 +6403,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C99*Inputs!$B$73</f>
+        <f>Inputs!C102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D99*Inputs!$B$73</f>
+        <f>Inputs!D102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E99*Inputs!$B$73</f>
+        <f>Inputs!E102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F99*Inputs!$B$73</f>
+        <f>Inputs!F102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G99*Inputs!$B$73</f>
+        <f>Inputs!G102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H99*Inputs!$B$73</f>
+        <f>Inputs!H102*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I99*Inputs!$B$73</f>
+        <f>Inputs!I102*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -5969,31 +6519,31 @@
         <v>1</v>
       </c>
       <c r="C12" s="27">
-        <f>MAX(0,B12*(1+Inputs!C117+Inputs!$B$75))</f>
+        <f>MAX(0,B12*(1+Inputs!C123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D12" s="27">
-        <f>MAX(0,C12*(1+Inputs!D117+Inputs!$B$75))</f>
+        <f>MAX(0,C12*(1+Inputs!D123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>MAX(0,D12*(1+Inputs!E117+Inputs!$B$75))</f>
+        <f>MAX(0,D12*(1+Inputs!E123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>MAX(0,E12*(1+Inputs!F117+Inputs!$B$75))</f>
+        <f>MAX(0,E12*(1+Inputs!F123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G12" s="27">
-        <f>MAX(0,F12*(1+Inputs!G117+Inputs!$B$75))</f>
+        <f>MAX(0,F12*(1+Inputs!G123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H12" s="27">
-        <f>MAX(0,G12*(1+Inputs!H117+Inputs!$B$75))</f>
+        <f>MAX(0,G12*(1+Inputs!H123+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I12" s="27">
-        <f>MAX(0,H12*(1+Inputs!I117+Inputs!$B$75))</f>
+        <f>MAX(0,H12*(1+Inputs!I123+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -6125,31 +6675,31 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>Inputs!C105+Inputs!$B$71</f>
+        <f>Inputs!C109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D16" s="32">
-        <f>Inputs!D105+Inputs!$B$71</f>
+        <f>Inputs!D109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>Inputs!E105+Inputs!$B$71</f>
+        <f>Inputs!E109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F16" s="32">
-        <f>Inputs!F105+Inputs!$B$71</f>
+        <f>Inputs!F109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>Inputs!G105+Inputs!$B$71</f>
+        <f>Inputs!G109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>Inputs!H105+Inputs!$B$71</f>
+        <f>Inputs!H109+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>Inputs!I105+Inputs!$B$71</f>
+        <f>Inputs!I109+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -6203,31 +6753,31 @@
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C111)</f>
+        <f>B18*(1+Inputs!C116)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D111)</f>
+        <f>C18*(1+Inputs!D116)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E111)</f>
+        <f>D18*(1+Inputs!E116)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F111)</f>
+        <f>E18*(1+Inputs!F116)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G111)</f>
+        <f>F18*(1+Inputs!G116)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H111)</f>
+        <f>G18*(1+Inputs!H116)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I111)</f>
+        <f>H18*(1+Inputs!I116)</f>
         <v/>
       </c>
     </row>
@@ -6321,31 +6871,31 @@
         <v/>
       </c>
       <c r="C21" s="38">
-        <f>B21*(1+Inputs!C111)</f>
+        <f>B21*(1+Inputs!C116)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>C21*(1+Inputs!D111)</f>
+        <f>C21*(1+Inputs!D116)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>D21*(1+Inputs!E111)</f>
+        <f>D21*(1+Inputs!E116)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>E21*(1+Inputs!F111)</f>
+        <f>E21*(1+Inputs!F116)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>F21*(1+Inputs!G111)</f>
+        <f>F21*(1+Inputs!G116)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>G21*(1+Inputs!H111)</f>
+        <f>G21*(1+Inputs!H116)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>H21*(1+Inputs!I111)</f>
+        <f>H21*(1+Inputs!I116)</f>
         <v/>
       </c>
     </row>
@@ -6512,31 +7062,31 @@
         <v/>
       </c>
       <c r="C26" s="36">
-        <f>Inputs!C123*Inputs!$B$74</f>
+        <f>Inputs!C130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="D26" s="36">
-        <f>Inputs!D123*Inputs!$B$74</f>
+        <f>Inputs!D130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="E26" s="36">
-        <f>Inputs!E123*Inputs!$B$74</f>
+        <f>Inputs!E130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="F26" s="36">
-        <f>Inputs!F123*Inputs!$B$74</f>
+        <f>Inputs!F130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="G26" s="36">
-        <f>Inputs!G123*Inputs!$B$74</f>
+        <f>Inputs!G130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="H26" s="36">
-        <f>Inputs!H123*Inputs!$B$74</f>
+        <f>Inputs!H130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="I26" s="36">
-        <f>Inputs!I123*Inputs!$B$74</f>
+        <f>Inputs!I130*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="J26" s="38">
@@ -7102,31 +7652,31 @@
         </is>
       </c>
       <c r="C6" s="32">
-        <f>Inputs!C88+Inputs!$B$72</f>
+        <f>Inputs!C89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="32">
-        <f>Inputs!D88+Inputs!$B$72</f>
+        <f>Inputs!D89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="32">
-        <f>Inputs!E88+Inputs!$B$72</f>
+        <f>Inputs!E89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="32">
-        <f>Inputs!F88+Inputs!$B$72</f>
+        <f>Inputs!F89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="32">
-        <f>Inputs!G88+Inputs!$B$72</f>
+        <f>Inputs!G89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="32">
-        <f>Inputs!H88+Inputs!$B$72</f>
+        <f>Inputs!H89+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="32">
-        <f>Inputs!I88+Inputs!$B$72</f>
+        <f>Inputs!I89+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -7176,31 +7726,31 @@
         </is>
       </c>
       <c r="C8" s="32">
-        <f>Inputs!C94</f>
+        <f>Inputs!C96</f>
         <v/>
       </c>
       <c r="D8" s="32">
-        <f>Inputs!D94</f>
+        <f>Inputs!D96</f>
         <v/>
       </c>
       <c r="E8" s="32">
-        <f>Inputs!E94</f>
+        <f>Inputs!E96</f>
         <v/>
       </c>
       <c r="F8" s="32">
-        <f>Inputs!F94</f>
+        <f>Inputs!F96</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Inputs!G94</f>
+        <f>Inputs!G96</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Inputs!H94</f>
+        <f>Inputs!H96</f>
         <v/>
       </c>
       <c r="I8" s="32">
-        <f>Inputs!I94</f>
+        <f>Inputs!I96</f>
         <v/>
       </c>
     </row>
@@ -7215,31 +7765,31 @@
         <v/>
       </c>
       <c r="C9" s="36">
-        <f>Inputs!C100*Inputs!$B$73</f>
+        <f>Inputs!C103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="36">
-        <f>Inputs!D100*Inputs!$B$73</f>
+        <f>Inputs!D103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="36">
-        <f>Inputs!E100*Inputs!$B$73</f>
+        <f>Inputs!E103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="36">
-        <f>Inputs!F100*Inputs!$B$73</f>
+        <f>Inputs!F103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>Inputs!G100*Inputs!$B$73</f>
+        <f>Inputs!G103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="36">
-        <f>Inputs!H100*Inputs!$B$73</f>
+        <f>Inputs!H103*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="36">
-        <f>Inputs!I100*Inputs!$B$73</f>
+        <f>Inputs!I103*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -7331,31 +7881,31 @@
         <v>1</v>
       </c>
       <c r="C12" s="27">
-        <f>MAX(0,B12*(1+Inputs!C118+Inputs!$B$75))</f>
+        <f>MAX(0,B12*(1+Inputs!C124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D12" s="27">
-        <f>MAX(0,C12*(1+Inputs!D118+Inputs!$B$75))</f>
+        <f>MAX(0,C12*(1+Inputs!D124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E12" s="27">
-        <f>MAX(0,D12*(1+Inputs!E118+Inputs!$B$75))</f>
+        <f>MAX(0,D12*(1+Inputs!E124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F12" s="27">
-        <f>MAX(0,E12*(1+Inputs!F118+Inputs!$B$75))</f>
+        <f>MAX(0,E12*(1+Inputs!F124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G12" s="27">
-        <f>MAX(0,F12*(1+Inputs!G118+Inputs!$B$75))</f>
+        <f>MAX(0,F12*(1+Inputs!G124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H12" s="27">
-        <f>MAX(0,G12*(1+Inputs!H118+Inputs!$B$75))</f>
+        <f>MAX(0,G12*(1+Inputs!H124+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I12" s="27">
-        <f>MAX(0,H12*(1+Inputs!I118+Inputs!$B$75))</f>
+        <f>MAX(0,H12*(1+Inputs!I124+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -7487,31 +8037,31 @@
         <v/>
       </c>
       <c r="C16" s="32">
-        <f>Inputs!C106+Inputs!$B$71</f>
+        <f>Inputs!C110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D16" s="32">
-        <f>Inputs!D106+Inputs!$B$71</f>
+        <f>Inputs!D110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E16" s="32">
-        <f>Inputs!E106+Inputs!$B$71</f>
+        <f>Inputs!E110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F16" s="32">
-        <f>Inputs!F106+Inputs!$B$71</f>
+        <f>Inputs!F110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G16" s="32">
-        <f>Inputs!G106+Inputs!$B$71</f>
+        <f>Inputs!G110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H16" s="32">
-        <f>Inputs!H106+Inputs!$B$71</f>
+        <f>Inputs!H110+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I16" s="32">
-        <f>Inputs!I106+Inputs!$B$71</f>
+        <f>Inputs!I110+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -7565,31 +8115,31 @@
         <v/>
       </c>
       <c r="C18" s="38">
-        <f>B18*(1+Inputs!C112)</f>
+        <f>B18*(1+Inputs!C117)</f>
         <v/>
       </c>
       <c r="D18" s="38">
-        <f>C18*(1+Inputs!D112)</f>
+        <f>C18*(1+Inputs!D117)</f>
         <v/>
       </c>
       <c r="E18" s="38">
-        <f>D18*(1+Inputs!E112)</f>
+        <f>D18*(1+Inputs!E117)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>E18*(1+Inputs!F112)</f>
+        <f>E18*(1+Inputs!F117)</f>
         <v/>
       </c>
       <c r="G18" s="38">
-        <f>F18*(1+Inputs!G112)</f>
+        <f>F18*(1+Inputs!G117)</f>
         <v/>
       </c>
       <c r="H18" s="38">
-        <f>G18*(1+Inputs!H112)</f>
+        <f>G18*(1+Inputs!H117)</f>
         <v/>
       </c>
       <c r="I18" s="38">
-        <f>H18*(1+Inputs!I112)</f>
+        <f>H18*(1+Inputs!I117)</f>
         <v/>
       </c>
     </row>
@@ -7683,31 +8233,31 @@
         <v/>
       </c>
       <c r="C21" s="38">
-        <f>B21*(1+Inputs!C112)</f>
+        <f>B21*(1+Inputs!C117)</f>
         <v/>
       </c>
       <c r="D21" s="38">
-        <f>C21*(1+Inputs!D112)</f>
+        <f>C21*(1+Inputs!D117)</f>
         <v/>
       </c>
       <c r="E21" s="38">
-        <f>D21*(1+Inputs!E112)</f>
+        <f>D21*(1+Inputs!E117)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>E21*(1+Inputs!F112)</f>
+        <f>E21*(1+Inputs!F117)</f>
         <v/>
       </c>
       <c r="G21" s="38">
-        <f>F21*(1+Inputs!G112)</f>
+        <f>F21*(1+Inputs!G117)</f>
         <v/>
       </c>
       <c r="H21" s="38">
-        <f>G21*(1+Inputs!H112)</f>
+        <f>G21*(1+Inputs!H117)</f>
         <v/>
       </c>
       <c r="I21" s="38">
-        <f>H21*(1+Inputs!I112)</f>
+        <f>H21*(1+Inputs!I117)</f>
         <v/>
       </c>
     </row>
@@ -7874,31 +8424,1361 @@
         <v/>
       </c>
       <c r="C26" s="36">
-        <f>Inputs!C124*Inputs!$B$74</f>
+        <f>Inputs!C131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="D26" s="36">
-        <f>Inputs!D124*Inputs!$B$74</f>
+        <f>Inputs!D131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="E26" s="36">
-        <f>Inputs!E124*Inputs!$B$74</f>
+        <f>Inputs!E131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="F26" s="36">
-        <f>Inputs!F124*Inputs!$B$74</f>
+        <f>Inputs!F131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="G26" s="36">
-        <f>Inputs!G124*Inputs!$B$74</f>
+        <f>Inputs!G131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="H26" s="36">
-        <f>Inputs!H124*Inputs!$B$74</f>
+        <f>Inputs!H131*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="I26" s="36">
-        <f>Inputs!I124*Inputs!$B$74</f>
+        <f>Inputs!I131*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="J26" s="38">
+        <f>J25*Inputs!$B$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Change in net working capital</t>
+        </is>
+      </c>
+      <c r="C27" s="38">
+        <f>Inputs!$B$65*(C14-B14)</f>
+        <v/>
+      </c>
+      <c r="D27" s="38">
+        <f>Inputs!$B$65*(D14-C14)</f>
+        <v/>
+      </c>
+      <c r="E27" s="38">
+        <f>Inputs!$B$65*(E14-D14)</f>
+        <v/>
+      </c>
+      <c r="F27" s="38">
+        <f>Inputs!$B$65*(F14-E14)</f>
+        <v/>
+      </c>
+      <c r="G27" s="38">
+        <f>Inputs!$B$65*(G14-F14)</f>
+        <v/>
+      </c>
+      <c r="H27" s="38">
+        <f>Inputs!$B$65*(H14-G14)</f>
+        <v/>
+      </c>
+      <c r="I27" s="38">
+        <f>Inputs!$B$65*(I14-H14)</f>
+        <v/>
+      </c>
+      <c r="J27" s="38">
+        <f>Inputs!$B$65*(J14-I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n"/>
+      <c r="C28" s="54">
+        <f>C24+C25-C26-C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="54">
+        <f>D24+D25-D26-D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="54">
+        <f>E24+E25-E26-E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="54">
+        <f>F24+F25-F26-F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="54">
+        <f>G24+G25-G26-G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="54">
+        <f>H24+H25-H26-H27</f>
+        <v/>
+      </c>
+      <c r="I28" s="54">
+        <f>I24+I25-I26-I27</f>
+        <v/>
+      </c>
+      <c r="J28" s="54">
+        <f>J24+J25-J26-J27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF margin</t>
+        </is>
+      </c>
+      <c r="C29" s="39">
+        <f>IF(C14=0,0,C28/C14)</f>
+        <v/>
+      </c>
+      <c r="D29" s="39">
+        <f>IF(D14=0,0,D28/D14)</f>
+        <v/>
+      </c>
+      <c r="E29" s="39">
+        <f>IF(E14=0,0,E28/E14)</f>
+        <v/>
+      </c>
+      <c r="F29" s="39">
+        <f>IF(F14=0,0,F28/F14)</f>
+        <v/>
+      </c>
+      <c r="G29" s="39">
+        <f>IF(G14=0,0,G28/G14)</f>
+        <v/>
+      </c>
+      <c r="H29" s="39">
+        <f>IF(H14=0,0,H28/H14)</f>
+        <v/>
+      </c>
+      <c r="I29" s="39">
+        <f>IF(I14=0,0,I28/I14)</f>
+        <v/>
+      </c>
+      <c r="J29" s="39">
+        <f>IF(J14=0,0,J28/J14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="C30" s="31">
+        <f>1/(1+Inputs!$B$62)^C4</f>
+        <v/>
+      </c>
+      <c r="D30" s="31">
+        <f>1/(1+Inputs!$B$62)^D4</f>
+        <v/>
+      </c>
+      <c r="E30" s="31">
+        <f>1/(1+Inputs!$B$62)^E4</f>
+        <v/>
+      </c>
+      <c r="F30" s="31">
+        <f>1/(1+Inputs!$B$62)^F4</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>1/(1+Inputs!$B$62)^G4</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>1/(1+Inputs!$B$62)^H4</f>
+        <v/>
+      </c>
+      <c r="I30" s="31">
+        <f>1/(1+Inputs!$B$62)^I4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C31" s="38">
+        <f>C28*C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="38">
+        <f>D28*D30</f>
+        <v/>
+      </c>
+      <c r="E31" s="38">
+        <f>E28*E30</f>
+        <v/>
+      </c>
+      <c r="F31" s="38">
+        <f>F28*F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="38">
+        <f>G28*G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="38">
+        <f>H28*H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="38">
+        <f>I28*I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION (value per share floored at $0: equity has limited liability)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Sum of PV of explicit FCF (2027-2033)</t>
+        </is>
+      </c>
+      <c r="B34" s="38">
+        <f>SUM(C31:I31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value at end-2033</t>
+        </is>
+      </c>
+      <c r="B35" s="38">
+        <f>IF(Inputs!$B$62&lt;=Inputs!$B$63,0,J28/(Inputs!$B$62-Inputs!$B$63))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B36" s="38">
+        <f>B35*I30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B37" s="38">
+        <f>B34+B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>+ Net cash (incl. Aug-26 raise)</t>
+        </is>
+      </c>
+      <c r="B38" s="36">
+        <f>Inputs!$B$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>+ Altera stake</t>
+        </is>
+      </c>
+      <c r="B39" s="36">
+        <f>Inputs!$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>- Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B40" s="36">
+        <f>-Inputs!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B41" s="38">
+        <f>B37+B38+B39+B40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B42" s="37">
+        <f>Inputs!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Value per share ($)</t>
+        </is>
+      </c>
+      <c r="B43" s="34">
+        <f>IF(B42=0,0,MAX(0,B41/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B44" s="33">
+        <f>Inputs!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs price</t>
+        </is>
+      </c>
+      <c r="B45" s="39">
+        <f>IF(B44=0,0,B43/B44-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B46" s="39">
+        <f>IF(B37=0,0,B36/B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B47" s="11">
+        <f>IF(C24&lt;=0,0,B43/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Market P/E on 2027 NOPAT/share</t>
+        </is>
+      </c>
+      <c r="B48" s="11">
+        <f>IF(C24&lt;=0,0,B44/(C24/B42))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Taiwan scenario: US$ bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Discount period (yrs from 30 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="C4" s="27">
+        <f>Inputs!$B$67+1</f>
+        <v/>
+      </c>
+      <c r="D4" s="27">
+        <f>Inputs!$B$67+2</f>
+        <v/>
+      </c>
+      <c r="E4" s="27">
+        <f>Inputs!$B$67+3</f>
+        <v/>
+      </c>
+      <c r="F4" s="27">
+        <f>Inputs!$B$67+4</f>
+        <v/>
+      </c>
+      <c r="G4" s="27">
+        <f>Inputs!$B$67+5</f>
+        <v/>
+      </c>
+      <c r="H4" s="27">
+        <f>Inputs!$B$67+6</f>
+        <v/>
+      </c>
+      <c r="I4" s="27">
+        <f>Inputs!$B$67+7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DCAI (server/data center) revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="36">
+        <f>Inputs!$B$38</f>
+        <v/>
+      </c>
+      <c r="C5" s="38">
+        <f>B5*(1+C6)</f>
+        <v/>
+      </c>
+      <c r="D5" s="38">
+        <f>C5*(1+D6)</f>
+        <v/>
+      </c>
+      <c r="E5" s="38">
+        <f>D5*(1+E6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="38">
+        <f>E5*(1+F6)</f>
+        <v/>
+      </c>
+      <c r="G5" s="38">
+        <f>F5*(1+G6)</f>
+        <v/>
+      </c>
+      <c r="H5" s="38">
+        <f>G5*(1+H6)</f>
+        <v/>
+      </c>
+      <c r="I5" s="38">
+        <f>H5*(1+I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C6" s="32">
+        <f>Inputs!C90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="D6" s="32">
+        <f>Inputs!D90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="E6" s="32">
+        <f>Inputs!E90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="F6" s="32">
+        <f>Inputs!F90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="G6" s="32">
+        <f>Inputs!G90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="H6" s="32">
+        <f>Inputs!H90+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="I6" s="32">
+        <f>Inputs!I90+Inputs!$B$72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CCPG (client) revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="36">
+        <f>Inputs!$B$39</f>
+        <v/>
+      </c>
+      <c r="C7" s="38">
+        <f>B7*(1+C8)</f>
+        <v/>
+      </c>
+      <c r="D7" s="38">
+        <f>C7*(1+D8)</f>
+        <v/>
+      </c>
+      <c r="E7" s="38">
+        <f>D7*(1+E8)</f>
+        <v/>
+      </c>
+      <c r="F7" s="38">
+        <f>E7*(1+F8)</f>
+        <v/>
+      </c>
+      <c r="G7" s="38">
+        <f>F7*(1+G8)</f>
+        <v/>
+      </c>
+      <c r="H7" s="38">
+        <f>G7*(1+H8)</f>
+        <v/>
+      </c>
+      <c r="I7" s="38">
+        <f>H7*(1+I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C8" s="32">
+        <f>Inputs!C97</f>
+        <v/>
+      </c>
+      <c r="D8" s="32">
+        <f>Inputs!D97</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>Inputs!E97</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>Inputs!F97</f>
+        <v/>
+      </c>
+      <c r="G8" s="32">
+        <f>Inputs!G97</f>
+        <v/>
+      </c>
+      <c r="H8" s="32">
+        <f>Inputs!H97</f>
+        <v/>
+      </c>
+      <c r="I8" s="32">
+        <f>Inputs!I97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>External foundry + packaging revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="36">
+        <f>Inputs!$B$40</f>
+        <v/>
+      </c>
+      <c r="C9" s="36">
+        <f>Inputs!C104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="D9" s="36">
+        <f>Inputs!D104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="E9" s="36">
+        <f>Inputs!E104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="F9" s="36">
+        <f>Inputs!F104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="G9" s="36">
+        <f>Inputs!G104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="H9" s="36">
+        <f>Inputs!H104*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="I9" s="36">
+        <f>Inputs!I104*Inputs!$B$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Other revenue (Mobileye etc.)</t>
+        </is>
+      </c>
+      <c r="B10" s="36">
+        <f>Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="C10" s="38">
+        <f>B10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="D10" s="38">
+        <f>C10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="E10" s="38">
+        <f>D10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="F10" s="38">
+        <f>E10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="G10" s="38">
+        <f>F10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="H10" s="38">
+        <f>G10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="I10" s="38">
+        <f>H10*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>China domestic-demand revenue exposed (pre-erosion)</t>
+        </is>
+      </c>
+      <c r="B11" s="38">
+        <f>(B5+B7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="C11" s="38">
+        <f>(C5+C7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D11" s="38">
+        <f>(D5+D7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="E11" s="38">
+        <f>(E5+E7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="F11" s="38">
+        <f>(F5+F7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G11" s="38">
+        <f>(G5+G7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="H11" s="38">
+        <f>(H5+H7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="I11" s="38">
+        <f>(I5+I7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China erosion index (2026 = 1.00)</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="27">
+        <f>MAX(0,B12*(1+Inputs!C125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>MAX(0,C12*(1+Inputs!D125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="E12" s="27">
+        <f>MAX(0,D12*(1+Inputs!E125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="F12" s="27">
+        <f>MAX(0,E12*(1+Inputs!F125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="G12" s="27">
+        <f>MAX(0,F12*(1+Inputs!G125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="H12" s="27">
+        <f>MAX(0,G12*(1+Inputs!H125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="I12" s="27">
+        <f>MAX(0,H12*(1+Inputs!I125+Inputs!$B$75))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Less: China localization / trade revenue loss</t>
+        </is>
+      </c>
+      <c r="B13" s="38">
+        <f>-B11*(1-B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="38">
+        <f>-C11*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="38">
+        <f>-D11*(1-D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="38">
+        <f>-E11*(1-E12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="38">
+        <f>-F11*(1-F12)</f>
+        <v/>
+      </c>
+      <c r="G13" s="38">
+        <f>-G11*(1-G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="38">
+        <f>-H11*(1-H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="38">
+        <f>-I11*(1-I12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="54">
+        <f>SUM(B5,B7,B9,B10,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="54">
+        <f>SUM(C5,C7,C9,C10,C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="54">
+        <f>SUM(D5,D7,D9,D10,D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>SUM(E5,E7,E9,E10,E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="54">
+        <f>SUM(F5,F7,F9,F10,F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="54">
+        <f>SUM(G5,G7,G9,G10,G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="54">
+        <f>SUM(H5,H7,H9,H10,H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="54">
+        <f>SUM(I5,I7,I9,I10,I13)</f>
+        <v/>
+      </c>
+      <c r="J14" s="54">
+        <f>I14*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C15" s="39">
+        <f>IF(B14=0,0,C14/B14-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="39">
+        <f>IF(C14=0,0,D14/C14-1)</f>
+        <v/>
+      </c>
+      <c r="E15" s="39">
+        <f>IF(D14=0,0,E14/D14-1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="39">
+        <f>IF(E14=0,0,F14/E14-1)</f>
+        <v/>
+      </c>
+      <c r="G15" s="39">
+        <f>IF(F14=0,0,G14/F14-1)</f>
+        <v/>
+      </c>
+      <c r="H15" s="39">
+        <f>IF(G14=0,0,H14/G14-1)</f>
+        <v/>
+      </c>
+      <c r="I15" s="39">
+        <f>IF(H14=0,0,I14/H14-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B16" s="32">
+        <f>Inputs!$B$32+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="C16" s="32">
+        <f>Inputs!C111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>Inputs!D111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>Inputs!E111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>Inputs!F111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>Inputs!G111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>Inputs!H111+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>Inputs!I111+Inputs!$B$71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B17" s="38">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="38">
+        <f>C14*C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="38">
+        <f>D14*D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="38">
+        <f>E14*E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="38">
+        <f>F14*F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="38">
+        <f>G14*G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="38">
+        <f>H14*H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="38">
+        <f>I14*I16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP opex</t>
+        </is>
+      </c>
+      <c r="B18" s="36">
+        <f>Inputs!$B$33</f>
+        <v/>
+      </c>
+      <c r="C18" s="38">
+        <f>B18*(1+Inputs!C118)</f>
+        <v/>
+      </c>
+      <c r="D18" s="38">
+        <f>C18*(1+Inputs!D118)</f>
+        <v/>
+      </c>
+      <c r="E18" s="38">
+        <f>D18*(1+Inputs!E118)</f>
+        <v/>
+      </c>
+      <c r="F18" s="38">
+        <f>E18*(1+Inputs!F118)</f>
+        <v/>
+      </c>
+      <c r="G18" s="38">
+        <f>F18*(1+Inputs!G118)</f>
+        <v/>
+      </c>
+      <c r="H18" s="38">
+        <f>G18*(1+Inputs!H118)</f>
+        <v/>
+      </c>
+      <c r="I18" s="38">
+        <f>H18*(1+Inputs!I118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>Non-GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B19" s="54">
+        <f>B17-B18</f>
+        <v/>
+      </c>
+      <c r="C19" s="54">
+        <f>C17-C18</f>
+        <v/>
+      </c>
+      <c r="D19" s="54">
+        <f>D17-D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>E17-E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="54">
+        <f>F17-F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="54">
+        <f>G17-G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="54">
+        <f>H17-H18</f>
+        <v/>
+      </c>
+      <c r="I19" s="54">
+        <f>I17-I18</f>
+        <v/>
+      </c>
+      <c r="J19" s="30" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  operating margin</t>
+        </is>
+      </c>
+      <c r="B20" s="39">
+        <f>IF(B14=0,0,B19/B14)</f>
+        <v/>
+      </c>
+      <c r="C20" s="39">
+        <f>IF(C14=0,0,C19/C14)</f>
+        <v/>
+      </c>
+      <c r="D20" s="39">
+        <f>IF(D14=0,0,D19/D14)</f>
+        <v/>
+      </c>
+      <c r="E20" s="39">
+        <f>IF(E14=0,0,E19/E14)</f>
+        <v/>
+      </c>
+      <c r="F20" s="39">
+        <f>IF(F14=0,0,F19/F14)</f>
+        <v/>
+      </c>
+      <c r="G20" s="39">
+        <f>IF(G14=0,0,G19/G14)</f>
+        <v/>
+      </c>
+      <c r="H20" s="39">
+        <f>IF(H14=0,0,H19/H14)</f>
+        <v/>
+      </c>
+      <c r="I20" s="39">
+        <f>IF(I14=0,0,I19/I14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
+        <f>Inputs!$B$34</f>
+        <v/>
+      </c>
+      <c r="C21" s="38">
+        <f>B21*(1+Inputs!C118)</f>
+        <v/>
+      </c>
+      <c r="D21" s="38">
+        <f>C21*(1+Inputs!D118)</f>
+        <v/>
+      </c>
+      <c r="E21" s="38">
+        <f>D21*(1+Inputs!E118)</f>
+        <v/>
+      </c>
+      <c r="F21" s="38">
+        <f>E21*(1+Inputs!F118)</f>
+        <v/>
+      </c>
+      <c r="G21" s="38">
+        <f>F21*(1+Inputs!G118)</f>
+        <v/>
+      </c>
+      <c r="H21" s="38">
+        <f>G21*(1+Inputs!H118)</f>
+        <v/>
+      </c>
+      <c r="I21" s="38">
+        <f>H21*(1+Inputs!I118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>EBIT after SBC</t>
+        </is>
+      </c>
+      <c r="C22" s="38">
+        <f>C19-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="38">
+        <f>D19-D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="38">
+        <f>E19-E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="38">
+        <f>F19-F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="38">
+        <f>G19-G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="38">
+        <f>H19-H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="38">
+        <f>I19-I21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Taxes on EBIT</t>
+        </is>
+      </c>
+      <c r="C23" s="38">
+        <f>MAX(0,C22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="D23" s="38">
+        <f>MAX(0,D22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="E23" s="38">
+        <f>MAX(0,E22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="F23" s="38">
+        <f>MAX(0,F22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G23" s="38">
+        <f>MAX(0,G22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="H23" s="38">
+        <f>MAX(0,H22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="I23" s="38">
+        <f>MAX(0,I22)*Inputs!$B$60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="C24" s="38">
+        <f>C22-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="38">
+        <f>D22-D23</f>
+        <v/>
+      </c>
+      <c r="E24" s="38">
+        <f>E22-E23</f>
+        <v/>
+      </c>
+      <c r="F24" s="38">
+        <f>F22-F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="38">
+        <f>G22-G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="38">
+        <f>H22-H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="38">
+        <f>I22-I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="38">
+        <f>I24*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B25" s="36">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="C25" s="38">
+        <f>B25+Inputs!$B$66*(B26-B25)</f>
+        <v/>
+      </c>
+      <c r="D25" s="38">
+        <f>C25+Inputs!$B$66*(C26-C25)</f>
+        <v/>
+      </c>
+      <c r="E25" s="38">
+        <f>D25+Inputs!$B$66*(D26-D25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="38">
+        <f>E25+Inputs!$B$66*(E26-E25)</f>
+        <v/>
+      </c>
+      <c r="G25" s="38">
+        <f>F25+Inputs!$B$66*(F26-F25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="38">
+        <f>G25+Inputs!$B$66*(G26-G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>H25+Inputs!$B$66*(H26-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="38">
+        <f>I25*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B26" s="36">
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="C26" s="36">
+        <f>Inputs!C132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="D26" s="36">
+        <f>Inputs!D132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="E26" s="36">
+        <f>Inputs!E132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="F26" s="36">
+        <f>Inputs!F132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="G26" s="36">
+        <f>Inputs!G132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="H26" s="36">
+        <f>Inputs!H132*Inputs!$B$74</f>
+        <v/>
+      </c>
+      <c r="I26" s="36">
+        <f>Inputs!I132*Inputs!$B$74</f>
         <v/>
       </c>
       <c r="J26" s="38">

--- a/research/model/intel_valuation_model.xlsx
+++ b/research/model/intel_valuation_model.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Base" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Bull" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Taiwan" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TaiwanMax" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -531,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -700,119 +701,1526 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
+          <t>- TAIWANMAX scenario (5th): Taiwan fabs destroyed or seized, the US transfers TSMC Arizona to Intel, and TSMC engineers join Intel. On top of Taiwan:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
+          <t xml:space="preserve">  Arizona wafer revenue ramps with its fabs ($8bn 2027 -&gt; $60bn 2033 at crisis pricing; Fab 1 N4 10-30k wafers/mo today, N3 H2-27, N2/A16 next),</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  talent lifts gross margin to 65%, a smaller 2027 client hit (TSMC-made tiles move to Arizona), capex $55-75bn/yr to finish the Arizona fabs.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Payment for the assets is an input (default $0 = government transfer). Caveat: until 2028-29 ALL Arizona chips are packaged in Taiwan, so 2027 output is packaging-bound.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
+          <t>- Margins on a non-GAAP basis, then stock-based comp deducted as a real cost. Unlevered FCF = NOPAT + D&amp;A - capex - change in NWC.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>- Discounted from 30 Sep 2026; Gordon-growth terminal value on normalized 2034 FCF (terminal capex = D&amp;A x ratio).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>HOW SCENARIOS MAP TO THE PRODUCT FINDINGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Bear: AMD Venice + Arm keep taking server share and the shortage-driven ASP spike reverses; client share erosion continues; no 14A anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">      customer, external foundry stays mostly Altera + small packaging deals; 18A cost parity slips; gross margin stays near 2026 levels.</t>
         </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANT CAVEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>- Not investment advice.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TaiwanMax scenario: US$ bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Discount period (yrs from 30 Sep 2026)</t>
+        </is>
+      </c>
+      <c r="C4" s="31">
+        <f>Inputs!$B$67+1</f>
+        <v/>
+      </c>
+      <c r="D4" s="31">
+        <f>Inputs!$B$67+2</f>
+        <v/>
+      </c>
+      <c r="E4" s="31">
+        <f>Inputs!$B$67+3</f>
+        <v/>
+      </c>
+      <c r="F4" s="31">
+        <f>Inputs!$B$67+4</f>
+        <v/>
+      </c>
+      <c r="G4" s="31">
+        <f>Inputs!$B$67+5</f>
+        <v/>
+      </c>
+      <c r="H4" s="31">
+        <f>Inputs!$B$67+6</f>
+        <v/>
+      </c>
+      <c r="I4" s="31">
+        <f>Inputs!$B$67+7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DCAI (server/data center) revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="39">
+        <f>Inputs!$B$38</f>
+        <v/>
+      </c>
+      <c r="C5" s="41">
+        <f>B5*(1+C6)</f>
+        <v/>
+      </c>
+      <c r="D5" s="41">
+        <f>C5*(1+D6)</f>
+        <v/>
+      </c>
+      <c r="E5" s="41">
+        <f>D5*(1+E6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="41">
+        <f>E5*(1+F6)</f>
+        <v/>
+      </c>
+      <c r="G5" s="41">
+        <f>F5*(1+G6)</f>
+        <v/>
+      </c>
+      <c r="H5" s="41">
+        <f>G5*(1+H6)</f>
+        <v/>
+      </c>
+      <c r="I5" s="41">
+        <f>H5*(1+I6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C6" s="35">
+        <f>Inputs!C95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="D6" s="35">
+        <f>Inputs!D95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="E6" s="35">
+        <f>Inputs!E95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="F6" s="35">
+        <f>Inputs!F95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="G6" s="35">
+        <f>Inputs!G95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="H6" s="35">
+        <f>Inputs!H95+Inputs!$B$72</f>
+        <v/>
+      </c>
+      <c r="I6" s="35">
+        <f>Inputs!I95+Inputs!$B$72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CCPG (client) revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="39">
+        <f>Inputs!$B$39</f>
+        <v/>
+      </c>
+      <c r="C7" s="41">
+        <f>B7*(1+C8)</f>
+        <v/>
+      </c>
+      <c r="D7" s="41">
+        <f>C7*(1+D8)</f>
+        <v/>
+      </c>
+      <c r="E7" s="41">
+        <f>D7*(1+E8)</f>
+        <v/>
+      </c>
+      <c r="F7" s="41">
+        <f>E7*(1+F8)</f>
+        <v/>
+      </c>
+      <c r="G7" s="41">
+        <f>F7*(1+G8)</f>
+        <v/>
+      </c>
+      <c r="H7" s="41">
+        <f>G7*(1+H8)</f>
+        <v/>
+      </c>
+      <c r="I7" s="41">
+        <f>H7*(1+I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C8" s="35">
+        <f>Inputs!C103</f>
+        <v/>
+      </c>
+      <c r="D8" s="35">
+        <f>Inputs!D103</f>
+        <v/>
+      </c>
+      <c r="E8" s="35">
+        <f>Inputs!E103</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>Inputs!F103</f>
+        <v/>
+      </c>
+      <c r="G8" s="35">
+        <f>Inputs!G103</f>
+        <v/>
+      </c>
+      <c r="H8" s="35">
+        <f>Inputs!H103</f>
+        <v/>
+      </c>
+      <c r="I8" s="35">
+        <f>Inputs!I103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>External foundry + packaging revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="39">
+        <f>Inputs!$B$40</f>
+        <v/>
+      </c>
+      <c r="C9" s="39">
+        <f>Inputs!C111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
+        <f>Inputs!D111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>Inputs!E111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="F9" s="39">
+        <f>Inputs!F111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="G9" s="39">
+        <f>Inputs!G111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="H9" s="39">
+        <f>Inputs!H111*Inputs!$B$73</f>
+        <v/>
+      </c>
+      <c r="I9" s="39">
+        <f>Inputs!I111*Inputs!$B$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>China tailwind: US onshoring / tariff-driven foundry revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="39">
+        <f>Inputs!$B$78*Inputs!C151</f>
+        <v/>
+      </c>
+      <c r="D10" s="39">
+        <f>Inputs!$B$78*Inputs!D151</f>
+        <v/>
+      </c>
+      <c r="E10" s="39">
+        <f>Inputs!$B$78*Inputs!E151</f>
+        <v/>
+      </c>
+      <c r="F10" s="39">
+        <f>Inputs!$B$78*Inputs!F151</f>
+        <v/>
+      </c>
+      <c r="G10" s="39">
+        <f>Inputs!$B$78*Inputs!G151</f>
+        <v/>
+      </c>
+      <c r="H10" s="39">
+        <f>Inputs!$B$78*Inputs!H151</f>
+        <v/>
+      </c>
+      <c r="I10" s="39">
+        <f>Inputs!$B$78*Inputs!I151</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Other revenue (Mobileye etc.)</t>
+        </is>
+      </c>
+      <c r="B11" s="39">
+        <f>Inputs!$B$41</f>
+        <v/>
+      </c>
+      <c r="C11" s="41">
+        <f>B11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="D11" s="41">
+        <f>C11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="E11" s="41">
+        <f>D11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="F11" s="41">
+        <f>E11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="G11" s="41">
+        <f>F11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="H11" s="41">
+        <f>G11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+      <c r="I11" s="41">
+        <f>H11*(1+Inputs!$B$68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>China domestic-demand revenue exposed (pre-erosion)</t>
+        </is>
+      </c>
+      <c r="B12" s="41">
+        <f>(B5+B7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="C12" s="41">
+        <f>(C5+C7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="D12" s="41">
+        <f>(D5+D7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="E12" s="41">
+        <f>(E5+E7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="F12" s="41">
+        <f>(F5+F7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="G12" s="41">
+        <f>(G5+G7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="H12" s="41">
+        <f>(H5+H7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+      <c r="I12" s="41">
+        <f>(I5+I7)*Inputs!$B$49*Inputs!$B$50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China erosion index (2026 = 1.00)</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="31">
+        <f>MAX(0,B13*(1+Inputs!C135+Inputs!$B$78*Inputs!C143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="D13" s="31">
+        <f>MAX(0,C13*(1+Inputs!D135+Inputs!$B$78*Inputs!D143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="E13" s="31">
+        <f>MAX(0,D13*(1+Inputs!E135+Inputs!$B$78*Inputs!E143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="F13" s="31">
+        <f>MAX(0,E13*(1+Inputs!F135+Inputs!$B$78*Inputs!F143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="G13" s="31">
+        <f>MAX(0,F13*(1+Inputs!G135+Inputs!$B$78*Inputs!G143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="H13" s="31">
+        <f>MAX(0,G13*(1+Inputs!H135+Inputs!$B$78*Inputs!H143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+      <c r="I13" s="31">
+        <f>MAX(0,H13*(1+Inputs!I135+Inputs!$B$78*Inputs!I143+Inputs!$B$75))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>China domestic revenue change vs 2026 (loss negative, tailwind gain positive)</t>
+        </is>
+      </c>
+      <c r="B14" s="41">
+        <f>-B12*(1-B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="41">
+        <f>-C12*(1-C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="41">
+        <f>-D12*(1-D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="41">
+        <f>-E12*(1-E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="41">
+        <f>-F12*(1-F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="41">
+        <f>-G12*(1-G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="41">
+        <f>-H12*(1-H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="41">
+        <f>-I12*(1-I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B15" s="58">
+        <f>SUM(B5,B7,B9,B10,B11,B14)</f>
+        <v/>
+      </c>
+      <c r="C15" s="58">
+        <f>SUM(C5,C7,C9,C10,C11,C14)</f>
+        <v/>
+      </c>
+      <c r="D15" s="58">
+        <f>SUM(D5,D7,D9,D10,D11,D14)</f>
+        <v/>
+      </c>
+      <c r="E15" s="58">
+        <f>SUM(E5,E7,E9,E10,E11,E14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="58">
+        <f>SUM(F5,F7,F9,F10,F11,F14)</f>
+        <v/>
+      </c>
+      <c r="G15" s="58">
+        <f>SUM(G5,G7,G9,G10,G11,G14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="58">
+        <f>SUM(H5,H7,H9,H10,H11,H14)</f>
+        <v/>
+      </c>
+      <c r="I15" s="58">
+        <f>SUM(I5,I7,I9,I10,I11,I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="58">
+        <f>I15*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  growth</t>
+        </is>
+      </c>
+      <c r="C16" s="42">
+        <f>IF(B15=0,0,C15/B15-1)</f>
+        <v/>
+      </c>
+      <c r="D16" s="42">
+        <f>IF(C15=0,0,D15/C15-1)</f>
+        <v/>
+      </c>
+      <c r="E16" s="42">
+        <f>IF(D15=0,0,E15/D15-1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="42">
+        <f>IF(E15=0,0,F15/E15-1)</f>
+        <v/>
+      </c>
+      <c r="G16" s="42">
+        <f>IF(F15=0,0,G15/F15-1)</f>
+        <v/>
+      </c>
+      <c r="H16" s="42">
+        <f>IF(G15=0,0,H15/G15-1)</f>
+        <v/>
+      </c>
+      <c r="I16" s="42">
+        <f>IF(H15=0,0,I15/H15-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>Inputs!$B$32+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>Inputs!C119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>Inputs!D119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>Inputs!E119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>Inputs!F119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="G17" s="35">
+        <f>Inputs!G119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="H17" s="35">
+        <f>Inputs!H119+Inputs!$B$71</f>
+        <v/>
+      </c>
+      <c r="I17" s="35">
+        <f>Inputs!I119+Inputs!$B$71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B18" s="41">
+        <f>B15*B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="41">
+        <f>C15*C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="41">
+        <f>D15*D17</f>
+        <v/>
+      </c>
+      <c r="E18" s="41">
+        <f>E15*E17</f>
+        <v/>
+      </c>
+      <c r="F18" s="41">
+        <f>F15*F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="41">
+        <f>G15*G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="41">
+        <f>H15*H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="41">
+        <f>I15*I17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Non-GAAP opex</t>
+        </is>
+      </c>
+      <c r="B19" s="39">
+        <f>Inputs!$B$33</f>
+        <v/>
+      </c>
+      <c r="C19" s="41">
+        <f>B19*(1+Inputs!C127)</f>
+        <v/>
+      </c>
+      <c r="D19" s="41">
+        <f>C19*(1+Inputs!D127)</f>
+        <v/>
+      </c>
+      <c r="E19" s="41">
+        <f>D19*(1+Inputs!E127)</f>
+        <v/>
+      </c>
+      <c r="F19" s="41">
+        <f>E19*(1+Inputs!F127)</f>
+        <v/>
+      </c>
+      <c r="G19" s="41">
+        <f>F19*(1+Inputs!G127)</f>
+        <v/>
+      </c>
+      <c r="H19" s="41">
+        <f>G19*(1+Inputs!H127)</f>
+        <v/>
+      </c>
+      <c r="I19" s="41">
+        <f>H19*(1+Inputs!I127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Non-GAAP operating income</t>
+        </is>
+      </c>
+      <c r="B20" s="58">
+        <f>B18-B19</f>
+        <v/>
+      </c>
+      <c r="C20" s="58">
+        <f>C18-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="58">
+        <f>D18-D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="58">
+        <f>E18-E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="58">
+        <f>F18-F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="58">
+        <f>G18-G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="58">
+        <f>H18-H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="58">
+        <f>I18-I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="34" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  operating margin</t>
+        </is>
+      </c>
+      <c r="B21" s="42">
+        <f>IF(B15=0,0,B20/B15)</f>
+        <v/>
+      </c>
+      <c r="C21" s="42">
+        <f>IF(C15=0,0,C20/C15)</f>
+        <v/>
+      </c>
+      <c r="D21" s="42">
+        <f>IF(D15=0,0,D20/D15)</f>
+        <v/>
+      </c>
+      <c r="E21" s="42">
+        <f>IF(E15=0,0,E20/E15)</f>
+        <v/>
+      </c>
+      <c r="F21" s="42">
+        <f>IF(F15=0,0,F20/F15)</f>
+        <v/>
+      </c>
+      <c r="G21" s="42">
+        <f>IF(G15=0,0,G20/G15)</f>
+        <v/>
+      </c>
+      <c r="H21" s="42">
+        <f>IF(H15=0,0,H20/H15)</f>
+        <v/>
+      </c>
+      <c r="I21" s="42">
+        <f>IF(I15=0,0,I20/I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="B22" s="39">
+        <f>Inputs!$B$34</f>
+        <v/>
+      </c>
+      <c r="C22" s="41">
+        <f>B22*(1+Inputs!C127)</f>
+        <v/>
+      </c>
+      <c r="D22" s="41">
+        <f>C22*(1+Inputs!D127)</f>
+        <v/>
+      </c>
+      <c r="E22" s="41">
+        <f>D22*(1+Inputs!E127)</f>
+        <v/>
+      </c>
+      <c r="F22" s="41">
+        <f>E22*(1+Inputs!F127)</f>
+        <v/>
+      </c>
+      <c r="G22" s="41">
+        <f>F22*(1+Inputs!G127)</f>
+        <v/>
+      </c>
+      <c r="H22" s="41">
+        <f>G22*(1+Inputs!H127)</f>
+        <v/>
+      </c>
+      <c r="I22" s="41">
+        <f>H22*(1+Inputs!I127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>EBIT after SBC</t>
+        </is>
+      </c>
+      <c r="C23" s="41">
+        <f>C20-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="41">
+        <f>D20-D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="41">
+        <f>E20-E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="41">
+        <f>F20-F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="41">
+        <f>G20-G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="41">
+        <f>H20-H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="41">
+        <f>I20-I22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Taxes on EBIT</t>
+        </is>
+      </c>
+      <c r="C24" s="41">
+        <f>MAX(0,C23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="D24" s="41">
+        <f>MAX(0,D23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="E24" s="41">
+        <f>MAX(0,E23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="F24" s="41">
+        <f>MAX(0,F23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="G24" s="41">
+        <f>MAX(0,G23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="H24" s="41">
+        <f>MAX(0,H23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+      <c r="I24" s="41">
+        <f>MAX(0,I23)*Inputs!$B$60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>NOPAT</t>
+        </is>
+      </c>
+      <c r="C25" s="41">
+        <f>C23-C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="41">
+        <f>D23-D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="41">
+        <f>E23-E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="41">
+        <f>F23-F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="41">
+        <f>G23-G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="41">
+        <f>H23-H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="41">
+        <f>I23-I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="41">
+        <f>I25*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>D&amp;A</t>
+        </is>
+      </c>
+      <c r="B26" s="39">
+        <f>Inputs!$B$35</f>
+        <v/>
+      </c>
+      <c r="C26" s="41">
+        <f>B26+Inputs!$B$66*(B27-B26)</f>
+        <v/>
+      </c>
+      <c r="D26" s="41">
+        <f>C26+Inputs!$B$66*(C27-C26)</f>
+        <v/>
+      </c>
+      <c r="E26" s="41">
+        <f>D26+Inputs!$B$66*(D27-D26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="41">
+        <f>E26+Inputs!$B$66*(E27-E26)</f>
+        <v/>
+      </c>
+      <c r="G26" s="41">
+        <f>F26+Inputs!$B$66*(F27-F26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="41">
+        <f>G26+Inputs!$B$66*(G27-G26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="41">
+        <f>H26+Inputs!$B$66*(H27-H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="41">
+        <f>I26*(1+Inputs!$B$63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B27" s="39">
+        <f>Inputs!$B$36</f>
+        <v/>
+      </c>
+      <c r="C27" s="39">
+        <f>Inputs!C159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="D27" s="39">
+        <f>Inputs!D159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="E27" s="39">
+        <f>Inputs!E159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="F27" s="39">
+        <f>Inputs!F159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="G27" s="39">
+        <f>Inputs!G159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="H27" s="39">
+        <f>Inputs!H159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="I27" s="39">
+        <f>Inputs!I159*Inputs!$B$74*(1-Inputs!$B$77)</f>
+        <v/>
+      </c>
+      <c r="J27" s="41">
+        <f>J26*Inputs!$B$64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Change in net working capital</t>
+        </is>
+      </c>
+      <c r="C28" s="41">
+        <f>Inputs!$B$65*(C15-B15)</f>
+        <v/>
+      </c>
+      <c r="D28" s="41">
+        <f>Inputs!$B$65*(D15-C15)</f>
+        <v/>
+      </c>
+      <c r="E28" s="41">
+        <f>Inputs!$B$65*(E15-D15)</f>
+        <v/>
+      </c>
+      <c r="F28" s="41">
+        <f>Inputs!$B$65*(F15-E15)</f>
+        <v/>
+      </c>
+      <c r="G28" s="41">
+        <f>Inputs!$B$65*(G15-F15)</f>
+        <v/>
+      </c>
+      <c r="H28" s="41">
+        <f>Inputs!$B$65*(H15-G15)</f>
+        <v/>
+      </c>
+      <c r="I28" s="41">
+        <f>Inputs!$B$65*(I15-H15)</f>
+        <v/>
+      </c>
+      <c r="J28" s="41">
+        <f>Inputs!$B$65*(J15-I15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="58">
+        <f>C25+C26-C27-C28</f>
+        <v/>
+      </c>
+      <c r="D29" s="58">
+        <f>D25+D26-D27-D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="58">
+        <f>E25+E26-E27-E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="58">
+        <f>F25+F26-F27-F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="58">
+        <f>G25+G26-G27-G28</f>
+        <v/>
+      </c>
+      <c r="H29" s="58">
+        <f>H25+H26-H27-H28</f>
+        <v/>
+      </c>
+      <c r="I29" s="58">
+        <f>I25+I26-I27-I28</f>
+        <v/>
+      </c>
+      <c r="J29" s="58">
+        <f>J25+J26-J27-J28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FCF margin</t>
+        </is>
+      </c>
+      <c r="C30" s="42">
+        <f>IF(C15=0,0,C29/C15)</f>
+        <v/>
+      </c>
+      <c r="D30" s="42">
+        <f>IF(D15=0,0,D29/D15)</f>
+        <v/>
+      </c>
+      <c r="E30" s="42">
+        <f>IF(E15=0,0,E29/E15)</f>
+        <v/>
+      </c>
+      <c r="F30" s="42">
+        <f>IF(F15=0,0,F29/F15)</f>
+        <v/>
+      </c>
+      <c r="G30" s="42">
+        <f>IF(G15=0,0,G29/G15)</f>
+        <v/>
+      </c>
+      <c r="H30" s="42">
+        <f>IF(H15=0,0,H29/H15)</f>
+        <v/>
+      </c>
+      <c r="I30" s="42">
+        <f>IF(I15=0,0,I29/I15)</f>
+        <v/>
+      </c>
+      <c r="J30" s="42">
+        <f>IF(J15=0,0,J29/J15)</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Base: Diamond Rapids lands mid-2027 roughly competitive; server share stabilizes; Panther/Nova Lake hold client roughly flat; EMIB-T packaging</t>
-        </is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="C31" s="17">
+        <f>1/(1+Inputs!$B$62)^C4</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>1/(1+Inputs!$B$62)^D4</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>1/(1+Inputs!$B$62)^E4</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>1/(1+Inputs!$B$62)^F4</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>1/(1+Inputs!$B$62)^G4</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>1/(1+Inputs!$B$62)^H4</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>1/(1+Inputs!$B$62)^I4</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      and an Apple 18A-P ramp build external revenue to ~$15bn by 2033; 18A reaches industry-standard yield in 2027; GM recovers to ~50%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Bull: Intel wins a 14A anchor customer, packaging becomes a multi-billion business, Diamond Rapids wins sockets, AI-driven CPU demand stays</t>
-        </is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="C32" s="41">
+        <f>C29*C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="41">
+        <f>D29*D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="41">
+        <f>E29*E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="41">
+        <f>F29*F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="41">
+        <f>G29*G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="41">
+        <f>H29*H31</f>
+        <v/>
+      </c>
+      <c r="I32" s="41">
+        <f>I29*I31</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      strong; GM rises to ~57% (still below TSMC's 67.7% and Intel's own 2010s levels ~60%).</t>
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>VALUATION (value per share floored at $0: equity has limited liability)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Sum of PV of explicit FCF (2027-2033)</t>
+        </is>
+      </c>
+      <c r="B35" s="41">
+        <f>SUM(C32:I32)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>IMPORTANT CAVEATS</t>
-        </is>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value at end-2033</t>
+        </is>
+      </c>
+      <c r="B36" s="41">
+        <f>IF(Inputs!$B$62&lt;=Inputs!$B$63,0,J29/(Inputs!$B$62-Inputs!$B$63))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>- Scenario drivers are MY judgment calls derived from the product evidence, not forecasts I believe will happen. They are labeled hypotheticals.</t>
-        </is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B37" s="41">
+        <f>B36*I31</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>- Some inputs are placeholders I could not source in this environment (D&amp;A, SBC, non-controlling interests, Q1-26 external foundry revenue).</t>
-        </is>
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B38" s="41">
+        <f>B35+B37</f>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  They are filled yellow. Replace them from the Q2 2026 10-Q before relying on the output.</t>
-        </is>
+          <t>+ Net cash (incl. Aug-26 raise)</t>
+        </is>
+      </c>
+      <c r="B39" s="39">
+        <f>Inputs!$B$16</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>- Share count is derived (Q2 non-GAAP net income / non-GAAP EPS + August 2026 offering shares); verify against the 10-Q cover page.</t>
-        </is>
+          <t>+ Altera stake</t>
+        </is>
+      </c>
+      <c r="B40" s="39">
+        <f>Inputs!$B$14</f>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>- Scenario assumptions were fixed BEFORE computing values and were not tuned toward the market price.</t>
-        </is>
+          <t>- Non-controlling interests</t>
+        </is>
+      </c>
+      <c r="B41" s="39">
+        <f>-Inputs!$B$15</f>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>- Not investment advice.</t>
-        </is>
+          <t>- Payment for TSMC Arizona assets (TaiwanMax only)</t>
+        </is>
+      </c>
+      <c r="B42" s="39">
+        <f>-Inputs!$B$76</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B43" s="41">
+        <f>B38+B39+B40+B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Diluted shares (bn)</t>
+        </is>
+      </c>
+      <c r="B44" s="40">
+        <f>Inputs!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Value per share ($)</t>
+        </is>
+      </c>
+      <c r="B45" s="37">
+        <f>IF(B44=0,0,MAX(0,B43/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Inputs!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs price</t>
+        </is>
+      </c>
+      <c r="B47" s="42">
+        <f>IF(B46=0,0,B45/B46-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B48" s="42">
+        <f>IF(B38=0,0,B37/B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(C25&lt;=0,0,B45/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Market P/E on 2027 NOPAT/share</t>
+        </is>
+      </c>
+      <c r="B50" s="11">
+        <f>IF(C25&lt;=0,0,B46/(C25/B44))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -826,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -835,7 +2243,8 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,6 +2282,11 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Prob-weighted</t>
         </is>
       </c>
@@ -884,22 +2298,26 @@
         </is>
       </c>
       <c r="B4" s="35">
-        <f>Inputs!$B$81</f>
+        <f>Inputs!$B$82</f>
         <v/>
       </c>
       <c r="C4" s="35">
-        <f>Inputs!$B$82</f>
+        <f>Inputs!$B$83</f>
         <v/>
       </c>
       <c r="D4" s="35">
-        <f>Inputs!$B$83</f>
+        <f>Inputs!$B$84</f>
         <v/>
       </c>
       <c r="E4" s="35">
-        <f>Inputs!$B$84</f>
-        <v/>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+        <f>Inputs!$B$85</f>
+        <v/>
+      </c>
+      <c r="F4" s="35">
+        <f>Inputs!$B$86</f>
+        <v/>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Weights are my judgment (Inputs sheet); they must sum to 100%</t>
         </is>
@@ -912,26 +2330,30 @@
         </is>
       </c>
       <c r="B5" s="36">
-        <f>Bear!B44</f>
+        <f>Bear!B45</f>
         <v/>
       </c>
       <c r="C5" s="36">
-        <f>Base!B44</f>
+        <f>Base!B45</f>
         <v/>
       </c>
       <c r="D5" s="36">
-        <f>Bull!B44</f>
+        <f>Bull!B45</f>
         <v/>
       </c>
       <c r="E5" s="36">
-        <f>Taiwan!B44</f>
-        <v/>
-      </c>
-      <c r="F5" s="37">
-        <f>SUMPRODUCT(B4:E4,B5:E5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+        <f>Taiwan!B45</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>TaiwanMax!B45</f>
+        <v/>
+      </c>
+      <c r="G5" s="37">
+        <f>SUMPRODUCT(B4:F4,B5:F5)</f>
+        <v/>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Check weights sum:</t>
         </is>
@@ -944,27 +2366,31 @@
         </is>
       </c>
       <c r="B6" s="35">
-        <f>Bear!B46</f>
+        <f>Bear!B47</f>
         <v/>
       </c>
       <c r="C6" s="35">
-        <f>Base!B46</f>
+        <f>Base!B47</f>
         <v/>
       </c>
       <c r="D6" s="35">
-        <f>Bull!B46</f>
+        <f>Bull!B47</f>
         <v/>
       </c>
       <c r="E6" s="35">
-        <f>Taiwan!B46</f>
-        <v/>
-      </c>
-      <c r="F6" s="38">
-        <f>IF(Inputs!$B$4=0,0,F5/Inputs!$B$4-1)</f>
-        <v/>
-      </c>
-      <c r="G6" s="2">
-        <f>IF(ABS(Inputs!$B$85-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
+        <f>Taiwan!B47</f>
+        <v/>
+      </c>
+      <c r="F6" s="35">
+        <f>TaiwanMax!B47</f>
+        <v/>
+      </c>
+      <c r="G6" s="38">
+        <f>IF(Inputs!$B$4=0,0,G5/Inputs!$B$4-1)</f>
+        <v/>
+      </c>
+      <c r="H6" s="2">
+        <f>IF(ABS(Inputs!$B$87-1)&lt;0.0001,"OK","WEIGHTS DO NOT SUM TO 100%")</f>
         <v/>
       </c>
     </row>
@@ -990,6 +2416,10 @@
         <f>Taiwan!B38</f>
         <v/>
       </c>
+      <c r="F7" s="39">
+        <f>TaiwanMax!B38</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -998,19 +2428,23 @@
         </is>
       </c>
       <c r="B8" s="35">
-        <f>Bear!B47</f>
+        <f>Bear!B48</f>
         <v/>
       </c>
       <c r="C8" s="35">
-        <f>Base!B47</f>
+        <f>Base!B48</f>
         <v/>
       </c>
       <c r="D8" s="35">
-        <f>Bull!B47</f>
+        <f>Bull!B48</f>
         <v/>
       </c>
       <c r="E8" s="35">
-        <f>Taiwan!B47</f>
+        <f>Taiwan!B48</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>TaiwanMax!B48</f>
         <v/>
       </c>
     </row>
@@ -1036,6 +2470,10 @@
         <f>Taiwan!F15</f>
         <v/>
       </c>
+      <c r="F9" s="39">
+        <f>TaiwanMax!F15</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1059,6 +2497,10 @@
         <f>Taiwan!I15</f>
         <v/>
       </c>
+      <c r="F10" s="39">
+        <f>TaiwanMax!I15</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1082,6 +2524,10 @@
         <f>Taiwan!F17</f>
         <v/>
       </c>
+      <c r="F11" s="35">
+        <f>TaiwanMax!F17</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1105,6 +2551,10 @@
         <f>Taiwan!F21</f>
         <v/>
       </c>
+      <c r="F12" s="35">
+        <f>TaiwanMax!F21</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1128,6 +2578,10 @@
         <f>Taiwan!I9</f>
         <v/>
       </c>
+      <c r="F13" s="39">
+        <f>TaiwanMax!I9</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1151,6 +2605,10 @@
         <f>Taiwan!I14</f>
         <v/>
       </c>
+      <c r="F14" s="39">
+        <f>TaiwanMax!I14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1174,6 +2632,10 @@
         <f>Taiwan!I10</f>
         <v/>
       </c>
+      <c r="F15" s="39">
+        <f>TaiwanMax!I10</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1197,6 +2659,10 @@
         <f>Taiwan!F29</f>
         <v/>
       </c>
+      <c r="F16" s="39">
+        <f>TaiwanMax!F29</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1220,6 +2686,10 @@
         <f>SUM(Taiwan!C29:I29)</f>
         <v/>
       </c>
+      <c r="F17" s="39">
+        <f>SUM(TaiwanMax!C29:I29)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1344,7 +2814,7 @@
         <f>B30/Base!I31*(Inputs!$B$62-Inputs!$B$63)</f>
         <v/>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>FCF in 2034 that the Base explicit years plus the market price imply</t>
         </is>
@@ -1414,7 +2884,7 @@
       <c r="B37" s="43" t="n">
         <v>0.603</v>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Source: TSMC Q2 2026 results (60.3% op margin). Context only</t>
         </is>
@@ -1522,7 +2992,7 @@
         </is>
       </c>
       <c r="B48" s="44">
-        <f>IF((Inputs!$B$81+Inputs!$B$82+Inputs!$B$83)=0,0,(B5*Inputs!$B$81+C5*Inputs!$B$82+D5*Inputs!$B$83)/(Inputs!$B$81+Inputs!$B$82+Inputs!$B$83))</f>
+        <f>IF((Inputs!$B$82+Inputs!$B$83+Inputs!$B$84)=0,0,(B5*Inputs!$B$82+C5*Inputs!$B$83+D5*Inputs!$B$84)/(Inputs!$B$82+Inputs!$B$83+Inputs!$B$84))</f>
         <v/>
       </c>
     </row>
@@ -1547,42 +3017,64 @@
         <f>IF(B47&lt;=B49,"Not reachable: Taiwan value &lt; price",(B49-B48)/(B47-B48))</f>
         <v/>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Read as: 'the market price is fair IF you believe this is the probability of a Taiwan cut-off (with Taiwan-scenario payoffs as modeled)'.</t>
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax-scenario value per share ($)</t>
+        </is>
+      </c>
+      <c r="B51" s="44">
+        <f>F5</f>
+        <v/>
+      </c>
+    </row>
     <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Break-even probability of TaiwanMax scenario to justify price</t>
+        </is>
+      </c>
+      <c r="B52" s="42">
+        <f>IF(B51&lt;=B49,"Not reachable: TaiwanMax value &lt; price",(B49-B48)/(B51-B48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>HOW TO READ THIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
+          <t>- 'If the scenario is true, the math says X.' None of the scenarios is a forecast I endorse. The weights express my judgment of plausibility from the product evidence.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>- The reverse DCF shows how much more (or less) terminal cash flow than my Base case the current price needs. A ratio well above 1.0x means the price embeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  assumptions closer to the Bull case: a 14A anchor customer, packaging at scale, sustained CPU pricing and gross margins in the mid-50s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>- Terminal value is a large share of EV in every scenario. Small changes in WACC or terminal growth move the answer a lot: see the Sensitivity sheet.</t>
         </is>
@@ -1599,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2236,157 +3728,311 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>Current price ($)</t>
-        </is>
-      </c>
-      <c r="B35" s="36">
-        <f>Inputs!$B$4</f>
-        <v/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>TaiwanMax scenario: value/share vs WACC and terminal growth (live formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>WACC (down) / terminal g (across)</t>
+        </is>
+      </c>
+      <c r="B36" s="43" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C36" s="43" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D36" s="43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E36" s="43" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="F36" s="43" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>TORNADO (Base scenario): one input flexed at a time</t>
-        </is>
+      <c r="A37" s="43" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="B37" s="44">
+        <f>MAX(0,IF($A37&lt;=B$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A37)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+B$36)+TaiwanMax!$I$26*(1+B$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*B$36)/($A37-B$36)/(1+$A37)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C37" s="44">
+        <f>MAX(0,IF($A37&lt;=C$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A37)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+C$36)+TaiwanMax!$I$26*(1+C$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*C$36)/($A37-C$36)/(1+$A37)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D37" s="44">
+        <f>MAX(0,IF($A37&lt;=D$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A37)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+D$36)+TaiwanMax!$I$26*(1+D$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*D$36)/($A37-D$36)/(1+$A37)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E37" s="44">
+        <f>MAX(0,IF($A37&lt;=E$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A37)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+E$36)+TaiwanMax!$I$26*(1+E$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*E$36)/($A37-E$36)/(1+$A37)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F37" s="44">
+        <f>MAX(0,IF($A37&lt;=F$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A37)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+F$36)+TaiwanMax!$I$26*(1+F$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*F$36)/($A37-F$36)/(1+$A37)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>Input flexed (Base scenario, others held)</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>Low case $/sh</t>
-        </is>
-      </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>High case $/sh</t>
-        </is>
-      </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>Base $/sh</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="inlineStr">
-        <is>
-          <t>Swing $/sh</t>
-        </is>
+      <c r="A38" s="43" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="B38" s="44">
+        <f>MAX(0,IF($A38&lt;=B$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A38)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+B$36)+TaiwanMax!$I$26*(1+B$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*B$36)/($A38-B$36)/(1+$A38)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C38" s="44">
+        <f>MAX(0,IF($A38&lt;=C$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A38)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+C$36)+TaiwanMax!$I$26*(1+C$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*C$36)/($A38-C$36)/(1+$A38)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D38" s="44">
+        <f>MAX(0,IF($A38&lt;=D$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A38)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+D$36)+TaiwanMax!$I$26*(1+D$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*D$36)/($A38-D$36)/(1+$A38)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E38" s="44">
+        <f>MAX(0,IF($A38&lt;=E$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A38)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+E$36)+TaiwanMax!$I$26*(1+E$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*E$36)/($A38-E$36)/(1+$A38)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F38" s="44">
+        <f>MAX(0,IF($A38&lt;=F$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A38)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+F$36)+TaiwanMax!$I$26*(1+F$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*F$36)/($A38-F$36)/(1+$A38)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Ext. foundry revenue x0.5 / x2.0</t>
-        </is>
-      </c>
-      <c r="B39" s="45" t="n">
-        <v>22.53</v>
-      </c>
-      <c r="C39" s="45" t="n">
-        <v>38.02</v>
-      </c>
-      <c r="D39" s="46">
-        <f>Base!B44</f>
-        <v/>
-      </c>
-      <c r="E39" s="47">
-        <f>C39-B39</f>
+      <c r="A39" s="43" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="B39" s="44">
+        <f>MAX(0,IF($A39&lt;=B$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A39)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+B$36)+TaiwanMax!$I$26*(1+B$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*B$36)/($A39-B$36)/(1+$A39)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C39" s="44">
+        <f>MAX(0,IF($A39&lt;=C$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A39)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+C$36)+TaiwanMax!$I$26*(1+C$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*C$36)/($A39-C$36)/(1+$A39)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D39" s="44">
+        <f>MAX(0,IF($A39&lt;=D$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A39)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+D$36)+TaiwanMax!$I$26*(1+D$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*D$36)/($A39-D$36)/(1+$A39)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E39" s="44">
+        <f>MAX(0,IF($A39&lt;=E$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A39)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+E$36)+TaiwanMax!$I$26*(1+E$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*E$36)/($A39-E$36)/(1+$A39)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F39" s="44">
+        <f>MAX(0,IF($A39&lt;=F$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A39)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+F$36)+TaiwanMax!$I$26*(1+F$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*F$36)/($A39-F$36)/(1+$A39)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>China erosion 10 pts/yr faster / 5 pts/yr slower</t>
-        </is>
-      </c>
-      <c r="B40" s="45" t="n">
-        <v>25.33</v>
-      </c>
-      <c r="C40" s="45" t="n">
-        <v>29.49</v>
-      </c>
-      <c r="D40" s="46">
-        <f>Base!B44</f>
-        <v/>
-      </c>
-      <c r="E40" s="47">
-        <f>C40-B40</f>
+      <c r="A40" s="43" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="B40" s="44">
+        <f>MAX(0,IF($A40&lt;=B$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A40)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+B$36)+TaiwanMax!$I$26*(1+B$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*B$36)/($A40-B$36)/(1+$A40)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C40" s="44">
+        <f>MAX(0,IF($A40&lt;=C$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A40)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+C$36)+TaiwanMax!$I$26*(1+C$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*C$36)/($A40-C$36)/(1+$A40)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D40" s="44">
+        <f>MAX(0,IF($A40&lt;=D$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A40)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+D$36)+TaiwanMax!$I$26*(1+D$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*D$36)/($A40-D$36)/(1+$A40)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E40" s="44">
+        <f>MAX(0,IF($A40&lt;=E$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A40)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+E$36)+TaiwanMax!$I$26*(1+E$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*E$36)/($A40-E$36)/(1+$A40)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F40" s="44">
+        <f>MAX(0,IF($A40&lt;=F$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A40)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+F$36)+TaiwanMax!$I$26*(1+F$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*F$36)/($A40-F$36)/(1+$A40)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>DCAI growth -3 / +3 pts per yr</t>
-        </is>
-      </c>
-      <c r="B41" s="45" t="n">
-        <v>23.62</v>
-      </c>
-      <c r="C41" s="45" t="n">
-        <v>32.47</v>
-      </c>
-      <c r="D41" s="46">
-        <f>Base!B44</f>
-        <v/>
-      </c>
-      <c r="E41" s="47">
-        <f>C41-B41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Gross margin -3 / +3 pts, all years</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="C42" s="45" t="n">
-        <v>32.28</v>
-      </c>
-      <c r="D42" s="46">
-        <f>Base!B44</f>
-        <v/>
-      </c>
-      <c r="E42" s="47">
-        <f>C42-B42</f>
+      <c r="A41" s="43" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="B41" s="44">
+        <f>MAX(0,IF($A41&lt;=B$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A41)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+B$36)+TaiwanMax!$I$26*(1+B$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*B$36)/($A41-B$36)/(1+$A41)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="C41" s="44">
+        <f>MAX(0,IF($A41&lt;=C$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A41)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+C$36)+TaiwanMax!$I$26*(1+C$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*C$36)/($A41-C$36)/(1+$A41)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="D41" s="44">
+        <f>MAX(0,IF($A41&lt;=D$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A41)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+D$36)+TaiwanMax!$I$26*(1+D$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*D$36)/($A41-D$36)/(1+$A41)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="E41" s="44">
+        <f>MAX(0,IF($A41&lt;=E$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A41)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+E$36)+TaiwanMax!$I$26*(1+E$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*E$36)/($A41-E$36)/(1+$A41)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
+        <v/>
+      </c>
+      <c r="F41" s="44">
+        <f>MAX(0,IF($A41&lt;=F$36,0,(SUMPRODUCT(TaiwanMax!$C$29:$I$29,1/(1+$A41)^TaiwanMax!$C$4:$I$4)+(TaiwanMax!$I$25*(1+F$36)+TaiwanMax!$I$26*(1+F$36)*(1-Inputs!$B$64)-Inputs!$B$65*TaiwanMax!$I$15*F$36)/($A41-F$36)/(1+$A41)^TaiwanMax!$I$4+Inputs!$B$16+Inputs!$B$14-Inputs!$B$15-Inputs!$B$76)/Inputs!$B$9))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>Current price ($)</t>
+        </is>
+      </c>
+      <c r="B43" s="36">
+        <f>Inputs!$B$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>TORNADO (Base scenario): one input flexed at a time</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>Input flexed (Base scenario, others held)</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Low case $/sh</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>High case $/sh</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>Base $/sh</t>
+        </is>
+      </c>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>Swing $/sh</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Ext. foundry revenue x0.5 / x2.0</t>
+        </is>
+      </c>
+      <c r="B47" s="45" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="C47" s="45" t="n">
+        <v>38.02</v>
+      </c>
+      <c r="D47" s="46">
+        <f>Base!B45</f>
+        <v/>
+      </c>
+      <c r="E47" s="47">
+        <f>C47-B47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>China erosion 10 pts/yr faster / 5 pts/yr slower</t>
+        </is>
+      </c>
+      <c r="B48" s="45" t="n">
+        <v>25.33</v>
+      </c>
+      <c r="C48" s="45" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="D48" s="46">
+        <f>Base!B45</f>
+        <v/>
+      </c>
+      <c r="E48" s="47">
+        <f>C48-B48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>DCAI growth -3 / +3 pts per yr</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="n">
+        <v>23.62</v>
+      </c>
+      <c r="C49" s="45" t="n">
+        <v>32.47</v>
+      </c>
+      <c r="D49" s="46">
+        <f>Base!B45</f>
+        <v/>
+      </c>
+      <c r="E49" s="47">
+        <f>C49-B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Gross margin -3 / +3 pts, all years</t>
+        </is>
+      </c>
+      <c r="B50" s="45" t="n">
+        <v>23.12</v>
+      </c>
+      <c r="C50" s="45" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="D50" s="46">
+        <f>Base!B45</f>
+        <v/>
+      </c>
+      <c r="E50" s="47">
+        <f>C50-B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>Capex x1.15 / x0.85 (2027+)</t>
         </is>
       </c>
-      <c r="B43" s="45" t="n">
+      <c r="B51" s="45" t="n">
         <v>25.55</v>
       </c>
-      <c r="C43" s="45" t="n">
+      <c r="C51" s="45" t="n">
         <v>29.84</v>
       </c>
-      <c r="D43" s="46">
-        <f>Base!B44</f>
-        <v/>
-      </c>
-      <c r="E43" s="47">
-        <f>C43-B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="48" t="inlineStr">
+      <c r="D51" s="46">
+        <f>Base!B45</f>
+        <v/>
+      </c>
+      <c r="E51" s="47">
+        <f>C51-B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
         <is>
           <t>Tornado values are static: computed by setting each Inputs 'FLEX LEVER' and recalculating at the default inputs. Re-run them via the flex levers if you change base inputs. WACC and terminal-growth sensitivity: live grids above.</t>
         </is>
@@ -3165,7 +4811,7 @@
         </is>
       </c>
       <c r="B39" s="44">
-        <f>Base!B44</f>
+        <f>Base!B45</f>
         <v/>
       </c>
     </row>
@@ -3349,7 +4995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -4380,75 +6026,75 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>CHINA TAILWIND 3: capex offset from 48D 35% fab tax credit + SCIP partner funding (share of gross capex)</t>
-        </is>
-      </c>
-      <c r="B76" s="43" t="n">
-        <v>0.1</v>
+          <t>TaiwanMax only: payment by Intel for TSMC Arizona assets ($bn)</t>
+        </is>
+      </c>
+      <c r="B76" s="53" t="n">
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>ASSUMPTION 10% (conservative). 48D gives a 35% refundable credit for fabs started by 31 Dec 2026; partners (Brookfield/Apollo) co-fund Arizona/Ireland. Set 0 to turn off</t>
+          <t>ASSUMPTION 0 = US government transfers the fabs to Intel at no cost to shareholders (generous). TSMC has committed ~$265bn to Arizona; try 65-150 if Intel must pay</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>CHINA TAILWIND 3: capex offset from 48D 35% fab tax credit + SCIP partner funding (share of gross capex)</t>
+        </is>
+      </c>
+      <c r="B77" s="43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>ASSUMPTION 10% (conservative). 48D gives a 35% refundable credit for fabs started by 31 Dec 2026; partners (Brookfield/Apollo) co-fund Arizona/Ireland. Set 0 to turn off</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
           <t>Tailwind switch: include China tailwinds 1 and 2 (1 = on, 0 = off)</t>
         </is>
       </c>
-      <c r="B77" s="30" t="n">
+      <c r="B78" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Set 0 to see the model without the China tailwinds</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>SCENARIO WEIGHTS (judgment; must sum to 100%)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B81" s="50" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>My judgment; edit</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="B82" s="50" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -4459,11 +6105,11 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="B83" s="50" t="n">
-        <v>0.24</v>
+        <v>0.43</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -4474,209 +6120,173 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Taiwan (disruption / cut-off of Taiwan fabs from Western customers, from 2027)</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="B84" s="50" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>My judgment; edit. The Summary sheet solves for the probability that would justify the current price</t>
+          <t>My judgment; edit</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>Taiwan (disruption / cut-off of Taiwan fabs from Western customers, from 2027)</t>
+        </is>
+      </c>
+      <c r="B85" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit. The Summary sheet solves for the probability that would justify the current price</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax (Taiwan fabs destroyed or seized + TSMC Arizona transferred to Intel + TSMC engineers join Intel)</t>
+        </is>
+      </c>
+      <c r="B86" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>My judgment; edit. A subset of a Taiwan conflict, so Taiwan + TaiwanMax together = 5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
           <t>Check: sum of weights</t>
         </is>
       </c>
-      <c r="B85" s="42">
-        <f>$B$81+$B$82+$B$83+$B$84</f>
-        <v/>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
+      <c r="B87" s="42">
+        <f>$B$82+$B$83+$B$84+$B$85+$B$86</f>
+        <v/>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Must equal 100%</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
         <is>
           <t>SCENARIO DRIVERS (2027-2033). Hypothetical paths tied to product evidence; NOT forecasts I endorse</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>DCAI revenue growth</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G90" s="3" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H90" s="3" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C89" s="50" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="D89" s="50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="E89" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G89" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H89" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I89" s="50" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  DCAI revenue growth - Base</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C90" s="50" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D90" s="50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E90" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F90" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G90" s="50" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H90" s="50" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I90" s="50" t="n">
-        <v>0.04</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
+          <t xml:space="preserve">  DCAI revenue growth - Bear</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C91" s="50" t="n">
-        <v>0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="D91" s="50" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="E91" s="50" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="50" t="n">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G91" s="50" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="H91" s="50" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I91" s="50" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  DCAI revenue growth - Taiwan</t>
+          <t xml:space="preserve">  DCAI revenue growth - Base</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C92" s="50" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="D92" s="50" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="E92" s="50" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
       </c>
       <c r="F92" s="50" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G92" s="50" t="n">
         <v>0.05</v>
@@ -4691,944 +6301,989 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Bear: shortage ASP spike (+48% YoY in Q2-26) reverses as Venice ships Q4-26 and Diamond Rapids slips; Bull: DMR competitive + agentic CPU demand persists</t>
-        </is>
+          <t xml:space="preserve">  DCAI revenue growth - Bull</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C93" s="50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D93" s="50" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E93" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F93" s="50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G93" s="50" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H93" s="50" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I93" s="50" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DCAI revenue growth - Taiwan</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C94" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D94" s="50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E94" s="50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F94" s="50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G94" s="50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H94" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I94" s="50" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="inlineStr">
-        <is>
-          <t>CCPG (client) revenue growth</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  DCAI revenue growth - TaiwanMax</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C95" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D95" s="50" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F95" s="50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G95" s="50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H95" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I95" s="50" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C96" s="50" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="D96" s="50" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="E96" s="50" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F96" s="50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="G96" s="50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="H96" s="50" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I96" s="50" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C97" s="50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="D97" s="50" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="E97" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F97" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G97" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H97" s="50" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I97" s="50" t="n">
-        <v>0.02</v>
+          <t xml:space="preserve">  Rationale: Bear: shortage ASP spike (+48% YoY in Q2-26) reverses as Venice ships Q4-26 and Diamond Rapids slips; Bull: DMR competitive + agentic CPU demand persists</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C98" s="50" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="D98" s="50" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E98" s="50" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F98" s="50" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G98" s="50" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H98" s="50" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I98" s="50" t="n">
-        <v>0.03</v>
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>CCPG (client) revenue growth</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CCPG (client) revenue growth - Taiwan</t>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bear</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C99" s="50" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="D99" s="50" t="n">
-        <v>0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="E99" s="50" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="F99" s="50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G99" s="50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="H99" s="50" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I99" s="50" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
-        </is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Base</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C100" s="50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="D100" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E100" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F100" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G100" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H100" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I100" s="50" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Bull</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C101" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D101" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E101" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F101" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G101" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H101" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I101" s="50" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="inlineStr">
-        <is>
-          <t>External foundry + packaging revenue ($bn)</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G102" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CCPG (client) revenue growth - Taiwan</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C102" s="50" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D102" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E102" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F102" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G102" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H102" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I102" s="50" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
+          <t xml:space="preserve">  CCPG (client) revenue growth - TaiwanMax</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C103" s="49" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="D103" s="49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E103" s="49" t="n">
-        <v>2</v>
-      </c>
-      <c r="F103" s="49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G103" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="H103" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I103" s="49" t="n">
-        <v>4</v>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C103" s="50" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D103" s="50" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E103" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F103" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G103" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H103" s="50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I103" s="50" t="n">
+        <v>0.03</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C104" s="49" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D104" s="49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E104" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="F104" s="49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G104" s="49" t="n">
-        <v>11</v>
-      </c>
-      <c r="H104" s="49" t="n">
-        <v>13</v>
-      </c>
-      <c r="I104" s="49" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C105" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="D105" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="E105" s="49" t="n">
-        <v>12</v>
-      </c>
-      <c r="F105" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="G105" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="H105" s="49" t="n">
-        <v>29</v>
-      </c>
-      <c r="I105" s="49" t="n">
-        <v>33</v>
+          <t xml:space="preserve">  Rationale: Mercury: AMD client share 30.3% Q2-26 and rising; Arm WoA ~3%. Bull assumes Nova Lake + NVIDIA x86 RTX SoCs hold share</t>
+        </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Taiwan</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C106" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="D106" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="E106" s="49" t="n">
-        <v>45</v>
-      </c>
-      <c r="F106" s="49" t="n">
-        <v>55</v>
-      </c>
-      <c r="G106" s="49" t="n">
-        <v>60</v>
-      </c>
-      <c r="H106" s="49" t="n">
-        <v>65</v>
-      </c>
-      <c r="I106" s="49" t="n">
-        <v>70</v>
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>External foundry + packaging revenue ($bn)</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
-        </is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C107" s="49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D107" s="49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E107" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G107" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H107" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I107" s="49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Base</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C108" s="49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D108" s="49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E108" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F108" s="49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G108" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="H108" s="49" t="n">
+        <v>13</v>
+      </c>
+      <c r="I108" s="49" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP gross margin</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Bull</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C109" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E109" s="49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F109" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="G109" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="H109" s="49" t="n">
+        <v>29</v>
+      </c>
+      <c r="I109" s="49" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - Taiwan</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C110" s="50" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="D110" s="50" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E110" s="50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F110" s="50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G110" s="50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H110" s="50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I110" s="50" t="n">
-        <v>0.4</v>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C110" s="49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D110" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="E110" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="F110" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="G110" s="49" t="n">
+        <v>60</v>
+      </c>
+      <c r="H110" s="49" t="n">
+        <v>65</v>
+      </c>
+      <c r="I110" s="49" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Base</t>
+          <t xml:space="preserve">  External foundry + packaging revenue ($bn) - TaiwanMax</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C111" s="50" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="D111" s="50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E111" s="50" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="F111" s="50" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G111" s="50" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H111" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I111" s="50" t="n">
-        <v>0.5</v>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C111" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="D111" s="49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E111" s="49" t="n">
+        <v>77</v>
+      </c>
+      <c r="F111" s="49" t="n">
+        <v>97</v>
+      </c>
+      <c r="G111" s="49" t="n">
+        <v>110</v>
+      </c>
+      <c r="H111" s="49" t="n">
+        <v>120</v>
+      </c>
+      <c r="I111" s="49" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C112" s="50" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="D112" s="50" t="n">
+          <t xml:space="preserve">  Rationale: Today ~$1.2bn annualized, mostly Altera. Base = EMIB-T packaging + Apple 18A-P ramp. Bull = 14A anchor customer. All ABOVE Intel's historical base rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP gross margin</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bear</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C115" s="50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D115" s="50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E115" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F115" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G115" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H115" s="50" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I115" s="50" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP gross margin - Base</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C116" s="50" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D116" s="50" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E116" s="50" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F116" s="50" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G116" s="50" t="n">
         <v>0.49</v>
       </c>
-      <c r="E112" s="50" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F112" s="50" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="G112" s="50" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H112" s="50" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I112" s="50" t="n">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Non-GAAP gross margin - Taiwan</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C113" s="50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D113" s="50" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E113" s="50" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F113" s="50" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="G113" s="50" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H113" s="50" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="I113" s="50" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="inlineStr">
-        <is>
-          <t>Non-GAAP opex growth</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G116" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="H116" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I116" s="50" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Bull</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="C117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.46</v>
       </c>
       <c r="D117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.49</v>
       </c>
       <c r="E117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="F117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.54</v>
       </c>
       <c r="G117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.55</v>
       </c>
       <c r="H117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I117" s="50" t="n">
-        <v>0.01</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - Taiwan</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.45</v>
       </c>
       <c r="D118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.55</v>
       </c>
       <c r="E118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="F118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="G118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="H118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
       <c r="I118" s="50" t="n">
-        <v>0.03</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
+          <t xml:space="preserve">  Non-GAAP gross margin - TaiwanMax</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>TaiwanMax</t>
         </is>
       </c>
       <c r="C119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.45</v>
       </c>
       <c r="D119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.57</v>
       </c>
       <c r="E119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.63</v>
       </c>
       <c r="F119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
       <c r="G119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
       <c r="H119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
       <c r="I119" s="50" t="n">
-        <v>0.04</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Non-GAAP opex growth - Taiwan</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I120" s="50" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
+          <t xml:space="preserve">  Rationale: Q2-26 41.8%. Compare TSMC 67.7% (Q2-26), Intel ~60% in the 2010s. Base requires 18A industry-standard yields in 2027 (CFO's own timeline)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>Non-GAAP opex growth</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="inlineStr">
-        <is>
-          <t>China domestic end-demand revenue change per year</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bear</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H123" s="50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I123" s="50" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bear</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Base</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Bear</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C124" s="50" t="n">
-        <v>-0.2</v>
+        <v>0.03</v>
       </c>
       <c r="D124" s="50" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="E124" s="50" t="n">
-        <v>-0.15</v>
+        <v>0.03</v>
       </c>
       <c r="F124" s="50" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="G124" s="50" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="H124" s="50" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I124" s="50" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Base</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Bull</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="C125" s="50" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D125" s="50" t="n">
-        <v>-0.08</v>
+        <v>0.04</v>
       </c>
       <c r="E125" s="50" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F125" s="50" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="G125" s="50" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="H125" s="50" t="n">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I125" s="50" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bull</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - Taiwan</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="D126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="E126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="G126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="H126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I126" s="50" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  China domestic end-demand revenue change per year - Taiwan</t>
+          <t xml:space="preserve">  Non-GAAP opex growth - TaiwanMax</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>TaiwanMax</t>
         </is>
       </c>
       <c r="C127" s="50" t="n">
-        <v>-1</v>
+        <v>0.08</v>
       </c>
       <c r="D127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="E127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="G127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I127" s="50" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Bear: truce lapses Nov-26, xinchuang spreads from government to SOEs/finance/telecom, and origin rule hits 18A (US-fabbed) parts. Base: steady localization. Bull: truce holds, erosion slow</t>
+          <t xml:space="preserve">  Rationale: Bull spends more (AI GPU, foundry customer support)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion)</t>
+          <t>China domestic end-demand revenue change per year</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5675,7 +7330,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Bear</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bear</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -5684,31 +7339,31 @@
         </is>
       </c>
       <c r="C131" s="50" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="D131" s="50" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E131" s="50" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F131" s="50" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="G131" s="50" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="H131" s="50" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="I131" s="50" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Base</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Base</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -5717,31 +7372,31 @@
         </is>
       </c>
       <c r="C132" s="50" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="D132" s="50" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E132" s="50" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F132" s="50" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G132" s="50" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="H132" s="50" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I132" s="50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Bull</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Bull</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -5750,31 +7405,31 @@
         </is>
       </c>
       <c r="C133" s="50" t="n">
-        <v>0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="D133" s="50" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="E133" s="50" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F133" s="50" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="G133" s="50" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H133" s="50" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I133" s="50" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Taiwan</t>
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - Taiwan</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -5783,7 +7438,7 @@
         </is>
       </c>
       <c r="C134" s="50" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D134" s="50" t="n">
         <v>0</v>
@@ -5807,377 +7462,695 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: China server CPU prices +40% since Jan-26, 6-month lead times, multi-year supply deals with Chinese AI data centers; domestic CPUs can't fill AI-server demand near term. Fades as Hygon/Kunpeng scale</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
-        <is>
-          <t>CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn)</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
+          <t xml:space="preserve">  China domestic end-demand revenue change per year - TaiwanMax</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C135" s="50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: Bear: truce lapses Nov-26, xinchuang spreads from government to SOEs/finance/telecom, and origin rule hits 18A (US-fabbed) parts. Base: steady localization. Bull: truce holds, erosion slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion)</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E137" s="3" t="inlineStr">
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I137" s="3" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Bear</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="49" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Base</t>
+          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Bear</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C139" s="49" t="n">
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C139" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D139" s="49" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E139" s="49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F139" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G139" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="H139" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="I139" s="49" t="n">
-        <v>5</v>
+      <c r="D139" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Bull</t>
+          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Base</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="C140" s="49" t="n">
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C140" s="50" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D140" s="50" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E140" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D140" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="F140" s="49" t="n">
-        <v>6</v>
-      </c>
-      <c r="G140" s="49" t="n">
-        <v>9</v>
-      </c>
-      <c r="H140" s="49" t="n">
-        <v>11</v>
-      </c>
-      <c r="I140" s="49" t="n">
-        <v>12</v>
+      <c r="F140" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Taiwan</t>
+          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Bull</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="C141" s="49" t="n">
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C141" s="50" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D141" s="50" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E141" s="50" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F141" s="50" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G141" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="D141" s="49" t="n">
+      <c r="H141" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="E141" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G141" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="49" t="n">
+      <c r="I141" s="50" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Rationale: Sec. 232 25% tariff on advanced chips made outside US (Jan-26); Phase 2 'build in America or pay' + 1:1 rule + tariff offsets (Sep-26). Intel competes with TSMC Arizona and Samsung Taylor for this demand. Taiwan scenario already includes it</t>
-        </is>
+          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - Taiwan</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHINA TAILWIND 1: China AI-server demand boost to China domestic revenue (pts/yr, added to erosion) - TaiwanMax</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>Gross capex ($bn)</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: China server CPU prices +40% since Jan-26, 6-month lead times, multi-year supply deals with Chinese AI data centers; domestic CPUs can't fill AI-server demand near term. Fades as Hygon/Kunpeng scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn)</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="C144" s="3" t="inlineStr">
+      <c r="C146" s="3" t="inlineStr">
         <is>
           <t>2027</t>
         </is>
       </c>
-      <c r="D144" s="3" t="inlineStr">
+      <c r="D146" s="3" t="inlineStr">
         <is>
           <t>2028</t>
         </is>
       </c>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>2030</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>2031</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>2032</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>2033</t>
         </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="C145" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="D145" s="49" t="n">
-        <v>18</v>
-      </c>
-      <c r="E145" s="49" t="n">
-        <v>16</v>
-      </c>
-      <c r="F145" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="G145" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="H145" s="49" t="n">
-        <v>15</v>
-      </c>
-      <c r="I145" s="49" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="C146" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="D146" s="49" t="n">
-        <v>26</v>
-      </c>
-      <c r="E146" s="49" t="n">
-        <v>24</v>
-      </c>
-      <c r="F146" s="49" t="n">
-        <v>22</v>
-      </c>
-      <c r="G146" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="H146" s="49" t="n">
-        <v>20</v>
-      </c>
-      <c r="I146" s="49" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Bull</t>
+          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Bear</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C147" s="49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D147" s="49" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E147" s="49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F147" s="49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G147" s="49" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H147" s="49" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I147" s="49" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross capex ($bn) - Taiwan</t>
+          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Base</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C148" s="49" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D148" s="49" t="n">
-        <v>50</v>
+        <v>0.5</v>
       </c>
       <c r="E148" s="49" t="n">
-        <v>50</v>
+        <v>1.5</v>
       </c>
       <c r="F148" s="49" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G148" s="49" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H148" s="49" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="I148" s="49" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Bull</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C149" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D149" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F149" s="49" t="n">
+        <v>6</v>
+      </c>
+      <c r="G149" s="49" t="n">
+        <v>9</v>
+      </c>
+      <c r="H149" s="49" t="n">
+        <v>11</v>
+      </c>
+      <c r="I149" s="49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - Taiwan</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  CHINA TAILWIND 2: US onshoring / tariff-driven extra foundry revenue ($bn) - TaiwanMax</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rationale: Sec. 232 25% tariff on advanced chips made outside US (Jan-26); Phase 2 'build in America or pay' + 1:1 rule + tariff offsets (Sep-26). Intel competes with TSMC Arizona and Samsung Taylor for this demand. Taiwan scenario already includes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>Gross capex ($bn)</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>2031</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>2033</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Bear</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="C155" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="D155" s="49" t="n">
+        <v>18</v>
+      </c>
+      <c r="E155" s="49" t="n">
+        <v>16</v>
+      </c>
+      <c r="F155" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="G155" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="H155" s="49" t="n">
+        <v>15</v>
+      </c>
+      <c r="I155" s="49" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Base</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="C156" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="D156" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="E156" s="49" t="n">
+        <v>24</v>
+      </c>
+      <c r="F156" s="49" t="n">
+        <v>22</v>
+      </c>
+      <c r="G156" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="H156" s="49" t="n">
+        <v>20</v>
+      </c>
+      <c r="I156" s="49" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Bull</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="C157" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="D157" s="49" t="n">
+        <v>32</v>
+      </c>
+      <c r="E157" s="49" t="n">
+        <v>30</v>
+      </c>
+      <c r="F157" s="49" t="n">
+        <v>28</v>
+      </c>
+      <c r="G157" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="H157" s="49" t="n">
+        <v>26</v>
+      </c>
+      <c r="I157" s="49" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - Taiwan</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="C158" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="D158" s="49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E158" s="49" t="n">
+        <v>50</v>
+      </c>
+      <c r="F158" s="49" t="n">
+        <v>45</v>
+      </c>
+      <c r="G158" s="49" t="n">
+        <v>40</v>
+      </c>
+      <c r="H158" s="49" t="n">
+        <v>35</v>
+      </c>
+      <c r="I158" s="49" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Gross capex ($bn) - TaiwanMax</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>TaiwanMax</t>
+        </is>
+      </c>
+      <c r="C159" s="49" t="n">
+        <v>60</v>
+      </c>
+      <c r="D159" s="49" t="n">
+        <v>75</v>
+      </c>
+      <c r="E159" s="49" t="n">
+        <v>75</v>
+      </c>
+      <c r="F159" s="49" t="n">
+        <v>70</v>
+      </c>
+      <c r="G159" s="49" t="n">
+        <v>60</v>
+      </c>
+      <c r="H159" s="49" t="n">
+        <v>55</v>
+      </c>
+      <c r="I159" s="49" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  Rationale: 2027 guided 'significantly above' 2026 (&gt;$20bn). Gross; excludes SCIP partner/government offsets (conservative)</t>
         </is>
@@ -6194,7 +8167,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6349,31 +8322,31 @@
         </is>
       </c>
       <c r="C6" s="35">
-        <f>Inputs!C89+Inputs!$B$72</f>
+        <f>Inputs!C91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="35">
-        <f>Inputs!D89+Inputs!$B$72</f>
+        <f>Inputs!D91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="35">
-        <f>Inputs!E89+Inputs!$B$72</f>
+        <f>Inputs!E91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>Inputs!F89+Inputs!$B$72</f>
+        <f>Inputs!F91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>Inputs!G89+Inputs!$B$72</f>
+        <f>Inputs!G91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>Inputs!H89+Inputs!$B$72</f>
+        <f>Inputs!H91+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>Inputs!I89+Inputs!$B$72</f>
+        <f>Inputs!I91+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -6423,31 +8396,31 @@
         </is>
       </c>
       <c r="C8" s="35">
-        <f>Inputs!C96</f>
+        <f>Inputs!C99</f>
         <v/>
       </c>
       <c r="D8" s="35">
-        <f>Inputs!D96</f>
+        <f>Inputs!D99</f>
         <v/>
       </c>
       <c r="E8" s="35">
-        <f>Inputs!E96</f>
+        <f>Inputs!E99</f>
         <v/>
       </c>
       <c r="F8" s="35">
-        <f>Inputs!F96</f>
+        <f>Inputs!F99</f>
         <v/>
       </c>
       <c r="G8" s="35">
-        <f>Inputs!G96</f>
+        <f>Inputs!G99</f>
         <v/>
       </c>
       <c r="H8" s="35">
-        <f>Inputs!H96</f>
+        <f>Inputs!H99</f>
         <v/>
       </c>
       <c r="I8" s="35">
-        <f>Inputs!I96</f>
+        <f>Inputs!I99</f>
         <v/>
       </c>
     </row>
@@ -6462,31 +8435,31 @@
         <v/>
       </c>
       <c r="C9" s="39">
-        <f>Inputs!C103*Inputs!$B$73</f>
+        <f>Inputs!C107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="39">
-        <f>Inputs!D103*Inputs!$B$73</f>
+        <f>Inputs!D107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>Inputs!E103*Inputs!$B$73</f>
+        <f>Inputs!E107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="39">
-        <f>Inputs!F103*Inputs!$B$73</f>
+        <f>Inputs!F107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="39">
-        <f>Inputs!G103*Inputs!$B$73</f>
+        <f>Inputs!G107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="39">
-        <f>Inputs!H103*Inputs!$B$73</f>
+        <f>Inputs!H107*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="39">
-        <f>Inputs!I103*Inputs!$B$73</f>
+        <f>Inputs!I107*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -6500,31 +8473,31 @@
         <v>0</v>
       </c>
       <c r="C10" s="39">
-        <f>Inputs!$B$77*Inputs!C138</f>
+        <f>Inputs!$B$78*Inputs!C147</f>
         <v/>
       </c>
       <c r="D10" s="39">
-        <f>Inputs!$B$77*Inputs!D138</f>
+        <f>Inputs!$B$78*Inputs!D147</f>
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>Inputs!$B$77*Inputs!E138</f>
+        <f>Inputs!$B$78*Inputs!E147</f>
         <v/>
       </c>
       <c r="F10" s="39">
-        <f>Inputs!$B$77*Inputs!F138</f>
+        <f>Inputs!$B$78*Inputs!F147</f>
         <v/>
       </c>
       <c r="G10" s="39">
-        <f>Inputs!$B$77*Inputs!G138</f>
+        <f>Inputs!$B$78*Inputs!G147</f>
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>Inputs!$B$77*Inputs!H138</f>
+        <f>Inputs!$B$78*Inputs!H147</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>Inputs!$B$77*Inputs!I138</f>
+        <f>Inputs!$B$78*Inputs!I147</f>
         <v/>
       </c>
     </row>
@@ -6616,31 +8589,31 @@
         <v>1</v>
       </c>
       <c r="C13" s="31">
-        <f>MAX(0,B13*(1+Inputs!C124+Inputs!$B$77*Inputs!C131+Inputs!$B$75))</f>
+        <f>MAX(0,B13*(1+Inputs!C131+Inputs!$B$78*Inputs!C139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>MAX(0,C13*(1+Inputs!D124+Inputs!$B$77*Inputs!D131+Inputs!$B$75))</f>
+        <f>MAX(0,C13*(1+Inputs!D131+Inputs!$B$78*Inputs!D139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>MAX(0,D13*(1+Inputs!E124+Inputs!$B$77*Inputs!E131+Inputs!$B$75))</f>
+        <f>MAX(0,D13*(1+Inputs!E131+Inputs!$B$78*Inputs!E139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>MAX(0,E13*(1+Inputs!F124+Inputs!$B$77*Inputs!F131+Inputs!$B$75))</f>
+        <f>MAX(0,E13*(1+Inputs!F131+Inputs!$B$78*Inputs!F139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>MAX(0,F13*(1+Inputs!G124+Inputs!$B$77*Inputs!G131+Inputs!$B$75))</f>
+        <f>MAX(0,F13*(1+Inputs!G131+Inputs!$B$78*Inputs!G139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>MAX(0,G13*(1+Inputs!H124+Inputs!$B$77*Inputs!H131+Inputs!$B$75))</f>
+        <f>MAX(0,G13*(1+Inputs!H131+Inputs!$B$78*Inputs!H139+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>MAX(0,H13*(1+Inputs!I124+Inputs!$B$77*Inputs!I131+Inputs!$B$75))</f>
+        <f>MAX(0,H13*(1+Inputs!I131+Inputs!$B$78*Inputs!I139+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -6772,31 +8745,31 @@
         <v/>
       </c>
       <c r="C17" s="35">
-        <f>Inputs!C110+Inputs!$B$71</f>
+        <f>Inputs!C115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D17" s="35">
-        <f>Inputs!D110+Inputs!$B$71</f>
+        <f>Inputs!D115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E17" s="35">
-        <f>Inputs!E110+Inputs!$B$71</f>
+        <f>Inputs!E115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F17" s="35">
-        <f>Inputs!F110+Inputs!$B$71</f>
+        <f>Inputs!F115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G17" s="35">
-        <f>Inputs!G110+Inputs!$B$71</f>
+        <f>Inputs!G115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H17" s="35">
-        <f>Inputs!H110+Inputs!$B$71</f>
+        <f>Inputs!H115+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I17" s="35">
-        <f>Inputs!I110+Inputs!$B$71</f>
+        <f>Inputs!I115+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -6850,31 +8823,31 @@
         <v/>
       </c>
       <c r="C19" s="41">
-        <f>B19*(1+Inputs!C117)</f>
+        <f>B19*(1+Inputs!C123)</f>
         <v/>
       </c>
       <c r="D19" s="41">
-        <f>C19*(1+Inputs!D117)</f>
+        <f>C19*(1+Inputs!D123)</f>
         <v/>
       </c>
       <c r="E19" s="41">
-        <f>D19*(1+Inputs!E117)</f>
+        <f>D19*(1+Inputs!E123)</f>
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>E19*(1+Inputs!F117)</f>
+        <f>E19*(1+Inputs!F123)</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>F19*(1+Inputs!G117)</f>
+        <f>F19*(1+Inputs!G123)</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>G19*(1+Inputs!H117)</f>
+        <f>G19*(1+Inputs!H123)</f>
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>H19*(1+Inputs!I117)</f>
+        <f>H19*(1+Inputs!I123)</f>
         <v/>
       </c>
     </row>
@@ -6968,31 +8941,31 @@
         <v/>
       </c>
       <c r="C22" s="41">
-        <f>B22*(1+Inputs!C117)</f>
+        <f>B22*(1+Inputs!C123)</f>
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>C22*(1+Inputs!D117)</f>
+        <f>C22*(1+Inputs!D123)</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>D22*(1+Inputs!E117)</f>
+        <f>D22*(1+Inputs!E123)</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>E22*(1+Inputs!F117)</f>
+        <f>E22*(1+Inputs!F123)</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>F22*(1+Inputs!G117)</f>
+        <f>F22*(1+Inputs!G123)</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>G22*(1+Inputs!H117)</f>
+        <f>G22*(1+Inputs!H123)</f>
         <v/>
       </c>
       <c r="I22" s="41">
-        <f>H22*(1+Inputs!I117)</f>
+        <f>H22*(1+Inputs!I123)</f>
         <v/>
       </c>
     </row>
@@ -7159,31 +9132,31 @@
         <v/>
       </c>
       <c r="C27" s="39">
-        <f>Inputs!C145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!C155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="D27" s="39">
-        <f>Inputs!D145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!D155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>Inputs!E145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!E155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>Inputs!F145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!F155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="G27" s="39">
-        <f>Inputs!G145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!G155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="H27" s="39">
-        <f>Inputs!H145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!H155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="I27" s="39">
-        <f>Inputs!I145*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!I155*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="J27" s="41">
@@ -7464,90 +9437,101 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- Payment for TSMC Arizona assets (TaiwanMax only)</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="41">
-        <f>B38+B39+B40+B41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B43" s="41">
+        <f>B38+B39+B40+B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Diluted shares (bn)</t>
         </is>
       </c>
-      <c r="B43" s="40">
+      <c r="B44" s="40">
         <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Value per share ($)</t>
         </is>
       </c>
-      <c r="B44" s="37">
-        <f>IF(B43=0,0,MAX(0,B42/B43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B45" s="36">
-        <f>Inputs!$B$4</f>
+      <c r="B45" s="37">
+        <f>IF(B44=0,0,MAX(0,B43/B44))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B46" s="42">
-        <f>IF(B45=0,0,B44/B45-1)</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Terminal value as % of EV</t>
+          <t>Upside / (downside) vs price</t>
         </is>
       </c>
       <c r="B47" s="42">
-        <f>IF(B38=0,0,B37/B38)</f>
+        <f>IF(B46=0,0,B45/B46-1)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B48" s="11">
-        <f>IF(C25&lt;=0,0,B44/(C25/B43))</f>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B48" s="42">
+        <f>IF(B38=0,0,B37/B38)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(C25&lt;=0,0,B45/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B49" s="11">
-        <f>IF(C25&lt;=0,0,B45/(C25/B43))</f>
+      <c r="B50" s="11">
+        <f>IF(C25&lt;=0,0,B46/(C25/B44))</f>
         <v/>
       </c>
     </row>
@@ -7718,31 +9702,31 @@
         </is>
       </c>
       <c r="C6" s="35">
-        <f>Inputs!C90+Inputs!$B$72</f>
+        <f>Inputs!C92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="35">
-        <f>Inputs!D90+Inputs!$B$72</f>
+        <f>Inputs!D92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="35">
-        <f>Inputs!E90+Inputs!$B$72</f>
+        <f>Inputs!E92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>Inputs!F90+Inputs!$B$72</f>
+        <f>Inputs!F92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>Inputs!G90+Inputs!$B$72</f>
+        <f>Inputs!G92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>Inputs!H90+Inputs!$B$72</f>
+        <f>Inputs!H92+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>Inputs!I90+Inputs!$B$72</f>
+        <f>Inputs!I92+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -7792,31 +9776,31 @@
         </is>
       </c>
       <c r="C8" s="35">
-        <f>Inputs!C97</f>
+        <f>Inputs!C100</f>
         <v/>
       </c>
       <c r="D8" s="35">
-        <f>Inputs!D97</f>
+        <f>Inputs!D100</f>
         <v/>
       </c>
       <c r="E8" s="35">
-        <f>Inputs!E97</f>
+        <f>Inputs!E100</f>
         <v/>
       </c>
       <c r="F8" s="35">
-        <f>Inputs!F97</f>
+        <f>Inputs!F100</f>
         <v/>
       </c>
       <c r="G8" s="35">
-        <f>Inputs!G97</f>
+        <f>Inputs!G100</f>
         <v/>
       </c>
       <c r="H8" s="35">
-        <f>Inputs!H97</f>
+        <f>Inputs!H100</f>
         <v/>
       </c>
       <c r="I8" s="35">
-        <f>Inputs!I97</f>
+        <f>Inputs!I100</f>
         <v/>
       </c>
     </row>
@@ -7831,31 +9815,31 @@
         <v/>
       </c>
       <c r="C9" s="39">
-        <f>Inputs!C104*Inputs!$B$73</f>
+        <f>Inputs!C108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="39">
-        <f>Inputs!D104*Inputs!$B$73</f>
+        <f>Inputs!D108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>Inputs!E104*Inputs!$B$73</f>
+        <f>Inputs!E108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="39">
-        <f>Inputs!F104*Inputs!$B$73</f>
+        <f>Inputs!F108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="39">
-        <f>Inputs!G104*Inputs!$B$73</f>
+        <f>Inputs!G108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="39">
-        <f>Inputs!H104*Inputs!$B$73</f>
+        <f>Inputs!H108*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="39">
-        <f>Inputs!I104*Inputs!$B$73</f>
+        <f>Inputs!I108*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -7869,31 +9853,31 @@
         <v>0</v>
       </c>
       <c r="C10" s="39">
-        <f>Inputs!$B$77*Inputs!C139</f>
+        <f>Inputs!$B$78*Inputs!C148</f>
         <v/>
       </c>
       <c r="D10" s="39">
-        <f>Inputs!$B$77*Inputs!D139</f>
+        <f>Inputs!$B$78*Inputs!D148</f>
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>Inputs!$B$77*Inputs!E139</f>
+        <f>Inputs!$B$78*Inputs!E148</f>
         <v/>
       </c>
       <c r="F10" s="39">
-        <f>Inputs!$B$77*Inputs!F139</f>
+        <f>Inputs!$B$78*Inputs!F148</f>
         <v/>
       </c>
       <c r="G10" s="39">
-        <f>Inputs!$B$77*Inputs!G139</f>
+        <f>Inputs!$B$78*Inputs!G148</f>
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>Inputs!$B$77*Inputs!H139</f>
+        <f>Inputs!$B$78*Inputs!H148</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>Inputs!$B$77*Inputs!I139</f>
+        <f>Inputs!$B$78*Inputs!I148</f>
         <v/>
       </c>
     </row>
@@ -7985,31 +9969,31 @@
         <v>1</v>
       </c>
       <c r="C13" s="31">
-        <f>MAX(0,B13*(1+Inputs!C125+Inputs!$B$77*Inputs!C132+Inputs!$B$75))</f>
+        <f>MAX(0,B13*(1+Inputs!C132+Inputs!$B$78*Inputs!C140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>MAX(0,C13*(1+Inputs!D125+Inputs!$B$77*Inputs!D132+Inputs!$B$75))</f>
+        <f>MAX(0,C13*(1+Inputs!D132+Inputs!$B$78*Inputs!D140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>MAX(0,D13*(1+Inputs!E125+Inputs!$B$77*Inputs!E132+Inputs!$B$75))</f>
+        <f>MAX(0,D13*(1+Inputs!E132+Inputs!$B$78*Inputs!E140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>MAX(0,E13*(1+Inputs!F125+Inputs!$B$77*Inputs!F132+Inputs!$B$75))</f>
+        <f>MAX(0,E13*(1+Inputs!F132+Inputs!$B$78*Inputs!F140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>MAX(0,F13*(1+Inputs!G125+Inputs!$B$77*Inputs!G132+Inputs!$B$75))</f>
+        <f>MAX(0,F13*(1+Inputs!G132+Inputs!$B$78*Inputs!G140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>MAX(0,G13*(1+Inputs!H125+Inputs!$B$77*Inputs!H132+Inputs!$B$75))</f>
+        <f>MAX(0,G13*(1+Inputs!H132+Inputs!$B$78*Inputs!H140+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>MAX(0,H13*(1+Inputs!I125+Inputs!$B$77*Inputs!I132+Inputs!$B$75))</f>
+        <f>MAX(0,H13*(1+Inputs!I132+Inputs!$B$78*Inputs!I140+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -8141,31 +10125,31 @@
         <v/>
       </c>
       <c r="C17" s="35">
-        <f>Inputs!C111+Inputs!$B$71</f>
+        <f>Inputs!C116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D17" s="35">
-        <f>Inputs!D111+Inputs!$B$71</f>
+        <f>Inputs!D116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E17" s="35">
-        <f>Inputs!E111+Inputs!$B$71</f>
+        <f>Inputs!E116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F17" s="35">
-        <f>Inputs!F111+Inputs!$B$71</f>
+        <f>Inputs!F116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G17" s="35">
-        <f>Inputs!G111+Inputs!$B$71</f>
+        <f>Inputs!G116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H17" s="35">
-        <f>Inputs!H111+Inputs!$B$71</f>
+        <f>Inputs!H116+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I17" s="35">
-        <f>Inputs!I111+Inputs!$B$71</f>
+        <f>Inputs!I116+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -8219,31 +10203,31 @@
         <v/>
       </c>
       <c r="C19" s="41">
-        <f>B19*(1+Inputs!C118)</f>
+        <f>B19*(1+Inputs!C124)</f>
         <v/>
       </c>
       <c r="D19" s="41">
-        <f>C19*(1+Inputs!D118)</f>
+        <f>C19*(1+Inputs!D124)</f>
         <v/>
       </c>
       <c r="E19" s="41">
-        <f>D19*(1+Inputs!E118)</f>
+        <f>D19*(1+Inputs!E124)</f>
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>E19*(1+Inputs!F118)</f>
+        <f>E19*(1+Inputs!F124)</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>F19*(1+Inputs!G118)</f>
+        <f>F19*(1+Inputs!G124)</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>G19*(1+Inputs!H118)</f>
+        <f>G19*(1+Inputs!H124)</f>
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>H19*(1+Inputs!I118)</f>
+        <f>H19*(1+Inputs!I124)</f>
         <v/>
       </c>
     </row>
@@ -8337,31 +10321,31 @@
         <v/>
       </c>
       <c r="C22" s="41">
-        <f>B22*(1+Inputs!C118)</f>
+        <f>B22*(1+Inputs!C124)</f>
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>C22*(1+Inputs!D118)</f>
+        <f>C22*(1+Inputs!D124)</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>D22*(1+Inputs!E118)</f>
+        <f>D22*(1+Inputs!E124)</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>E22*(1+Inputs!F118)</f>
+        <f>E22*(1+Inputs!F124)</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>F22*(1+Inputs!G118)</f>
+        <f>F22*(1+Inputs!G124)</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>G22*(1+Inputs!H118)</f>
+        <f>G22*(1+Inputs!H124)</f>
         <v/>
       </c>
       <c r="I22" s="41">
-        <f>H22*(1+Inputs!I118)</f>
+        <f>H22*(1+Inputs!I124)</f>
         <v/>
       </c>
     </row>
@@ -8528,31 +10512,31 @@
         <v/>
       </c>
       <c r="C27" s="39">
-        <f>Inputs!C146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!C156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="D27" s="39">
-        <f>Inputs!D146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!D156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>Inputs!E146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!E156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>Inputs!F146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!F156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="G27" s="39">
-        <f>Inputs!G146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!G156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="H27" s="39">
-        <f>Inputs!H146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!H156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="I27" s="39">
-        <f>Inputs!I146*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!I156*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="J27" s="41">
@@ -8834,94 +10818,104 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- Payment for TSMC Arizona assets (TaiwanMax only)</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="41">
-        <f>B38+B39+B40+B41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B43" s="41">
+        <f>B38+B39+B40+B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Diluted shares (bn)</t>
         </is>
       </c>
-      <c r="B43" s="40">
+      <c r="B44" s="40">
         <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Value per share ($)</t>
         </is>
       </c>
-      <c r="B44" s="37">
-        <f>IF(B43=0,0,MAX(0,B42/B43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B45" s="36">
-        <f>Inputs!$B$4</f>
+      <c r="B45" s="37">
+        <f>IF(B44=0,0,MAX(0,B43/B44))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B46" s="42">
-        <f>IF(B45=0,0,B44/B45-1)</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Terminal value as % of EV</t>
+          <t>Upside / (downside) vs price</t>
         </is>
       </c>
       <c r="B47" s="42">
-        <f>IF(B38=0,0,B37/B38)</f>
+        <f>IF(B46=0,0,B45/B46-1)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B48" s="11">
-        <f>IF(C25&lt;=0,0,B44/(C25/B43))</f>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B48" s="42">
+        <f>IF(B38=0,0,B37/B38)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(C25&lt;=0,0,B45/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B49" s="11">
-        <f>IF(C25&lt;=0,0,B45/(C25/B43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50"/>
+      <c r="B50" s="11">
+        <f>IF(C25&lt;=0,0,B46/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
     <row r="51"/>
     <row r="52"/>
     <row r="53"/>
@@ -8962,7 +10956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -9117,31 +11111,31 @@
         </is>
       </c>
       <c r="C6" s="35">
-        <f>Inputs!C91+Inputs!$B$72</f>
+        <f>Inputs!C93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="35">
-        <f>Inputs!D91+Inputs!$B$72</f>
+        <f>Inputs!D93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="35">
-        <f>Inputs!E91+Inputs!$B$72</f>
+        <f>Inputs!E93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>Inputs!F91+Inputs!$B$72</f>
+        <f>Inputs!F93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>Inputs!G91+Inputs!$B$72</f>
+        <f>Inputs!G93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>Inputs!H91+Inputs!$B$72</f>
+        <f>Inputs!H93+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>Inputs!I91+Inputs!$B$72</f>
+        <f>Inputs!I93+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -9191,31 +11185,31 @@
         </is>
       </c>
       <c r="C8" s="35">
-        <f>Inputs!C98</f>
+        <f>Inputs!C101</f>
         <v/>
       </c>
       <c r="D8" s="35">
-        <f>Inputs!D98</f>
+        <f>Inputs!D101</f>
         <v/>
       </c>
       <c r="E8" s="35">
-        <f>Inputs!E98</f>
+        <f>Inputs!E101</f>
         <v/>
       </c>
       <c r="F8" s="35">
-        <f>Inputs!F98</f>
+        <f>Inputs!F101</f>
         <v/>
       </c>
       <c r="G8" s="35">
-        <f>Inputs!G98</f>
+        <f>Inputs!G101</f>
         <v/>
       </c>
       <c r="H8" s="35">
-        <f>Inputs!H98</f>
+        <f>Inputs!H101</f>
         <v/>
       </c>
       <c r="I8" s="35">
-        <f>Inputs!I98</f>
+        <f>Inputs!I101</f>
         <v/>
       </c>
     </row>
@@ -9230,31 +11224,31 @@
         <v/>
       </c>
       <c r="C9" s="39">
-        <f>Inputs!C105*Inputs!$B$73</f>
+        <f>Inputs!C109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="39">
-        <f>Inputs!D105*Inputs!$B$73</f>
+        <f>Inputs!D109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>Inputs!E105*Inputs!$B$73</f>
+        <f>Inputs!E109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="39">
-        <f>Inputs!F105*Inputs!$B$73</f>
+        <f>Inputs!F109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="39">
-        <f>Inputs!G105*Inputs!$B$73</f>
+        <f>Inputs!G109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="39">
-        <f>Inputs!H105*Inputs!$B$73</f>
+        <f>Inputs!H109*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="39">
-        <f>Inputs!I105*Inputs!$B$73</f>
+        <f>Inputs!I109*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -9268,31 +11262,31 @@
         <v>0</v>
       </c>
       <c r="C10" s="39">
-        <f>Inputs!$B$77*Inputs!C140</f>
+        <f>Inputs!$B$78*Inputs!C149</f>
         <v/>
       </c>
       <c r="D10" s="39">
-        <f>Inputs!$B$77*Inputs!D140</f>
+        <f>Inputs!$B$78*Inputs!D149</f>
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>Inputs!$B$77*Inputs!E140</f>
+        <f>Inputs!$B$78*Inputs!E149</f>
         <v/>
       </c>
       <c r="F10" s="39">
-        <f>Inputs!$B$77*Inputs!F140</f>
+        <f>Inputs!$B$78*Inputs!F149</f>
         <v/>
       </c>
       <c r="G10" s="39">
-        <f>Inputs!$B$77*Inputs!G140</f>
+        <f>Inputs!$B$78*Inputs!G149</f>
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>Inputs!$B$77*Inputs!H140</f>
+        <f>Inputs!$B$78*Inputs!H149</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>Inputs!$B$77*Inputs!I140</f>
+        <f>Inputs!$B$78*Inputs!I149</f>
         <v/>
       </c>
     </row>
@@ -9384,31 +11378,31 @@
         <v>1</v>
       </c>
       <c r="C13" s="31">
-        <f>MAX(0,B13*(1+Inputs!C126+Inputs!$B$77*Inputs!C133+Inputs!$B$75))</f>
+        <f>MAX(0,B13*(1+Inputs!C133+Inputs!$B$78*Inputs!C141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>MAX(0,C13*(1+Inputs!D126+Inputs!$B$77*Inputs!D133+Inputs!$B$75))</f>
+        <f>MAX(0,C13*(1+Inputs!D133+Inputs!$B$78*Inputs!D141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>MAX(0,D13*(1+Inputs!E126+Inputs!$B$77*Inputs!E133+Inputs!$B$75))</f>
+        <f>MAX(0,D13*(1+Inputs!E133+Inputs!$B$78*Inputs!E141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>MAX(0,E13*(1+Inputs!F126+Inputs!$B$77*Inputs!F133+Inputs!$B$75))</f>
+        <f>MAX(0,E13*(1+Inputs!F133+Inputs!$B$78*Inputs!F141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>MAX(0,F13*(1+Inputs!G126+Inputs!$B$77*Inputs!G133+Inputs!$B$75))</f>
+        <f>MAX(0,F13*(1+Inputs!G133+Inputs!$B$78*Inputs!G141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>MAX(0,G13*(1+Inputs!H126+Inputs!$B$77*Inputs!H133+Inputs!$B$75))</f>
+        <f>MAX(0,G13*(1+Inputs!H133+Inputs!$B$78*Inputs!H141+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>MAX(0,H13*(1+Inputs!I126+Inputs!$B$77*Inputs!I133+Inputs!$B$75))</f>
+        <f>MAX(0,H13*(1+Inputs!I133+Inputs!$B$78*Inputs!I141+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -9540,31 +11534,31 @@
         <v/>
       </c>
       <c r="C17" s="35">
-        <f>Inputs!C112+Inputs!$B$71</f>
+        <f>Inputs!C117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D17" s="35">
-        <f>Inputs!D112+Inputs!$B$71</f>
+        <f>Inputs!D117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E17" s="35">
-        <f>Inputs!E112+Inputs!$B$71</f>
+        <f>Inputs!E117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F17" s="35">
-        <f>Inputs!F112+Inputs!$B$71</f>
+        <f>Inputs!F117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G17" s="35">
-        <f>Inputs!G112+Inputs!$B$71</f>
+        <f>Inputs!G117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H17" s="35">
-        <f>Inputs!H112+Inputs!$B$71</f>
+        <f>Inputs!H117+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I17" s="35">
-        <f>Inputs!I112+Inputs!$B$71</f>
+        <f>Inputs!I117+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -9618,31 +11612,31 @@
         <v/>
       </c>
       <c r="C19" s="41">
-        <f>B19*(1+Inputs!C119)</f>
+        <f>B19*(1+Inputs!C125)</f>
         <v/>
       </c>
       <c r="D19" s="41">
-        <f>C19*(1+Inputs!D119)</f>
+        <f>C19*(1+Inputs!D125)</f>
         <v/>
       </c>
       <c r="E19" s="41">
-        <f>D19*(1+Inputs!E119)</f>
+        <f>D19*(1+Inputs!E125)</f>
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>E19*(1+Inputs!F119)</f>
+        <f>E19*(1+Inputs!F125)</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>F19*(1+Inputs!G119)</f>
+        <f>F19*(1+Inputs!G125)</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>G19*(1+Inputs!H119)</f>
+        <f>G19*(1+Inputs!H125)</f>
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>H19*(1+Inputs!I119)</f>
+        <f>H19*(1+Inputs!I125)</f>
         <v/>
       </c>
     </row>
@@ -9736,31 +11730,31 @@
         <v/>
       </c>
       <c r="C22" s="41">
-        <f>B22*(1+Inputs!C119)</f>
+        <f>B22*(1+Inputs!C125)</f>
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>C22*(1+Inputs!D119)</f>
+        <f>C22*(1+Inputs!D125)</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>D22*(1+Inputs!E119)</f>
+        <f>D22*(1+Inputs!E125)</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>E22*(1+Inputs!F119)</f>
+        <f>E22*(1+Inputs!F125)</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>F22*(1+Inputs!G119)</f>
+        <f>F22*(1+Inputs!G125)</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>G22*(1+Inputs!H119)</f>
+        <f>G22*(1+Inputs!H125)</f>
         <v/>
       </c>
       <c r="I22" s="41">
-        <f>H22*(1+Inputs!I119)</f>
+        <f>H22*(1+Inputs!I125)</f>
         <v/>
       </c>
     </row>
@@ -9927,31 +11921,31 @@
         <v/>
       </c>
       <c r="C27" s="39">
-        <f>Inputs!C147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!C157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="D27" s="39">
-        <f>Inputs!D147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!D157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>Inputs!E147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!E157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>Inputs!F147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!F157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="G27" s="39">
-        <f>Inputs!G147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!G157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="H27" s="39">
-        <f>Inputs!H147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!H157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="I27" s="39">
-        <f>Inputs!I147*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!I157*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="J27" s="41">
@@ -10232,90 +12226,101 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- Payment for TSMC Arizona assets (TaiwanMax only)</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="41">
-        <f>B38+B39+B40+B41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B43" s="41">
+        <f>B38+B39+B40+B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Diluted shares (bn)</t>
         </is>
       </c>
-      <c r="B43" s="40">
+      <c r="B44" s="40">
         <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Value per share ($)</t>
         </is>
       </c>
-      <c r="B44" s="37">
-        <f>IF(B43=0,0,MAX(0,B42/B43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B45" s="36">
-        <f>Inputs!$B$4</f>
+      <c r="B45" s="37">
+        <f>IF(B44=0,0,MAX(0,B43/B44))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B46" s="42">
-        <f>IF(B45=0,0,B44/B45-1)</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Terminal value as % of EV</t>
+          <t>Upside / (downside) vs price</t>
         </is>
       </c>
       <c r="B47" s="42">
-        <f>IF(B38=0,0,B37/B38)</f>
+        <f>IF(B46=0,0,B45/B46-1)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B48" s="11">
-        <f>IF(C25&lt;=0,0,B44/(C25/B43))</f>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B48" s="42">
+        <f>IF(B38=0,0,B37/B38)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(C25&lt;=0,0,B45/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B49" s="11">
-        <f>IF(C25&lt;=0,0,B45/(C25/B43))</f>
+      <c r="B50" s="11">
+        <f>IF(C25&lt;=0,0,B46/(C25/B44))</f>
         <v/>
       </c>
     </row>
@@ -10330,7 +12335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -10485,31 +12490,31 @@
         </is>
       </c>
       <c r="C6" s="35">
-        <f>Inputs!C92+Inputs!$B$72</f>
+        <f>Inputs!C94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="D6" s="35">
-        <f>Inputs!D92+Inputs!$B$72</f>
+        <f>Inputs!D94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="E6" s="35">
-        <f>Inputs!E92+Inputs!$B$72</f>
+        <f>Inputs!E94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="F6" s="35">
-        <f>Inputs!F92+Inputs!$B$72</f>
+        <f>Inputs!F94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="G6" s="35">
-        <f>Inputs!G92+Inputs!$B$72</f>
+        <f>Inputs!G94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="H6" s="35">
-        <f>Inputs!H92+Inputs!$B$72</f>
+        <f>Inputs!H94+Inputs!$B$72</f>
         <v/>
       </c>
       <c r="I6" s="35">
-        <f>Inputs!I92+Inputs!$B$72</f>
+        <f>Inputs!I94+Inputs!$B$72</f>
         <v/>
       </c>
     </row>
@@ -10559,31 +12564,31 @@
         </is>
       </c>
       <c r="C8" s="35">
-        <f>Inputs!C99</f>
+        <f>Inputs!C102</f>
         <v/>
       </c>
       <c r="D8" s="35">
-        <f>Inputs!D99</f>
+        <f>Inputs!D102</f>
         <v/>
       </c>
       <c r="E8" s="35">
-        <f>Inputs!E99</f>
+        <f>Inputs!E102</f>
         <v/>
       </c>
       <c r="F8" s="35">
-        <f>Inputs!F99</f>
+        <f>Inputs!F102</f>
         <v/>
       </c>
       <c r="G8" s="35">
-        <f>Inputs!G99</f>
+        <f>Inputs!G102</f>
         <v/>
       </c>
       <c r="H8" s="35">
-        <f>Inputs!H99</f>
+        <f>Inputs!H102</f>
         <v/>
       </c>
       <c r="I8" s="35">
-        <f>Inputs!I99</f>
+        <f>Inputs!I102</f>
         <v/>
       </c>
     </row>
@@ -10598,31 +12603,31 @@
         <v/>
       </c>
       <c r="C9" s="39">
-        <f>Inputs!C106*Inputs!$B$73</f>
+        <f>Inputs!C110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="D9" s="39">
-        <f>Inputs!D106*Inputs!$B$73</f>
+        <f>Inputs!D110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>Inputs!E106*Inputs!$B$73</f>
+        <f>Inputs!E110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="F9" s="39">
-        <f>Inputs!F106*Inputs!$B$73</f>
+        <f>Inputs!F110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="G9" s="39">
-        <f>Inputs!G106*Inputs!$B$73</f>
+        <f>Inputs!G110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="H9" s="39">
-        <f>Inputs!H106*Inputs!$B$73</f>
+        <f>Inputs!H110*Inputs!$B$73</f>
         <v/>
       </c>
       <c r="I9" s="39">
-        <f>Inputs!I106*Inputs!$B$73</f>
+        <f>Inputs!I110*Inputs!$B$73</f>
         <v/>
       </c>
     </row>
@@ -10636,31 +12641,31 @@
         <v>0</v>
       </c>
       <c r="C10" s="39">
-        <f>Inputs!$B$77*Inputs!C141</f>
+        <f>Inputs!$B$78*Inputs!C150</f>
         <v/>
       </c>
       <c r="D10" s="39">
-        <f>Inputs!$B$77*Inputs!D141</f>
+        <f>Inputs!$B$78*Inputs!D150</f>
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>Inputs!$B$77*Inputs!E141</f>
+        <f>Inputs!$B$78*Inputs!E150</f>
         <v/>
       </c>
       <c r="F10" s="39">
-        <f>Inputs!$B$77*Inputs!F141</f>
+        <f>Inputs!$B$78*Inputs!F150</f>
         <v/>
       </c>
       <c r="G10" s="39">
-        <f>Inputs!$B$77*Inputs!G141</f>
+        <f>Inputs!$B$78*Inputs!G150</f>
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>Inputs!$B$77*Inputs!H141</f>
+        <f>Inputs!$B$78*Inputs!H150</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>Inputs!$B$77*Inputs!I141</f>
+        <f>Inputs!$B$78*Inputs!I150</f>
         <v/>
       </c>
     </row>
@@ -10752,31 +12757,31 @@
         <v>1</v>
       </c>
       <c r="C13" s="31">
-        <f>MAX(0,B13*(1+Inputs!C127+Inputs!$B$77*Inputs!C134+Inputs!$B$75))</f>
+        <f>MAX(0,B13*(1+Inputs!C134+Inputs!$B$78*Inputs!C142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="D13" s="31">
-        <f>MAX(0,C13*(1+Inputs!D127+Inputs!$B$77*Inputs!D134+Inputs!$B$75))</f>
+        <f>MAX(0,C13*(1+Inputs!D134+Inputs!$B$78*Inputs!D142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="E13" s="31">
-        <f>MAX(0,D13*(1+Inputs!E127+Inputs!$B$77*Inputs!E134+Inputs!$B$75))</f>
+        <f>MAX(0,D13*(1+Inputs!E134+Inputs!$B$78*Inputs!E142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="F13" s="31">
-        <f>MAX(0,E13*(1+Inputs!F127+Inputs!$B$77*Inputs!F134+Inputs!$B$75))</f>
+        <f>MAX(0,E13*(1+Inputs!F134+Inputs!$B$78*Inputs!F142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="G13" s="31">
-        <f>MAX(0,F13*(1+Inputs!G127+Inputs!$B$77*Inputs!G134+Inputs!$B$75))</f>
+        <f>MAX(0,F13*(1+Inputs!G134+Inputs!$B$78*Inputs!G142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="H13" s="31">
-        <f>MAX(0,G13*(1+Inputs!H127+Inputs!$B$77*Inputs!H134+Inputs!$B$75))</f>
+        <f>MAX(0,G13*(1+Inputs!H134+Inputs!$B$78*Inputs!H142+Inputs!$B$75))</f>
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>MAX(0,H13*(1+Inputs!I127+Inputs!$B$77*Inputs!I134+Inputs!$B$75))</f>
+        <f>MAX(0,H13*(1+Inputs!I134+Inputs!$B$78*Inputs!I142+Inputs!$B$75))</f>
         <v/>
       </c>
     </row>
@@ -10908,31 +12913,31 @@
         <v/>
       </c>
       <c r="C17" s="35">
-        <f>Inputs!C113+Inputs!$B$71</f>
+        <f>Inputs!C118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="D17" s="35">
-        <f>Inputs!D113+Inputs!$B$71</f>
+        <f>Inputs!D118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="E17" s="35">
-        <f>Inputs!E113+Inputs!$B$71</f>
+        <f>Inputs!E118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="F17" s="35">
-        <f>Inputs!F113+Inputs!$B$71</f>
+        <f>Inputs!F118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="G17" s="35">
-        <f>Inputs!G113+Inputs!$B$71</f>
+        <f>Inputs!G118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="H17" s="35">
-        <f>Inputs!H113+Inputs!$B$71</f>
+        <f>Inputs!H118+Inputs!$B$71</f>
         <v/>
       </c>
       <c r="I17" s="35">
-        <f>Inputs!I113+Inputs!$B$71</f>
+        <f>Inputs!I118+Inputs!$B$71</f>
         <v/>
       </c>
     </row>
@@ -10986,31 +12991,31 @@
         <v/>
       </c>
       <c r="C19" s="41">
-        <f>B19*(1+Inputs!C120)</f>
+        <f>B19*(1+Inputs!C126)</f>
         <v/>
       </c>
       <c r="D19" s="41">
-        <f>C19*(1+Inputs!D120)</f>
+        <f>C19*(1+Inputs!D126)</f>
         <v/>
       </c>
       <c r="E19" s="41">
-        <f>D19*(1+Inputs!E120)</f>
+        <f>D19*(1+Inputs!E126)</f>
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>E19*(1+Inputs!F120)</f>
+        <f>E19*(1+Inputs!F126)</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>F19*(1+Inputs!G120)</f>
+        <f>F19*(1+Inputs!G126)</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>G19*(1+Inputs!H120)</f>
+        <f>G19*(1+Inputs!H126)</f>
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>H19*(1+Inputs!I120)</f>
+        <f>H19*(1+Inputs!I126)</f>
         <v/>
       </c>
     </row>
@@ -11104,31 +13109,31 @@
         <v/>
       </c>
       <c r="C22" s="41">
-        <f>B22*(1+Inputs!C120)</f>
+        <f>B22*(1+Inputs!C126)</f>
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>C22*(1+Inputs!D120)</f>
+        <f>C22*(1+Inputs!D126)</f>
         <v/>
       </c>
       <c r="E22" s="41">
-        <f>D22*(1+Inputs!E120)</f>
+        <f>D22*(1+Inputs!E126)</f>
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>E22*(1+Inputs!F120)</f>
+        <f>E22*(1+Inputs!F126)</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>F22*(1+Inputs!G120)</f>
+        <f>F22*(1+Inputs!G126)</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>G22*(1+Inputs!H120)</f>
+        <f>G22*(1+Inputs!H126)</f>
         <v/>
       </c>
       <c r="I22" s="41">
-        <f>H22*(1+Inputs!I120)</f>
+        <f>H22*(1+Inputs!I126)</f>
         <v/>
       </c>
     </row>
@@ -11295,31 +13300,31 @@
         <v/>
       </c>
       <c r="C27" s="39">
-        <f>Inputs!C148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!C158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="D27" s="39">
-        <f>Inputs!D148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!D158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>Inputs!E148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!E158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="F27" s="39">
-        <f>Inputs!F148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!F158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="G27" s="39">
-        <f>Inputs!G148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!G158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="H27" s="39">
-        <f>Inputs!H148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!H158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="I27" s="39">
-        <f>Inputs!I148*Inputs!$B$74*(1-Inputs!$B$76)</f>
+        <f>Inputs!I158*Inputs!$B$74*(1-Inputs!$B$77)</f>
         <v/>
       </c>
       <c r="J27" s="41">
@@ -11600,90 +13605,101 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>- Payment for TSMC Arizona assets (TaiwanMax only)</t>
+        </is>
+      </c>
+      <c r="B42" s="41">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B42" s="41">
-        <f>B38+B39+B40+B41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="B43" s="41">
+        <f>B38+B39+B40+B41+B42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Diluted shares (bn)</t>
         </is>
       </c>
-      <c r="B43" s="40">
+      <c r="B44" s="40">
         <f>Inputs!$B$9</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>Value per share ($)</t>
         </is>
       </c>
-      <c r="B44" s="37">
-        <f>IF(B43=0,0,MAX(0,B42/B43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Current share price ($)</t>
-        </is>
-      </c>
-      <c r="B45" s="36">
-        <f>Inputs!$B$4</f>
+      <c r="B45" s="37">
+        <f>IF(B44=0,0,MAX(0,B43/B44))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Upside / (downside) vs price</t>
-        </is>
-      </c>
-      <c r="B46" s="42">
-        <f>IF(B45=0,0,B44/B45-1)</f>
+          <t>Current share price ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="36">
+        <f>Inputs!$B$4</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Terminal value as % of EV</t>
+          <t>Upside / (downside) vs price</t>
         </is>
       </c>
       <c r="B47" s="42">
-        <f>IF(B38=0,0,B37/B38)</f>
+        <f>IF(B46=0,0,B45/B46-1)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Implied P/E on 2027 NOPAT/share at value</t>
-        </is>
-      </c>
-      <c r="B48" s="11">
-        <f>IF(C25&lt;=0,0,B44/(C25/B43))</f>
+          <t>Terminal value as % of EV</t>
+        </is>
+      </c>
+      <c r="B48" s="42">
+        <f>IF(B38=0,0,B37/B38)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>Implied P/E on 2027 NOPAT/share at value</t>
+        </is>
+      </c>
+      <c r="B49" s="11">
+        <f>IF(C25&lt;=0,0,B45/(C25/B44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Market P/E on 2027 NOPAT/share</t>
         </is>
       </c>
-      <c r="B49" s="11">
-        <f>IF(C25&lt;=0,0,B45/(C25/B43))</f>
+      <c r="B50" s="11">
+        <f>IF(C25&lt;=0,0,B46/(C25/B44))</f>
         <v/>
       </c>
     </row>
